--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD933992-36B5-4A1A-A1FC-07798FC6CB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DDFD51-402B-4989-A279-C8273E2E8033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$Q$102</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="34">
   <si>
     <t>H22</t>
   </si>
@@ -119,13 +122,32 @@
   <si>
     <t>H36</t>
   </si>
+  <si>
+    <t>gTRUE</t>
+  </si>
+  <si>
+    <t>x1030.884</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -265,61 +287,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -749,22 +771,22 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(F2:H2)</f>
-        <v>1110.1949999999999</v>
+        <v>401.53999999999996</v>
       </c>
       <c r="E2" s="5">
-        <v>369.21100000000001</v>
+        <v>379.02</v>
       </c>
       <c r="F2" s="6">
-        <v>257.93099999999998</v>
+        <v>142.38</v>
       </c>
       <c r="G2" s="6">
-        <v>205.797</v>
+        <v>120.7</v>
       </c>
       <c r="H2" s="6">
-        <v>646.46699999999998</v>
+        <v>138.46</v>
       </c>
       <c r="I2" s="7">
-        <v>1081.153</v>
+        <v>226.37</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>0</v>
@@ -777,57 +799,57 @@
       </c>
       <c r="M2" s="4">
         <f>SUM(O2:Q2)</f>
-        <v>32.097999999999999</v>
+        <v>35.099999999999994</v>
       </c>
       <c r="N2" s="5">
-        <v>66.688000000000002</v>
+        <v>67.77</v>
       </c>
       <c r="O2" s="6">
-        <v>4.835</v>
+        <v>5.3</v>
       </c>
       <c r="P2" s="6">
-        <v>11.948</v>
+        <v>12.99</v>
       </c>
       <c r="Q2" s="6">
-        <v>15.315</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="R2" s="7">
-        <v>26.135999999999999</v>
+        <v>28.39</v>
       </c>
       <c r="S2" s="16" t="s">
         <v>0</v>
       </c>
       <c r="T2" s="5">
-        <f>ROUND(B2/K2,3)</f>
+        <f t="shared" ref="T2:T16" si="0">ROUND(B2/K2,3)</f>
         <v>1</v>
       </c>
       <c r="U2" s="5">
-        <f>ROUND(C2/L2,3)</f>
+        <f t="shared" ref="U2:U16" si="1">ROUND(C2/L2,3)</f>
         <v>1</v>
       </c>
       <c r="V2" s="4">
-        <f>ROUND(D2/M2,3)</f>
-        <v>34.588000000000001</v>
+        <f t="shared" ref="V2:V16" si="2">ROUND(D2/M2,3)</f>
+        <v>11.44</v>
       </c>
       <c r="W2" s="5">
-        <f>ROUND(E2/N2,3)</f>
-        <v>5.5359999999999996</v>
+        <f t="shared" ref="W2:W16" si="3">ROUND(E2/N2,3)</f>
+        <v>5.593</v>
       </c>
       <c r="X2" s="6">
-        <f>ROUND(F2/O2,3)</f>
-        <v>53.347000000000001</v>
+        <f t="shared" ref="X2:X16" si="4">ROUND(F2/O2,3)</f>
+        <v>26.864000000000001</v>
       </c>
       <c r="Y2" s="6">
-        <f>ROUND(G2/P2,3)</f>
-        <v>17.224</v>
+        <f t="shared" ref="Y2:Y16" si="5">ROUND(G2/P2,3)</f>
+        <v>9.2919999999999998</v>
       </c>
       <c r="Z2" s="6">
-        <f>ROUND(H2/Q2,3)</f>
-        <v>42.210999999999999</v>
+        <f t="shared" ref="Z2:Z16" si="6">ROUND(H2/Q2,3)</f>
+        <v>8.2370000000000001</v>
       </c>
       <c r="AA2" s="7">
-        <f>ROUND(I2/R2,3)</f>
-        <v>41.366</v>
+        <f t="shared" ref="AA2:AA16" si="7">ROUND(I2/R2,3)</f>
+        <v>7.9740000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -836,95 +858,95 @@
       </c>
       <c r="B3" s="2">
         <f>D$2/D3</f>
-        <v>1.5594422391342821</v>
+        <v>1.5459900666076312</v>
       </c>
       <c r="C3" s="2">
         <f>D2/D3</f>
-        <v>1.5594422391342821</v>
+        <v>1.5459900666076312</v>
       </c>
       <c r="D3" s="8">
-        <f t="shared" ref="D3:D16" si="0">SUM(F3:H3)</f>
-        <v>711.91800000000001</v>
+        <f t="shared" ref="D3:D16" si="8">SUM(F3:H3)</f>
+        <v>259.72999999999996</v>
       </c>
       <c r="E3" s="5">
-        <v>376.32499999999999</v>
+        <v>379.46</v>
       </c>
       <c r="F3" s="6">
-        <v>264.76499999999999</v>
+        <v>139.13</v>
       </c>
       <c r="G3" s="6">
-        <v>439.76499999999999</v>
+        <v>118.16</v>
       </c>
       <c r="H3" s="1">
-        <v>7.3879999999999999</v>
+        <v>2.44</v>
       </c>
       <c r="I3" s="9">
-        <v>1124.867</v>
+        <v>227.29</v>
       </c>
       <c r="J3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="2">
         <f>M$2/M3</f>
-        <v>1.8711670747347557</v>
+        <v>1.9306930693069304</v>
       </c>
       <c r="L3" s="2">
         <f>M2/M3</f>
-        <v>1.8711670747347557</v>
+        <v>1.9306930693069304</v>
       </c>
       <c r="M3" s="8">
-        <f t="shared" ref="M3:M16" si="1">SUM(O3:Q3)</f>
-        <v>17.154</v>
+        <f t="shared" ref="M3:M16" si="9">SUM(O3:Q3)</f>
+        <v>18.18</v>
       </c>
       <c r="N3" s="5">
-        <v>65.647999999999996</v>
+        <v>68.98</v>
       </c>
       <c r="O3" s="6">
-        <v>4.7640000000000002</v>
+        <v>5.09</v>
       </c>
       <c r="P3" s="6">
-        <v>11.94</v>
+        <v>12.62</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="R3" s="9">
-        <v>25.870999999999999</v>
+        <v>27.38</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="2">
-        <f>ROUND(B3/K3,3)</f>
-        <v>0.83299999999999996</v>
+        <f t="shared" si="0"/>
+        <v>0.80100000000000005</v>
       </c>
       <c r="U3" s="2">
-        <f>ROUND(C3/L3,3)</f>
-        <v>0.83299999999999996</v>
+        <f t="shared" si="1"/>
+        <v>0.80100000000000005</v>
       </c>
       <c r="V3" s="8">
-        <f>ROUND(D3/M3,3)</f>
-        <v>41.502000000000002</v>
+        <f t="shared" si="2"/>
+        <v>14.287000000000001</v>
       </c>
       <c r="W3" s="5">
-        <f>ROUND(E3/N3,3)</f>
-        <v>5.7320000000000002</v>
+        <f t="shared" si="3"/>
+        <v>5.5010000000000003</v>
       </c>
       <c r="X3" s="6">
-        <f>ROUND(F3/O3,3)</f>
-        <v>55.576000000000001</v>
+        <f t="shared" si="4"/>
+        <v>27.334</v>
       </c>
       <c r="Y3" s="6">
-        <f>ROUND(G3/P3,3)</f>
-        <v>36.831000000000003</v>
+        <f t="shared" si="5"/>
+        <v>9.3629999999999995</v>
       </c>
       <c r="Z3" s="1">
-        <f>ROUND(H3/Q3,3)</f>
-        <v>16.417999999999999</v>
+        <f t="shared" si="6"/>
+        <v>5.1909999999999998</v>
       </c>
       <c r="AA3" s="9">
-        <f>ROUND(I3/R3,3)</f>
-        <v>43.48</v>
+        <f t="shared" si="7"/>
+        <v>8.3010000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -932,96 +954,96 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B12" si="2">D$2/D4</f>
-        <v>2.0688122631066981</v>
+        <f t="shared" ref="B4:B12" si="10">D$2/D4</f>
+        <v>1.9822283655032826</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C12" si="3">D3/D4</f>
-        <v>1.3266360312615302</v>
+        <f t="shared" ref="C4:C12" si="11">D3/D4</f>
+        <v>1.2821740632867649</v>
       </c>
       <c r="D4" s="8">
-        <f t="shared" si="0"/>
-        <v>536.63400000000001</v>
+        <f t="shared" si="8"/>
+        <v>202.57</v>
       </c>
       <c r="E4" s="5">
-        <v>366.06299999999999</v>
+        <v>364.8</v>
       </c>
       <c r="F4" s="1">
-        <v>106.236</v>
+        <v>74.77</v>
       </c>
       <c r="G4" s="6">
-        <v>422.755</v>
+        <v>125.29</v>
       </c>
       <c r="H4" s="6">
-        <v>7.6429999999999998</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="I4" s="7">
-        <v>1082.0139999999999</v>
+        <v>222.02</v>
       </c>
       <c r="J4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="2">
-        <f t="shared" ref="K4:K12" si="4">M$2/M4</f>
-        <v>1.9399250574156897</v>
+        <f t="shared" ref="K4:K12" si="12">M$2/M4</f>
+        <v>2.0671378091872787</v>
       </c>
       <c r="L4" s="2">
-        <f t="shared" ref="L4:L12" si="5">M3/M4</f>
-        <v>1.0367460413392966</v>
+        <f t="shared" ref="L4:L12" si="13">M3/M4</f>
+        <v>1.0706713780918728</v>
       </c>
       <c r="M4" s="8">
-        <f t="shared" si="1"/>
-        <v>16.545999999999999</v>
+        <f t="shared" si="9"/>
+        <v>16.98</v>
       </c>
       <c r="N4" s="5">
-        <v>65.464000000000013</v>
+        <v>68.959999999999994</v>
       </c>
       <c r="O4" s="1">
-        <v>3.714</v>
+        <v>3.8</v>
       </c>
       <c r="P4" s="6">
-        <v>12.343</v>
+        <v>12.7</v>
       </c>
       <c r="Q4" s="6">
-        <v>0.48899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="R4" s="7">
-        <v>27.152999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="S4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <f>ROUND(B4/K4,3)</f>
-        <v>1.0660000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.95899999999999996</v>
       </c>
       <c r="U4" s="2">
-        <f>ROUND(C4/L4,3)</f>
-        <v>1.28</v>
+        <f t="shared" si="1"/>
+        <v>1.198</v>
       </c>
       <c r="V4" s="8">
-        <f>ROUND(D4/M4,3)</f>
-        <v>32.433</v>
+        <f t="shared" si="2"/>
+        <v>11.93</v>
       </c>
       <c r="W4" s="5">
-        <f>ROUND(E4/N4,3)</f>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="3"/>
+        <v>5.29</v>
       </c>
       <c r="X4" s="1">
-        <f>ROUND(F4/O4,3)</f>
-        <v>28.603999999999999</v>
+        <f t="shared" si="4"/>
+        <v>19.675999999999998</v>
       </c>
       <c r="Y4" s="6">
-        <f>ROUND(G4/P4,3)</f>
-        <v>34.250999999999998</v>
+        <f t="shared" si="5"/>
+        <v>9.8650000000000002</v>
       </c>
       <c r="Z4" s="6">
-        <f>ROUND(H4/Q4,3)</f>
-        <v>15.63</v>
+        <f t="shared" si="6"/>
+        <v>5.2290000000000001</v>
       </c>
       <c r="AA4" s="7">
-        <f>ROUND(I4/R4,3)</f>
-        <v>39.848999999999997</v>
+        <f t="shared" si="7"/>
+        <v>8.1029999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1029,96 +1051,96 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" si="2"/>
-        <v>3.7036005350929577</v>
+        <f t="shared" si="10"/>
+        <v>2.2621971830985914</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="3"/>
-        <v>1.7902061976040915</v>
+        <f t="shared" si="11"/>
+        <v>1.1412394366197183</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="0"/>
-        <v>299.76099999999997</v>
+        <f t="shared" si="8"/>
+        <v>177.5</v>
       </c>
       <c r="E5" s="5">
-        <v>376.71799999999996</v>
+        <v>379.87</v>
       </c>
       <c r="F5" s="6">
-        <v>109.84399999999999</v>
+        <v>75.06</v>
       </c>
       <c r="G5" s="1">
-        <v>182.58099999999999</v>
+        <v>100.06</v>
       </c>
       <c r="H5" s="6">
-        <v>7.3360000000000003</v>
+        <v>2.38</v>
       </c>
       <c r="I5" s="7">
-        <v>946.61900000000003</v>
+        <v>221.9</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="4"/>
-        <v>3.5137383689107828</v>
+        <f t="shared" si="12"/>
+        <v>3.7741935483870961</v>
       </c>
       <c r="L5" s="2">
-        <f t="shared" si="5"/>
-        <v>1.8112753147235905</v>
+        <f t="shared" si="13"/>
+        <v>1.8258064516129031</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="1"/>
-        <v>9.1349999999999998</v>
+        <f t="shared" si="9"/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="N5" s="5">
-        <v>68.033000000000001</v>
+        <v>67.48</v>
       </c>
       <c r="O5" s="6">
-        <v>3.7240000000000002</v>
+        <v>3.79</v>
       </c>
       <c r="P5" s="1">
-        <v>4.9530000000000003</v>
+        <v>5.03</v>
       </c>
       <c r="Q5" s="6">
-        <v>0.45800000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="R5" s="7">
-        <v>27.033999999999999</v>
+        <v>27.22</v>
       </c>
       <c r="S5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="T5" s="2">
-        <f>ROUND(B5/K5,3)</f>
-        <v>1.054</v>
+        <f t="shared" si="0"/>
+        <v>0.59899999999999998</v>
       </c>
       <c r="U5" s="2">
-        <f>ROUND(C5/L5,3)</f>
-        <v>0.98799999999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.625</v>
       </c>
       <c r="V5" s="8">
-        <f>ROUND(D5/M5,3)</f>
-        <v>32.814999999999998</v>
+        <f t="shared" si="2"/>
+        <v>19.085999999999999</v>
       </c>
       <c r="W5" s="5">
-        <f>ROUND(E5/N5,3)</f>
-        <v>5.5369999999999999</v>
+        <f t="shared" si="3"/>
+        <v>5.6289999999999996</v>
       </c>
       <c r="X5" s="6">
-        <f>ROUND(F5/O5,3)</f>
-        <v>29.495999999999999</v>
+        <f t="shared" si="4"/>
+        <v>19.805</v>
       </c>
       <c r="Y5" s="1">
-        <f>ROUND(G5/P5,3)</f>
-        <v>36.863</v>
+        <f t="shared" si="5"/>
+        <v>19.893000000000001</v>
       </c>
       <c r="Z5" s="6">
-        <f>ROUND(H5/Q5,3)</f>
-        <v>16.016999999999999</v>
+        <f t="shared" si="6"/>
+        <v>4.9580000000000002</v>
       </c>
       <c r="AA5" s="7">
-        <f>ROUND(I5/R5,3)</f>
-        <v>35.015999999999998</v>
+        <f t="shared" si="7"/>
+        <v>8.1519999999999992</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1126,96 +1148,96 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" si="2"/>
-        <v>3.7416964096134593</v>
+        <f t="shared" si="10"/>
+        <v>2.3345348837209294</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" si="3"/>
-        <v>1.0102861726472738</v>
+        <f t="shared" si="11"/>
+        <v>1.0319767441860463</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" si="0"/>
-        <v>296.709</v>
+        <f t="shared" si="8"/>
+        <v>172.00000000000003</v>
       </c>
       <c r="E6" s="5">
-        <v>378.40699999999998</v>
+        <v>361.21</v>
       </c>
       <c r="F6" s="6">
-        <v>106.133</v>
+        <v>73.44</v>
       </c>
       <c r="G6" s="6">
-        <v>183.876</v>
+        <v>96.29</v>
       </c>
       <c r="H6" s="10">
-        <v>6.7</v>
+        <v>2.27</v>
       </c>
       <c r="I6" s="3">
-        <v>155.20400000000001</v>
+        <v>80.819999999999993</v>
       </c>
       <c r="J6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="5">
-        <f t="shared" si="4"/>
-        <v>3.5620907779380753</v>
+        <f t="shared" si="12"/>
+        <v>3.7864077669902909</v>
       </c>
       <c r="L6" s="5">
-        <f t="shared" si="5"/>
-        <v>1.0137609588280989</v>
+        <f t="shared" si="13"/>
+        <v>1.0032362459546926</v>
       </c>
       <c r="M6" s="4">
-        <f t="shared" si="1"/>
-        <v>9.011000000000001</v>
+        <f t="shared" si="9"/>
+        <v>9.27</v>
       </c>
       <c r="N6" s="5">
-        <v>66.353999999999999</v>
+        <v>67.34</v>
       </c>
       <c r="O6" s="6">
-        <v>3.64</v>
+        <v>3.79</v>
       </c>
       <c r="P6" s="6">
-        <v>4.8940000000000001</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="10">
-        <v>0.47699999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="R6" s="3">
-        <v>4.4000000000000004</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="S6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="T6" s="5">
-        <f>ROUND(B6/K6,3)</f>
-        <v>1.05</v>
+        <f t="shared" si="0"/>
+        <v>0.61699999999999999</v>
       </c>
       <c r="U6" s="5">
-        <f>ROUND(C6/L6,3)</f>
-        <v>0.997</v>
+        <f t="shared" si="1"/>
+        <v>1.0289999999999999</v>
       </c>
       <c r="V6" s="4">
-        <f>ROUND(D6/M6,3)</f>
-        <v>32.927</v>
+        <f t="shared" si="2"/>
+        <v>18.553999999999998</v>
       </c>
       <c r="W6" s="5">
-        <f>ROUND(E6/N6,3)</f>
-        <v>5.7030000000000003</v>
+        <f t="shared" si="3"/>
+        <v>5.3639999999999999</v>
       </c>
       <c r="X6" s="6">
-        <f>ROUND(F6/O6,3)</f>
-        <v>29.157</v>
+        <f t="shared" si="4"/>
+        <v>19.376999999999999</v>
       </c>
       <c r="Y6" s="6">
-        <f>ROUND(G6/P6,3)</f>
-        <v>37.572000000000003</v>
+        <f t="shared" si="5"/>
+        <v>19.257999999999999</v>
       </c>
       <c r="Z6" s="10">
-        <f>ROUND(H6/Q6,3)</f>
-        <v>14.045999999999999</v>
+        <f t="shared" si="6"/>
+        <v>4.7290000000000001</v>
       </c>
       <c r="AA6" s="3">
-        <f>ROUND(I6/R6,3)</f>
-        <v>35.274000000000001</v>
+        <f t="shared" si="7"/>
+        <v>17.724</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1223,96 +1245,96 @@
         <v>5</v>
       </c>
       <c r="B7" s="5">
-        <f t="shared" si="2"/>
-        <v>3.6921457576049832</v>
+        <f t="shared" si="10"/>
+        <v>2.1703691692340952</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" si="3"/>
-        <v>0.98675716931999968</v>
+        <f t="shared" si="11"/>
+        <v>0.92967947678503882</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" si="0"/>
-        <v>300.69099999999997</v>
+        <f t="shared" si="8"/>
+        <v>185.01</v>
       </c>
       <c r="E7" s="5">
-        <v>369.14400000000001</v>
+        <v>377.51</v>
       </c>
       <c r="F7" s="6">
-        <v>115.97799999999999</v>
+        <v>82.34</v>
       </c>
       <c r="G7" s="6">
-        <v>181.94800000000001</v>
+        <v>101.48</v>
       </c>
       <c r="H7" s="1">
-        <v>2.7650000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="I7" s="7">
-        <v>155.75899999999999</v>
+        <v>82.8</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="4"/>
-        <v>3.7051829620223939</v>
+        <f t="shared" si="12"/>
+        <v>3.908685968819599</v>
       </c>
       <c r="L7" s="5">
-        <f t="shared" si="5"/>
-        <v>1.0401708415098696</v>
+        <f t="shared" si="13"/>
+        <v>1.0322939866369711</v>
       </c>
       <c r="M7" s="4">
-        <f t="shared" si="1"/>
-        <v>8.6630000000000003</v>
+        <f t="shared" si="9"/>
+        <v>8.9799999999999986</v>
       </c>
       <c r="N7" s="5">
-        <v>76.664000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="O7" s="6">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P7" s="6">
-        <v>4.9160000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.20699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="R7" s="7">
-        <v>4.4710000000000001</v>
+        <v>4.57</v>
       </c>
       <c r="S7" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="5">
-        <f>ROUND(B7/K7,3)</f>
-        <v>0.996</v>
+        <f t="shared" si="0"/>
+        <v>0.55500000000000005</v>
       </c>
       <c r="U7" s="5">
-        <f>ROUND(C7/L7,3)</f>
-        <v>0.94899999999999995</v>
+        <f t="shared" si="1"/>
+        <v>0.90100000000000002</v>
       </c>
       <c r="V7" s="4">
-        <f>ROUND(D7/M7,3)</f>
-        <v>34.71</v>
+        <f t="shared" si="2"/>
+        <v>20.602</v>
       </c>
       <c r="W7" s="5">
-        <f>ROUND(E7/N7,3)</f>
-        <v>4.8150000000000004</v>
+        <f t="shared" si="3"/>
+        <v>4.8639999999999999</v>
       </c>
       <c r="X7" s="6">
-        <f>ROUND(F7/O7,3)</f>
-        <v>32.762</v>
+        <f t="shared" si="4"/>
+        <v>22.375</v>
       </c>
       <c r="Y7" s="6">
-        <f>ROUND(G7/P7,3)</f>
-        <v>37.011000000000003</v>
+        <f t="shared" si="5"/>
+        <v>19.898</v>
       </c>
       <c r="Z7" s="1">
-        <f>ROUND(H7/Q7,3)</f>
-        <v>13.356999999999999</v>
+        <f t="shared" si="6"/>
+        <v>5.95</v>
       </c>
       <c r="AA7" s="7">
-        <f>ROUND(I7/R7,3)</f>
-        <v>34.838000000000001</v>
+        <f t="shared" si="7"/>
+        <v>18.117999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1320,96 +1342,96 @@
         <v>6</v>
       </c>
       <c r="B8" s="5">
-        <f t="shared" si="2"/>
-        <v>3.6069416557827632</v>
+        <f t="shared" si="10"/>
+        <v>2.1691966938577059</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" si="3"/>
-        <v>0.97692287698915492</v>
+        <f t="shared" si="11"/>
+        <v>0.99945978067095231</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" si="0"/>
-        <v>307.79400000000004</v>
+        <f t="shared" si="8"/>
+        <v>185.11</v>
       </c>
       <c r="E8" s="5">
-        <v>474.36200000000002</v>
+        <v>492.18</v>
       </c>
       <c r="F8" s="6">
-        <v>117.661</v>
+        <v>82.65</v>
       </c>
       <c r="G8" s="6">
-        <v>187.90100000000001</v>
+        <v>101.41</v>
       </c>
       <c r="H8" s="6">
-        <v>2.2320000000000002</v>
+        <v>1.05</v>
       </c>
       <c r="I8" s="7">
-        <v>158.601</v>
+        <v>82.93</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="4"/>
-        <v>3.6654105287198813</v>
+        <f t="shared" si="12"/>
+        <v>3.9795918367346932</v>
       </c>
       <c r="L8" s="5">
-        <f t="shared" si="5"/>
-        <v>0.98926573027292464</v>
+        <f t="shared" si="13"/>
+        <v>1.0181405895691609</v>
       </c>
       <c r="M8" s="4">
-        <f t="shared" si="1"/>
-        <v>8.7569999999999997</v>
+        <f t="shared" si="9"/>
+        <v>8.82</v>
       </c>
       <c r="N8" s="5">
-        <v>88.951999999999998</v>
+        <v>96.53</v>
       </c>
       <c r="O8" s="6">
-        <v>3.6080000000000001</v>
+        <v>3.62</v>
       </c>
       <c r="P8" s="6">
-        <v>4.9589999999999996</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="6">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="R8" s="7">
-        <v>4.4660000000000002</v>
+        <v>4.47</v>
       </c>
       <c r="S8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="T8" s="5">
-        <f>ROUND(B8/K8,3)</f>
-        <v>0.98399999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.54500000000000004</v>
       </c>
       <c r="U8" s="5">
-        <f>ROUND(C8/L8,3)</f>
-        <v>0.98799999999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.98199999999999998</v>
       </c>
       <c r="V8" s="4">
-        <f>ROUND(D8/M8,3)</f>
-        <v>35.148000000000003</v>
+        <f t="shared" si="2"/>
+        <v>20.988</v>
       </c>
       <c r="W8" s="5">
-        <f>ROUND(E8/N8,3)</f>
-        <v>5.3330000000000002</v>
+        <f t="shared" si="3"/>
+        <v>5.0990000000000002</v>
       </c>
       <c r="X8" s="6">
-        <f>ROUND(F8/O8,3)</f>
-        <v>32.610999999999997</v>
+        <f t="shared" si="4"/>
+        <v>22.831</v>
       </c>
       <c r="Y8" s="6">
-        <f>ROUND(G8/P8,3)</f>
-        <v>37.890999999999998</v>
+        <f t="shared" si="5"/>
+        <v>20.282</v>
       </c>
       <c r="Z8" s="6">
-        <f>ROUND(H8/Q8,3)</f>
-        <v>11.747</v>
+        <f t="shared" si="6"/>
+        <v>5.25</v>
       </c>
       <c r="AA8" s="7">
-        <f>ROUND(I8/R8,3)</f>
-        <v>35.512999999999998</v>
+        <f t="shared" si="7"/>
+        <v>18.553000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1417,96 +1439,96 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" si="2"/>
-        <v>3.6616292377563102</v>
+        <f t="shared" si="10"/>
+        <v>2.2096632181377944</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" si="3"/>
-        <v>1.0151617595160902</v>
+        <f t="shared" si="11"/>
+        <v>1.0186550737398197</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="0"/>
-        <v>303.197</v>
+        <f t="shared" si="8"/>
+        <v>181.71999999999997</v>
       </c>
       <c r="E9" s="5">
-        <v>484.762</v>
+        <v>489.21</v>
       </c>
       <c r="F9" s="6">
-        <v>114.488</v>
+        <v>81.44</v>
       </c>
       <c r="G9" s="6">
-        <v>186.03100000000001</v>
+        <v>99.21</v>
       </c>
       <c r="H9" s="6">
-        <v>2.6779999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="I9" s="7">
-        <v>159.75899999999999</v>
+        <v>80.959999999999994</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="4"/>
-        <v>3.7245300533766534</v>
+        <f t="shared" si="12"/>
+        <v>4.0391254315304943</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="5"/>
-        <v>1.0161290322580645</v>
+        <f t="shared" si="13"/>
+        <v>1.0149597238204835</v>
       </c>
       <c r="M9" s="4">
-        <f t="shared" si="1"/>
-        <v>8.6180000000000003</v>
+        <f t="shared" si="9"/>
+        <v>8.69</v>
       </c>
       <c r="N9" s="5">
-        <v>91.009</v>
+        <v>91.73</v>
       </c>
       <c r="O9" s="6">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="P9" s="6">
-        <v>4.8780000000000001</v>
+        <v>4.92</v>
       </c>
       <c r="Q9" s="6">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="R9" s="7">
-        <v>4.42</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="S9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="T9" s="5">
-        <f>ROUND(B9/K9,3)</f>
-        <v>0.98299999999999998</v>
+        <f t="shared" si="0"/>
+        <v>0.54700000000000004</v>
       </c>
       <c r="U9" s="5">
-        <f>ROUND(C9/L9,3)</f>
-        <v>0.999</v>
+        <f t="shared" si="1"/>
+        <v>1.004</v>
       </c>
       <c r="V9" s="4">
-        <f>ROUND(D9/M9,3)</f>
-        <v>35.182000000000002</v>
+        <f t="shared" si="2"/>
+        <v>20.911000000000001</v>
       </c>
       <c r="W9" s="5">
-        <f>ROUND(E9/N9,3)</f>
-        <v>5.327</v>
+        <f t="shared" si="3"/>
+        <v>5.3330000000000002</v>
       </c>
       <c r="X9" s="6">
-        <f>ROUND(F9/O9,3)</f>
-        <v>32.25</v>
+        <f t="shared" si="4"/>
+        <v>22.812000000000001</v>
       </c>
       <c r="Y9" s="6">
-        <f>ROUND(G9/P9,3)</f>
-        <v>38.137</v>
+        <f t="shared" si="5"/>
+        <v>20.164999999999999</v>
       </c>
       <c r="Z9" s="6">
-        <f>ROUND(H9/Q9,3)</f>
-        <v>14.095000000000001</v>
+        <f t="shared" si="6"/>
+        <v>5.35</v>
       </c>
       <c r="AA9" s="7">
-        <f>ROUND(I9/R9,3)</f>
-        <v>36.145000000000003</v>
+        <f t="shared" si="7"/>
+        <v>18.234000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1514,96 +1536,96 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <f t="shared" si="2"/>
-        <v>3.6123638280426387</v>
+        <f t="shared" si="10"/>
+        <v>2.2138052707023927</v>
       </c>
       <c r="C10" s="5">
-        <f t="shared" si="3"/>
-        <v>0.98654549477438103</v>
+        <f t="shared" si="11"/>
+        <v>1.0018745175873855</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="0"/>
-        <v>307.33199999999994</v>
+        <f t="shared" si="8"/>
+        <v>181.38</v>
       </c>
       <c r="E10" s="2">
-        <v>247.297</v>
+        <v>249.29</v>
       </c>
       <c r="F10" s="6">
-        <v>120.297</v>
+        <v>81.16</v>
       </c>
       <c r="G10" s="6">
-        <v>184.65199999999999</v>
+        <v>99</v>
       </c>
       <c r="H10" s="10">
-        <v>2.383</v>
+        <v>1.22</v>
       </c>
       <c r="I10" s="7">
-        <v>157.55099999999999</v>
+        <v>80.72</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="K10" s="5">
-        <f t="shared" si="4"/>
-        <v>3.6750629722921921</v>
+        <f t="shared" si="12"/>
+        <v>3.9705882352941169</v>
       </c>
       <c r="L10" s="5">
-        <f t="shared" si="5"/>
-        <v>0.9867185711014429</v>
+        <f t="shared" si="13"/>
+        <v>0.98303167420814475</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" si="1"/>
-        <v>8.7339999999999982</v>
+        <f t="shared" si="9"/>
+        <v>8.84</v>
       </c>
       <c r="N10" s="2">
-        <v>74.891999999999996</v>
+        <v>76.53</v>
       </c>
       <c r="O10" s="6">
-        <v>3.5640000000000001</v>
+        <v>3.62</v>
       </c>
       <c r="P10" s="6">
-        <v>4.9729999999999999</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="Q10" s="10">
-        <v>0.19700000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="R10" s="7">
-        <v>4.468</v>
+        <v>4.54</v>
       </c>
       <c r="S10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="T10" s="5">
-        <f>ROUND(B10/K10,3)</f>
-        <v>0.98299999999999998</v>
+        <f t="shared" si="0"/>
+        <v>0.55800000000000005</v>
       </c>
       <c r="U10" s="5">
-        <f>ROUND(C10/L10,3)</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>1.0189999999999999</v>
       </c>
       <c r="V10" s="4">
-        <f>ROUND(D10/M10,3)</f>
-        <v>35.188000000000002</v>
+        <f t="shared" si="2"/>
+        <v>20.518000000000001</v>
       </c>
       <c r="W10" s="2">
-        <f>ROUND(E10/N10,3)</f>
-        <v>3.302</v>
+        <f t="shared" si="3"/>
+        <v>3.2570000000000001</v>
       </c>
       <c r="X10" s="6">
-        <f>ROUND(F10/O10,3)</f>
-        <v>33.753</v>
+        <f t="shared" si="4"/>
+        <v>22.42</v>
       </c>
       <c r="Y10" s="6">
-        <f>ROUND(G10/P10,3)</f>
-        <v>37.131</v>
+        <f t="shared" si="5"/>
+        <v>19.721</v>
       </c>
       <c r="Z10" s="10">
-        <f>ROUND(H10/Q10,3)</f>
-        <v>12.096</v>
+        <f t="shared" si="6"/>
+        <v>6.1</v>
       </c>
       <c r="AA10" s="7">
-        <f>ROUND(I10/R10,3)</f>
-        <v>35.262</v>
+        <f t="shared" si="7"/>
+        <v>17.78</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1611,96 +1633,96 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <f t="shared" si="2"/>
-        <v>4.6453617306163437</v>
+        <f t="shared" si="10"/>
+        <v>2.7188028979619472</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="3"/>
-        <v>1.2859617557219964</v>
+        <f t="shared" si="11"/>
+        <v>1.2281129392646759</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="0"/>
-        <v>238.99</v>
+        <f t="shared" si="8"/>
+        <v>147.69</v>
       </c>
       <c r="E11" s="5">
-        <v>212.548</v>
+        <v>215.95</v>
       </c>
       <c r="F11" s="1">
-        <v>48.052999999999997</v>
+        <v>43.93</v>
       </c>
       <c r="G11" s="6">
-        <v>188.84100000000001</v>
+        <v>102.58</v>
       </c>
       <c r="H11" s="6">
-        <v>2.0960000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="I11" s="9">
-        <v>162.86699999999999</v>
+        <v>90.86</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" si="4"/>
-        <v>4.0344394167923578</v>
+        <f t="shared" si="12"/>
+        <v>4.3120393120393112</v>
       </c>
       <c r="L11" s="2">
-        <f t="shared" si="5"/>
-        <v>1.0977878330819506</v>
+        <f t="shared" si="13"/>
+        <v>1.085995085995086</v>
       </c>
       <c r="M11" s="8">
-        <f t="shared" si="1"/>
-        <v>7.9559999999999995</v>
+        <f t="shared" si="9"/>
+        <v>8.14</v>
       </c>
       <c r="N11" s="5">
-        <v>73.527000000000001</v>
+        <v>76.48</v>
       </c>
       <c r="O11" s="1">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P11" s="6">
-        <v>6.3529999999999998</v>
+        <v>6.49</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.193</v>
+        <v>0.2</v>
       </c>
       <c r="R11" s="9">
-        <v>5.8819999999999997</v>
+        <v>6.06</v>
       </c>
       <c r="S11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="T11" s="2">
-        <f>ROUND(B11/K11,3)</f>
-        <v>1.151</v>
+        <f t="shared" si="0"/>
+        <v>0.63100000000000001</v>
       </c>
       <c r="U11" s="2">
-        <f>ROUND(C11/L11,3)</f>
-        <v>1.171</v>
+        <f t="shared" si="1"/>
+        <v>1.131</v>
       </c>
       <c r="V11" s="8">
-        <f>ROUND(D11/M11,3)</f>
-        <v>30.039000000000001</v>
+        <f t="shared" si="2"/>
+        <v>18.143999999999998</v>
       </c>
       <c r="W11" s="5">
-        <f>ROUND(E11/N11,3)</f>
-        <v>2.891</v>
+        <f t="shared" si="3"/>
+        <v>2.8239999999999998</v>
       </c>
       <c r="X11" s="1">
-        <f>ROUND(F11/O11,3)</f>
-        <v>34.08</v>
+        <f t="shared" si="4"/>
+        <v>30.297000000000001</v>
       </c>
       <c r="Y11" s="6">
-        <f>ROUND(G11/P11,3)</f>
-        <v>29.725000000000001</v>
+        <f t="shared" si="5"/>
+        <v>15.805999999999999</v>
       </c>
       <c r="Z11" s="6">
-        <f>ROUND(H11/Q11,3)</f>
-        <v>10.86</v>
+        <f t="shared" si="6"/>
+        <v>5.9</v>
       </c>
       <c r="AA11" s="9">
-        <f>ROUND(I11/R11,3)</f>
-        <v>27.689</v>
+        <f t="shared" si="7"/>
+        <v>14.993</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1708,96 +1730,96 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" si="2"/>
-        <v>5.2597181096766548</v>
+        <f t="shared" si="10"/>
+        <v>2.9416849816849813</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="3"/>
-        <v>1.1322515693473885</v>
+        <f t="shared" si="11"/>
+        <v>1.081978021978022</v>
       </c>
       <c r="D12" s="8">
-        <f t="shared" si="0"/>
-        <v>211.07499999999999</v>
+        <f t="shared" si="8"/>
+        <v>136.5</v>
       </c>
       <c r="E12" s="5">
-        <v>216.54</v>
+        <v>217.24</v>
       </c>
       <c r="F12" s="10">
-        <v>46.692999999999998</v>
+        <v>45.28</v>
       </c>
       <c r="G12" s="1">
-        <v>161.774</v>
+        <v>90.1</v>
       </c>
       <c r="H12" s="6">
-        <v>2.6080000000000001</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="I12" s="3">
-        <v>135.74</v>
+        <v>73.63</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="K12" s="2">
-        <f t="shared" si="4"/>
-        <v>5.1046437659033073</v>
+        <f t="shared" si="12"/>
+        <v>5.5802861685214618</v>
       </c>
       <c r="L12" s="2">
-        <f t="shared" si="5"/>
-        <v>1.2652671755725189</v>
+        <f t="shared" si="13"/>
+        <v>1.2941176470588236</v>
       </c>
       <c r="M12" s="8">
-        <f t="shared" si="1"/>
-        <v>6.2880000000000003</v>
+        <f t="shared" si="9"/>
+        <v>6.29</v>
       </c>
       <c r="N12" s="5">
-        <v>73.069999999999993</v>
+        <v>75.3</v>
       </c>
       <c r="O12" s="10">
-        <v>1.359</v>
+        <v>1.27</v>
       </c>
       <c r="P12" s="1">
-        <v>4.7460000000000004</v>
+        <v>4.82</v>
       </c>
       <c r="Q12" s="6">
-        <v>0.183</v>
+        <v>0.2</v>
       </c>
       <c r="R12" s="3">
-        <v>3.9609999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="S12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="T12" s="2">
-        <f>ROUND(B12/K12,3)</f>
-        <v>1.03</v>
+        <f t="shared" si="0"/>
+        <v>0.52700000000000002</v>
       </c>
       <c r="U12" s="2">
-        <f>ROUND(C12/L12,3)</f>
-        <v>0.89500000000000002</v>
+        <f t="shared" si="1"/>
+        <v>0.83599999999999997</v>
       </c>
       <c r="V12" s="8">
-        <f>ROUND(D12/M12,3)</f>
-        <v>33.567999999999998</v>
+        <f t="shared" si="2"/>
+        <v>21.701000000000001</v>
       </c>
       <c r="W12" s="5">
-        <f>ROUND(E12/N12,3)</f>
-        <v>2.9630000000000001</v>
+        <f t="shared" si="3"/>
+        <v>2.8849999999999998</v>
       </c>
       <c r="X12" s="10">
-        <f>ROUND(F12/O12,3)</f>
-        <v>34.357999999999997</v>
+        <f t="shared" si="4"/>
+        <v>35.654000000000003</v>
       </c>
       <c r="Y12" s="1">
-        <f>ROUND(G12/P12,3)</f>
-        <v>34.085999999999999</v>
+        <f t="shared" si="5"/>
+        <v>18.693000000000001</v>
       </c>
       <c r="Z12" s="6">
-        <f>ROUND(H12/Q12,3)</f>
-        <v>14.250999999999999</v>
+        <f t="shared" si="6"/>
+        <v>5.6</v>
       </c>
       <c r="AA12" s="3">
-        <f>ROUND(I12/R12,3)</f>
-        <v>34.268999999999998</v>
+        <f t="shared" si="7"/>
+        <v>18.18</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1805,96 +1827,96 @@
         <v>22</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" ref="B13:B14" si="6">D$2/D13</f>
-        <v>5.7513819023887356</v>
+        <f t="shared" ref="B13:B14" si="14">D$2/D13</f>
+        <v>3.4176525661758448</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" ref="C13:C14" si="7">D12/D13</f>
-        <v>1.0934772135045667</v>
+        <f t="shared" ref="C13:C14" si="15">D12/D13</f>
+        <v>1.1618010043407949</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="0"/>
-        <v>193.03099999999998</v>
+        <f t="shared" si="8"/>
+        <v>117.49</v>
       </c>
       <c r="E13" s="5">
-        <v>208.959</v>
+        <v>217.95</v>
       </c>
       <c r="F13" s="1">
-        <v>28.623999999999999</v>
+        <v>26.86</v>
       </c>
       <c r="G13" s="10">
-        <v>161.77099999999999</v>
+        <v>89.56</v>
       </c>
       <c r="H13" s="6">
-        <v>2.6360000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="I13" s="9">
-        <v>136.84</v>
+        <v>73.39</v>
       </c>
       <c r="J13" s="17" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" ref="K13:K14" si="8">M$2/M13</f>
-        <v>5.5360469127285263</v>
+        <f t="shared" ref="K13:K14" si="16">M$2/M13</f>
+        <v>5.8892617449664417</v>
       </c>
       <c r="L13" s="2">
-        <f t="shared" ref="L13:L14" si="9">M12/M13</f>
-        <v>1.0845119006553983</v>
+        <f t="shared" ref="L13:L14" si="17">M12/M13</f>
+        <v>1.0553691275167785</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="1"/>
-        <v>5.7980000000000009</v>
+        <f t="shared" si="9"/>
+        <v>5.96</v>
       </c>
       <c r="N13" s="5">
-        <v>74.635999999999996</v>
+        <v>75.64</v>
       </c>
       <c r="O13" s="1">
-        <v>0.86799999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P13" s="10">
-        <v>4.7380000000000004</v>
+        <v>4.87</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.192</v>
+        <v>0.2</v>
       </c>
       <c r="R13" s="9">
-        <v>3.9350000000000001</v>
+        <v>4.08</v>
       </c>
       <c r="S13" s="17" t="s">
         <v>22</v>
       </c>
       <c r="T13" s="2">
-        <f>ROUND(B13/K13,3)</f>
-        <v>1.0389999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.57999999999999996</v>
       </c>
       <c r="U13" s="2">
-        <f>ROUND(C13/L13,3)</f>
-        <v>1.008</v>
+        <f t="shared" si="1"/>
+        <v>1.101</v>
       </c>
       <c r="V13" s="8">
-        <f>ROUND(D13/M13,3)</f>
-        <v>33.292999999999999</v>
+        <f t="shared" si="2"/>
+        <v>19.713000000000001</v>
       </c>
       <c r="W13" s="5">
-        <f>ROUND(E13/N13,3)</f>
-        <v>2.8</v>
+        <f t="shared" si="3"/>
+        <v>2.8809999999999998</v>
       </c>
       <c r="X13" s="1">
-        <f>ROUND(F13/O13,3)</f>
-        <v>32.976999999999997</v>
+        <f t="shared" si="4"/>
+        <v>30.18</v>
       </c>
       <c r="Y13" s="10">
-        <f>ROUND(G13/P13,3)</f>
-        <v>34.143000000000001</v>
+        <f t="shared" si="5"/>
+        <v>18.39</v>
       </c>
       <c r="Z13" s="6">
-        <f>ROUND(H13/Q13,3)</f>
-        <v>13.728999999999999</v>
+        <f t="shared" si="6"/>
+        <v>5.35</v>
       </c>
       <c r="AA13" s="9">
-        <f>ROUND(I13/R13,3)</f>
-        <v>34.774999999999999</v>
+        <f t="shared" si="7"/>
+        <v>17.988</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1902,96 +1924,96 @@
         <v>23</v>
       </c>
       <c r="B14" s="5">
-        <f t="shared" si="6"/>
-        <v>5.6105591380460487</v>
+        <f t="shared" si="14"/>
+        <v>3.4684287812041115</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" si="7"/>
-        <v>0.97551496897046619</v>
+        <f t="shared" si="15"/>
+        <v>1.0148570441392415</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="0"/>
-        <v>197.876</v>
+        <f t="shared" si="8"/>
+        <v>115.77</v>
       </c>
       <c r="E14" s="5">
-        <v>208.315</v>
+        <v>217.66</v>
       </c>
       <c r="F14" s="1">
-        <v>27.504000000000001</v>
+        <v>25.05</v>
       </c>
       <c r="G14" s="10">
-        <v>168.22900000000001</v>
+        <v>89.65</v>
       </c>
       <c r="H14" s="6">
-        <v>2.1429999999999998</v>
+        <v>1.07</v>
       </c>
       <c r="I14" s="9">
-        <v>135.52000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="5">
-        <f t="shared" si="8"/>
-        <v>5.5513663092355587</v>
+        <f t="shared" si="16"/>
+        <v>5.9795570698466767</v>
       </c>
       <c r="L14" s="5">
+        <f t="shared" si="17"/>
+        <v>1.0153321976149914</v>
+      </c>
+      <c r="M14" s="4">
         <f t="shared" si="9"/>
-        <v>1.0027672085783468</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="1"/>
-        <v>5.782</v>
+        <v>5.87</v>
       </c>
       <c r="N14" s="5">
-        <v>74.734999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="O14" s="1">
-        <v>0.84899999999999998</v>
+        <v>0.85</v>
       </c>
       <c r="P14" s="10">
-        <v>4.7370000000000001</v>
+        <v>4.83</v>
       </c>
       <c r="Q14" s="6">
-        <v>0.19600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="R14" s="9">
-        <v>3.9279999999999999</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="S14" s="18" t="s">
         <v>23</v>
       </c>
       <c r="T14" s="5">
-        <f>ROUND(B14/K14,3)</f>
-        <v>1.0109999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.57999999999999996</v>
       </c>
       <c r="U14" s="5">
-        <f>ROUND(C14/L14,3)</f>
-        <v>0.97299999999999998</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="V14" s="4">
-        <f>ROUND(D14/M14,3)</f>
-        <v>34.222999999999999</v>
+        <f t="shared" si="2"/>
+        <v>19.722000000000001</v>
       </c>
       <c r="W14" s="5">
-        <f>ROUND(E14/N14,3)</f>
-        <v>2.7869999999999999</v>
+        <f t="shared" si="3"/>
+        <v>2.8340000000000001</v>
       </c>
       <c r="X14" s="1">
-        <f>ROUND(F14/O14,3)</f>
-        <v>32.396000000000001</v>
+        <f t="shared" si="4"/>
+        <v>29.471</v>
       </c>
       <c r="Y14" s="10">
-        <f>ROUND(G14/P14,3)</f>
-        <v>35.514000000000003</v>
+        <f t="shared" si="5"/>
+        <v>18.561</v>
       </c>
       <c r="Z14" s="6">
-        <f>ROUND(H14/Q14,3)</f>
-        <v>10.933999999999999</v>
+        <f t="shared" si="6"/>
+        <v>5.6319999999999997</v>
       </c>
       <c r="AA14" s="9">
-        <f>ROUND(I14/R14,3)</f>
-        <v>34.500999999999998</v>
+        <f t="shared" si="7"/>
+        <v>18.178999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1999,96 +2021,96 @@
         <v>25</v>
       </c>
       <c r="B15" s="2">
-        <f t="shared" ref="B15" si="10">D$2/D15</f>
-        <v>8.1359788941409263</v>
+        <f t="shared" ref="B15" si="18">D$2/D15</f>
+        <v>4.1558683502380456</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15" si="11">D14/D15</f>
-        <v>1.4501190868784584</v>
+        <f t="shared" ref="C15" si="19">D14/D15</f>
+        <v>1.1981991306147797</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="0"/>
-        <v>136.45499999999998</v>
+        <f t="shared" si="8"/>
+        <v>96.61999999999999</v>
       </c>
       <c r="E15" s="5">
-        <v>208.24299999999999</v>
+        <v>223.25</v>
       </c>
       <c r="F15" s="10">
-        <v>28.242000000000001</v>
+        <v>24.74</v>
       </c>
       <c r="G15" s="1">
-        <v>106.137</v>
+        <v>70.88</v>
       </c>
       <c r="H15" s="6">
-        <v>2.0760000000000001</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
-        <v>88.338999999999999</v>
+        <v>50.93</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" ref="K15" si="12">M$2/M15</f>
-        <v>6.004115226337448</v>
+        <f t="shared" ref="K15" si="20">M$2/M15</f>
+        <v>6.4640883977900545</v>
       </c>
       <c r="L15" s="2">
-        <f t="shared" ref="L15" si="13">M14/M15</f>
-        <v>1.0815563037785261</v>
+        <f t="shared" ref="L15" si="21">M14/M15</f>
+        <v>1.0810313075506446</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="1"/>
-        <v>5.3460000000000001</v>
+        <f t="shared" si="9"/>
+        <v>5.43</v>
       </c>
       <c r="N15" s="5">
-        <v>73.634</v>
+        <v>76.180000000000007</v>
       </c>
       <c r="O15" s="10">
-        <v>0.82599999999999996</v>
+        <v>0.84</v>
       </c>
       <c r="P15" s="1">
-        <v>4.3220000000000001</v>
+        <v>4.38</v>
       </c>
       <c r="Q15" s="6">
-        <v>0.19800000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="R15" s="3">
-        <v>3.7160000000000002</v>
+        <v>3.75</v>
       </c>
       <c r="S15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="T15" s="2">
-        <f>ROUND(B15/K15,3)</f>
-        <v>1.355</v>
+        <f t="shared" si="0"/>
+        <v>0.64300000000000002</v>
       </c>
       <c r="U15" s="2">
-        <f>ROUND(C15/L15,3)</f>
-        <v>1.341</v>
+        <f t="shared" si="1"/>
+        <v>1.1080000000000001</v>
       </c>
       <c r="V15" s="8">
-        <f>ROUND(D15/M15,3)</f>
-        <v>25.524999999999999</v>
+        <f t="shared" si="2"/>
+        <v>17.794</v>
       </c>
       <c r="W15" s="5">
-        <f>ROUND(E15/N15,3)</f>
-        <v>2.8279999999999998</v>
+        <f t="shared" si="3"/>
+        <v>2.931</v>
       </c>
       <c r="X15" s="10">
-        <f>ROUND(F15/O15,3)</f>
-        <v>34.191000000000003</v>
+        <f t="shared" si="4"/>
+        <v>29.452000000000002</v>
       </c>
       <c r="Y15" s="1">
-        <f>ROUND(G15/P15,3)</f>
-        <v>24.556999999999999</v>
+        <f t="shared" si="5"/>
+        <v>16.183</v>
       </c>
       <c r="Z15" s="6">
-        <f>ROUND(H15/Q15,3)</f>
-        <v>10.484999999999999</v>
+        <f t="shared" si="6"/>
+        <v>4.7619999999999996</v>
       </c>
       <c r="AA15" s="3">
-        <f>ROUND(I15/R15,3)</f>
-        <v>23.773</v>
+        <f t="shared" si="7"/>
+        <v>13.581</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2096,96 +2118,96 @@
         <v>27</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" ref="B16" si="14">D$2/D16</f>
-        <v>8.0471655032944103</v>
+        <f t="shared" ref="B16" si="22">D$2/D16</f>
+        <v>4.1264001644229786</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16" si="15">D15/D16</f>
-        <v>0.98908387152891031</v>
+        <f t="shared" ref="C16" si="23">D15/D16</f>
+        <v>0.99290925906895489</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="0"/>
-        <v>137.96099999999998</v>
+        <f t="shared" si="8"/>
+        <v>97.309999999999988</v>
       </c>
       <c r="E16" s="19">
-        <v>211.654</v>
+        <v>213.73</v>
       </c>
       <c r="F16" s="11">
-        <v>27.997</v>
+        <v>25.4</v>
       </c>
       <c r="G16" s="11">
-        <v>108.008</v>
+        <v>70.92</v>
       </c>
       <c r="H16" s="11">
-        <v>1.956</v>
+        <v>0.99</v>
       </c>
       <c r="I16" s="12">
-        <v>89.71</v>
+        <v>50.22</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16" si="16">M$2/M16</f>
-        <v>6.1302521008403348</v>
+        <f t="shared" ref="K16" si="24">M$2/M16</f>
+        <v>6.3818181818181809</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16" si="17">M15/M16</f>
-        <v>1.0210084033613445</v>
+        <f t="shared" ref="L16" si="25">M15/M16</f>
+        <v>0.98727272727272719</v>
       </c>
       <c r="M16" s="4">
-        <f t="shared" si="1"/>
-        <v>5.2360000000000007</v>
+        <f t="shared" si="9"/>
+        <v>5.5</v>
       </c>
       <c r="N16" s="1">
-        <v>10.299000000000001</v>
+        <v>11.43</v>
       </c>
       <c r="O16" s="6">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="P16" s="6">
-        <v>4.2370000000000001</v>
+        <v>4.43</v>
       </c>
       <c r="Q16" s="6">
-        <v>0.189</v>
+        <v>0.2</v>
       </c>
       <c r="R16" s="7">
-        <v>3.6360000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="S16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="T16" s="2">
-        <f>ROUND(B16/K16,3)</f>
-        <v>1.3129999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0.64700000000000002</v>
       </c>
       <c r="U16" s="2">
-        <f>ROUND(C16/L16,3)</f>
-        <v>0.96899999999999997</v>
+        <f t="shared" si="1"/>
+        <v>1.006</v>
       </c>
       <c r="V16" s="8">
-        <f>ROUND(D16/M16,3)</f>
-        <v>26.349</v>
+        <f t="shared" si="2"/>
+        <v>17.693000000000001</v>
       </c>
       <c r="W16" s="2">
-        <f>ROUND(E16/N16,3)</f>
-        <v>20.550999999999998</v>
+        <f t="shared" si="3"/>
+        <v>18.699000000000002</v>
       </c>
       <c r="X16" s="10">
-        <f>ROUND(F16/O16,3)</f>
-        <v>34.564</v>
+        <f t="shared" si="4"/>
+        <v>29.195</v>
       </c>
       <c r="Y16" s="1">
-        <f>ROUND(G16/P16,3)</f>
-        <v>25.492000000000001</v>
+        <f t="shared" si="5"/>
+        <v>16.009</v>
       </c>
       <c r="Z16" s="6">
-        <f>ROUND(H16/Q16,3)</f>
-        <v>10.349</v>
+        <f t="shared" si="6"/>
+        <v>4.95</v>
       </c>
       <c r="AA16" s="3">
-        <f>ROUND(I16/R16,3)</f>
-        <v>24.672999999999998</v>
+        <f t="shared" si="7"/>
+        <v>13.391999999999999</v>
       </c>
     </row>
     <row r="17" spans="10:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2208,9 +2230,4452 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C6226A-ABDF-4A08-82A9-477B53B06893}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>9919</v>
+      </c>
+      <c r="B2">
+        <v>219.036</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2">
+        <v>34.073</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <v>97.314999999999998</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2">
+        <v>16.395</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2">
+        <v>136.66999999999999</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>9903</v>
+      </c>
+      <c r="B3">
+        <v>217.83199999999999</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>44.164000000000001</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3">
+        <v>100.629</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>9927</v>
+      </c>
+      <c r="B4">
+        <v>220.21799999999999</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4">
+        <v>49.726999999999997</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>102.742</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <v>134.36699999999999</v>
+      </c>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>9983</v>
+      </c>
+      <c r="B5">
+        <v>1108.6300000000001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>0.109</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>59.207999999999998</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>181.86799999999999</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5">
+        <v>27.983000000000001</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5">
+        <v>702.64499999999998</v>
+      </c>
+      <c r="O5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>9935</v>
+      </c>
+      <c r="B6">
+        <v>1088.848</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>0.108</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>77.597999999999999</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>179.95400000000001</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>1.6579999999999999</v>
+      </c>
+      <c r="M6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6">
+        <v>782.60900000000004</v>
+      </c>
+      <c r="O6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>9999</v>
+      </c>
+      <c r="B7">
+        <v>1094.576</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>0.112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>79.326999999999998</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7">
+        <v>185.82</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7">
+        <v>3.137</v>
+      </c>
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>608.697</v>
+      </c>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>9915</v>
+      </c>
+      <c r="B8">
+        <v>219.679</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>80.709000000000003</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>112.83199999999999</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>9967</v>
+      </c>
+      <c r="B9">
+        <v>1119.96</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>0.126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>0.72</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>98.391999999999996</v>
+      </c>
+      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9">
+        <v>380.51799999999997</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9943</v>
+      </c>
+      <c r="B10">
+        <v>1069.046</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>0.108</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10">
+        <v>1.3640000000000001</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>99.152000000000001</v>
+      </c>
+      <c r="I10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>196.178</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9991</v>
+      </c>
+      <c r="B11">
+        <v>1069.5609999999999</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>0.109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11">
+        <v>0.751</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <v>100.3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11">
+        <v>375.56</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>9951</v>
+      </c>
+      <c r="B12">
+        <v>1095.3119999999999</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>103.086</v>
+      </c>
+      <c r="I12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12">
+        <v>186.29300000000001</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>9911</v>
+      </c>
+      <c r="B13">
+        <v>950.19500000000005</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>0.115</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13">
+        <v>1.462</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13">
+        <v>105.358</v>
+      </c>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>194.51599999999999</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13">
+        <v>0.91</v>
+      </c>
+      <c r="M13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>598.93600000000004</v>
+      </c>
+      <c r="O13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>9931</v>
+      </c>
+      <c r="B14">
+        <v>943.678</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>0.108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14">
+        <v>2.085</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14">
+        <v>124.22499999999999</v>
+      </c>
+      <c r="I14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14">
+        <v>204.14400000000001</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="M14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>9905</v>
+      </c>
+      <c r="B15">
+        <v>220.523</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>6.3E-2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15">
+        <v>0.83</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15">
+        <v>134.33699999999999</v>
+      </c>
+      <c r="I15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15">
+        <v>219.11199999999999</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15">
+        <v>6.0090000000000003</v>
+      </c>
+      <c r="M15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15">
+        <v>664.64300000000003</v>
+      </c>
+      <c r="O15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>9945</v>
+      </c>
+      <c r="B16">
+        <v>221.63200000000001</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16">
+        <v>136.03700000000001</v>
+      </c>
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16">
+        <v>136.447</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>9917</v>
+      </c>
+      <c r="B17">
+        <v>224.14599999999999</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17">
+        <v>136.428</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17">
+        <v>110.295</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17">
+        <v>1.099</v>
+      </c>
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>137.167</v>
+      </c>
+      <c r="O17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>9900</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>367.072</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18">
+        <v>1.306</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>137.22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18">
+        <v>111.29600000000001</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18">
+        <v>0.06</v>
+      </c>
+      <c r="M18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>9914</v>
+      </c>
+      <c r="B19">
+        <v>221.89500000000001</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19">
+        <v>137.41300000000001</v>
+      </c>
+      <c r="I19" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19">
+        <v>116.036</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="M19" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19">
+        <v>138.041</v>
+      </c>
+      <c r="O19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>9904</v>
+      </c>
+      <c r="B20">
+        <v>217.22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20">
+        <v>0.06</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20">
+        <v>137.60300000000001</v>
+      </c>
+      <c r="I20" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20">
+        <v>113.041</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="M20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20">
+        <v>138.215</v>
+      </c>
+      <c r="O20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>9929</v>
+      </c>
+      <c r="B21">
+        <v>221.92500000000001</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21">
+        <v>0.74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21">
+        <v>138.68199999999999</v>
+      </c>
+      <c r="I21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21">
+        <v>105.206</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="M21" t="s">
+        <v>13</v>
+      </c>
+      <c r="N21">
+        <v>133.29599999999999</v>
+      </c>
+      <c r="O21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>9901</v>
+      </c>
+      <c r="B22">
+        <v>223.875</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22">
+        <v>138.77199999999999</v>
+      </c>
+      <c r="I22" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22">
+        <v>134.18899999999999</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>9928</v>
+      </c>
+      <c r="B23">
+        <v>219.34200000000001</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23">
+        <v>139.30600000000001</v>
+      </c>
+      <c r="I23" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23">
+        <v>115.015</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="M23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>9924</v>
+      </c>
+      <c r="B24">
+        <v>220.78700000000001</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24">
+        <v>139.328</v>
+      </c>
+      <c r="I24" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24">
+        <v>114.999</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24">
+        <v>0.11</v>
+      </c>
+      <c r="M24" t="s">
+        <v>13</v>
+      </c>
+      <c r="N24">
+        <v>133.916</v>
+      </c>
+      <c r="O24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>9925</v>
+      </c>
+      <c r="B25">
+        <v>217.19200000000001</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>4.7E-2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25">
+        <v>140.202</v>
+      </c>
+      <c r="I25" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25">
+        <v>132.07599999999999</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25">
+        <v>3.9E-2</v>
+      </c>
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>9916</v>
+      </c>
+      <c r="B26">
+        <v>221.86799999999999</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26">
+        <v>142.28200000000001</v>
+      </c>
+      <c r="I26" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26">
+        <v>116.477</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>9926</v>
+      </c>
+      <c r="B27">
+        <v>219.12299999999999</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27">
+        <v>142.67099999999999</v>
+      </c>
+      <c r="I27" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27">
+        <v>115.599</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="M27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>9918</v>
+      </c>
+      <c r="B28">
+        <v>226.91399999999999</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28">
+        <v>143.91900000000001</v>
+      </c>
+      <c r="I28" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28">
+        <v>114.758</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>9902</v>
+      </c>
+      <c r="B29">
+        <v>213.19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>0.06</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29">
+        <v>0.878</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29">
+        <v>144.78</v>
+      </c>
+      <c r="I29" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29">
+        <v>113.82299999999999</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29">
+        <v>0.06</v>
+      </c>
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>9979</v>
+      </c>
+      <c r="B30">
+        <v>1142.654</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>0.108</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30">
+        <v>1.1459999999999999</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30">
+        <v>145.21700000000001</v>
+      </c>
+      <c r="I30" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30">
+        <v>211.29400000000001</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="M30" t="s">
+        <v>13</v>
+      </c>
+      <c r="N30">
+        <v>812.71500000000003</v>
+      </c>
+      <c r="O30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>9920</v>
+      </c>
+      <c r="B31">
+        <v>227.18100000000001</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31">
+        <v>5.5E-2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31">
+        <v>145.541</v>
+      </c>
+      <c r="I31" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31">
+        <v>117.809</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>9947</v>
+      </c>
+      <c r="B32">
+        <v>1076.1379999999999</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32">
+        <v>0.107</v>
+      </c>
+      <c r="E32" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32">
+        <v>1.8640000000000001</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32">
+        <v>147.94399999999999</v>
+      </c>
+      <c r="I32" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32">
+        <v>191.40600000000001</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="M32" t="s">
+        <v>13</v>
+      </c>
+      <c r="N32">
+        <v>579.46400000000006</v>
+      </c>
+      <c r="O32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>9939</v>
+      </c>
+      <c r="B33">
+        <v>1032.4929999999999</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33">
+        <v>0.108</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33">
+        <v>2.2679999999999998</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33">
+        <v>150.749</v>
+      </c>
+      <c r="I33" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33">
+        <v>204.63300000000001</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33">
+        <v>0.877</v>
+      </c>
+      <c r="M33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N33">
+        <v>604.15899999999999</v>
+      </c>
+      <c r="O33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>9995</v>
+      </c>
+      <c r="B34">
+        <v>1105.6199999999999</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <v>0.108</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34">
+        <v>1.34</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34">
+        <v>151.119</v>
+      </c>
+      <c r="I34" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34">
+        <v>313.23500000000001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34">
+        <v>18.132000000000001</v>
+      </c>
+      <c r="M34" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34">
+        <v>646.46699999999998</v>
+      </c>
+      <c r="O34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>9907</v>
+      </c>
+      <c r="B35">
+        <v>987.89400000000001</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="E35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35">
+        <v>2.7559999999999998</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35">
+        <v>151.952</v>
+      </c>
+      <c r="I35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35">
+        <v>226.35400000000001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>9971</v>
+      </c>
+      <c r="B36">
+        <v>1121.288</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36">
+        <v>0.109</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36">
+        <v>1.425</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36">
+        <v>155.75899999999999</v>
+      </c>
+      <c r="I36" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36">
+        <v>184.43899999999999</v>
+      </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="M36" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36">
+        <v>773.32600000000002</v>
+      </c>
+      <c r="O36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>9963</v>
+      </c>
+      <c r="B37">
+        <v>1097.509</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37">
+        <v>0.108</v>
+      </c>
+      <c r="E37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37">
+        <v>1.778</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37">
+        <v>157.09800000000001</v>
+      </c>
+      <c r="I37" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37">
+        <v>202.864</v>
+      </c>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>9923</v>
+      </c>
+      <c r="B38">
+        <v>924.36099999999999</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38">
+        <v>0.108</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38">
+        <v>1.599</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38">
+        <v>158.89599999999999</v>
+      </c>
+      <c r="I38" t="s">
+        <v>12</v>
+      </c>
+      <c r="J38">
+        <v>198.626</v>
+      </c>
+      <c r="K38" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>0.435</v>
+      </c>
+      <c r="M38" t="s">
+        <v>13</v>
+      </c>
+      <c r="N38">
+        <v>203.04400000000001</v>
+      </c>
+      <c r="O38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>9955</v>
+      </c>
+      <c r="B39">
+        <v>1109.586</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39">
+        <v>0.111</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39">
+        <v>1.64</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39">
+        <v>160.24299999999999</v>
+      </c>
+      <c r="I39" t="s">
+        <v>12</v>
+      </c>
+      <c r="J39">
+        <v>383.78899999999999</v>
+      </c>
+      <c r="K39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="M39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>9976</v>
+      </c>
+      <c r="B40">
+        <v>1121.624</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40">
+        <v>0.109</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40">
+        <v>5.9749999999999996</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40">
+        <v>233.55099999999999</v>
+      </c>
+      <c r="I40" t="s">
+        <v>12</v>
+      </c>
+      <c r="J40">
+        <v>207.44</v>
+      </c>
+      <c r="K40" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>9982</v>
+      </c>
+      <c r="B41">
+        <v>1027.048</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41">
+        <v>0.108</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41">
+        <v>1.1990000000000001</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41">
+        <v>237.88200000000001</v>
+      </c>
+      <c r="I41" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41">
+        <v>209.239</v>
+      </c>
+      <c r="K41" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="M41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>9981</v>
+      </c>
+      <c r="B42">
+        <v>1097.0219999999999</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42">
+        <v>0.109</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42">
+        <v>1.089</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42">
+        <v>246.32300000000001</v>
+      </c>
+      <c r="I42" t="s">
+        <v>12</v>
+      </c>
+      <c r="J42">
+        <v>430.61700000000002</v>
+      </c>
+      <c r="K42" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42">
+        <v>2.044</v>
+      </c>
+      <c r="M42" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42">
+        <v>589.43100000000004</v>
+      </c>
+      <c r="O42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>9942</v>
+      </c>
+      <c r="B43">
+        <v>1066.79</v>
+      </c>
+      <c r="C43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43">
+        <v>0.108</v>
+      </c>
+      <c r="E43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43">
+        <v>4.9340000000000002</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43">
+        <v>251.93700000000001</v>
+      </c>
+      <c r="I43" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43">
+        <v>204.84299999999999</v>
+      </c>
+      <c r="K43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M43" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>9970</v>
+      </c>
+      <c r="B44">
+        <v>1072.8440000000001</v>
+      </c>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44">
+        <v>0.111</v>
+      </c>
+      <c r="E44" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44">
+        <v>3.4129999999999998</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44">
+        <v>254.46899999999999</v>
+      </c>
+      <c r="I44" t="s">
+        <v>12</v>
+      </c>
+      <c r="J44">
+        <v>204.13</v>
+      </c>
+      <c r="K44" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="M44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>9922</v>
+      </c>
+      <c r="B45">
+        <v>941.49300000000005</v>
+      </c>
+      <c r="C45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45">
+        <v>0.107</v>
+      </c>
+      <c r="E45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45">
+        <v>3.7480000000000002</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45">
+        <v>255.35</v>
+      </c>
+      <c r="I45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45">
+        <v>217.07599999999999</v>
+      </c>
+      <c r="K45" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45">
+        <v>4.7E-2</v>
+      </c>
+      <c r="M45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>9980</v>
+      </c>
+      <c r="B46">
+        <v>1241.654</v>
+      </c>
+      <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>0.108</v>
+      </c>
+      <c r="E46" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46">
+        <v>2.1389999999999998</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46">
+        <v>255.352</v>
+      </c>
+      <c r="I46" t="s">
+        <v>12</v>
+      </c>
+      <c r="J46">
+        <v>206.90100000000001</v>
+      </c>
+      <c r="K46" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M46" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>9937</v>
+      </c>
+      <c r="B47">
+        <v>1101.893</v>
+      </c>
+      <c r="C47" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47">
+        <v>0.308</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47">
+        <v>3.1339999999999999</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47">
+        <v>255.374</v>
+      </c>
+      <c r="I47" t="s">
+        <v>12</v>
+      </c>
+      <c r="J47">
+        <v>230.48599999999999</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>9998</v>
+      </c>
+      <c r="B48">
+        <v>1112.681</v>
+      </c>
+      <c r="C48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48">
+        <v>0.109</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48">
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48">
+        <v>255.58600000000001</v>
+      </c>
+      <c r="I48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48">
+        <v>206.935</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48">
+        <v>1.157</v>
+      </c>
+      <c r="M48" t="s">
+        <v>13</v>
+      </c>
+      <c r="N48">
+        <v>837.75400000000002</v>
+      </c>
+      <c r="O48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>9985</v>
+      </c>
+      <c r="B49">
+        <v>1098.797</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49">
+        <v>0.113</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49">
+        <v>1.0620000000000001</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49">
+        <v>256.00400000000002</v>
+      </c>
+      <c r="I49" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49">
+        <v>235.6</v>
+      </c>
+      <c r="K49" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="M49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>9932</v>
+      </c>
+      <c r="B50">
+        <v>939.61400000000003</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50">
+        <v>5.3330000000000002</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50">
+        <v>257.39</v>
+      </c>
+      <c r="I50" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50">
+        <v>208.30600000000001</v>
+      </c>
+      <c r="K50" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50">
+        <v>4.1520000000000001</v>
+      </c>
+      <c r="M50" t="s">
+        <v>13</v>
+      </c>
+      <c r="N50">
+        <v>591.10599999999999</v>
+      </c>
+      <c r="O50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>9944</v>
+      </c>
+      <c r="B51">
+        <v>1085.624</v>
+      </c>
+      <c r="C51" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51">
+        <v>0.108</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51">
+        <v>4.593</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51">
+        <v>257.44</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51">
+        <v>382.339</v>
+      </c>
+      <c r="K51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L51">
+        <v>3.3940000000000001</v>
+      </c>
+      <c r="M51" t="s">
+        <v>13</v>
+      </c>
+      <c r="N51">
+        <v>140.24600000000001</v>
+      </c>
+      <c r="O51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>9984</v>
+      </c>
+      <c r="B52">
+        <v>1127.414</v>
+      </c>
+      <c r="C52" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52">
+        <v>0.109</v>
+      </c>
+      <c r="E52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52">
+        <v>1.5529999999999999</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52">
+        <v>257.93099999999998</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52">
+        <v>187.69499999999999</v>
+      </c>
+      <c r="K52" t="s">
+        <v>32</v>
+      </c>
+      <c r="L52">
+        <v>0.318</v>
+      </c>
+      <c r="M52" t="s">
+        <v>13</v>
+      </c>
+      <c r="N52">
+        <v>749.04899999999998</v>
+      </c>
+      <c r="O52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>9936</v>
+      </c>
+      <c r="B53">
+        <v>1107.5070000000001</v>
+      </c>
+      <c r="C53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53">
+        <v>0.108</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53">
+        <v>4.2629999999999999</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53">
+        <v>258.096</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53">
+        <v>202.82400000000001</v>
+      </c>
+      <c r="K53" t="s">
+        <v>32</v>
+      </c>
+      <c r="L53">
+        <v>0.04</v>
+      </c>
+      <c r="M53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>9978</v>
+      </c>
+      <c r="B54">
+        <v>1150.518</v>
+      </c>
+      <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54">
+        <v>0.108</v>
+      </c>
+      <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54">
+        <v>2.5790000000000002</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54">
+        <v>258.471</v>
+      </c>
+      <c r="I54" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54">
+        <v>210.01</v>
+      </c>
+      <c r="K54" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54">
+        <v>0.51</v>
+      </c>
+      <c r="M54" t="s">
+        <v>13</v>
+      </c>
+      <c r="N54">
+        <v>722.57100000000003</v>
+      </c>
+      <c r="O54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>9958</v>
+      </c>
+      <c r="B55">
+        <v>1128.296</v>
+      </c>
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55">
+        <v>0.154</v>
+      </c>
+      <c r="E55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55">
+        <v>3.851</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55">
+        <v>258.54399999999998</v>
+      </c>
+      <c r="I55" t="s">
+        <v>12</v>
+      </c>
+      <c r="J55">
+        <v>405.96</v>
+      </c>
+      <c r="K55" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>9930</v>
+      </c>
+      <c r="B56">
+        <v>426.214</v>
+      </c>
+      <c r="C56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>0.108</v>
+      </c>
+      <c r="E56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56">
+        <v>5.3109999999999999</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56">
+        <v>258.92399999999998</v>
+      </c>
+      <c r="I56" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56">
+        <v>207.36199999999999</v>
+      </c>
+      <c r="K56" t="s">
+        <v>32</v>
+      </c>
+      <c r="L56">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>9950</v>
+      </c>
+      <c r="B57">
+        <v>1106.2470000000001</v>
+      </c>
+      <c r="C57" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57">
+        <v>0.115</v>
+      </c>
+      <c r="E57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57">
+        <v>2.9929999999999999</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57">
+        <v>259.60399999999998</v>
+      </c>
+      <c r="I57" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57">
+        <v>210.28700000000001</v>
+      </c>
+      <c r="K57" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57">
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="M57" t="s">
+        <v>13</v>
+      </c>
+      <c r="N57">
+        <v>833.42399999999998</v>
+      </c>
+      <c r="O57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>9912</v>
+      </c>
+      <c r="B58">
+        <v>884.83399999999995</v>
+      </c>
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58">
+        <v>0.107</v>
+      </c>
+      <c r="E58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58">
+        <v>4.5</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58">
+        <v>259.70499999999998</v>
+      </c>
+      <c r="I58" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58">
+        <v>204.94300000000001</v>
+      </c>
+      <c r="K58" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="M58" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>9996</v>
+      </c>
+      <c r="B59">
+        <v>1093.646</v>
+      </c>
+      <c r="C59" t="s">
+        <v>30</v>
+      </c>
+      <c r="D59">
+        <v>0.109</v>
+      </c>
+      <c r="E59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59">
+        <v>3.2010000000000001</v>
+      </c>
+      <c r="G59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59">
+        <v>260.16500000000002</v>
+      </c>
+      <c r="I59" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59">
+        <v>205.26599999999999</v>
+      </c>
+      <c r="K59" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="M59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>9964</v>
+      </c>
+      <c r="B60">
+        <v>1081.153</v>
+      </c>
+      <c r="C60" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60">
+        <v>0.108</v>
+      </c>
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60">
+        <v>4.306</v>
+      </c>
+      <c r="G60" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60">
+        <v>260.29599999999999</v>
+      </c>
+      <c r="I60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J60">
+        <v>409.63900000000001</v>
+      </c>
+      <c r="K60" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60">
+        <v>0.316</v>
+      </c>
+      <c r="M60" t="s">
+        <v>13</v>
+      </c>
+      <c r="N60">
+        <v>646.44399999999996</v>
+      </c>
+      <c r="O60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>9974</v>
+      </c>
+      <c r="B61">
+        <v>1112.903</v>
+      </c>
+      <c r="C61" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61">
+        <v>0.127</v>
+      </c>
+      <c r="E61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61">
+        <v>5.0570000000000004</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61">
+        <v>260.38</v>
+      </c>
+      <c r="I61" t="s">
+        <v>12</v>
+      </c>
+      <c r="J61">
+        <v>208.58600000000001</v>
+      </c>
+      <c r="K61" t="s">
+        <v>32</v>
+      </c>
+      <c r="L61">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="M61" t="s">
+        <v>13</v>
+      </c>
+      <c r="N61">
+        <v>801.09900000000005</v>
+      </c>
+      <c r="O61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>9960</v>
+      </c>
+      <c r="B62">
+        <v>1100.175</v>
+      </c>
+      <c r="C62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>0.108</v>
+      </c>
+      <c r="E62" t="s">
+        <v>31</v>
+      </c>
+      <c r="F62">
+        <v>4.069</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62">
+        <v>261.33699999999999</v>
+      </c>
+      <c r="I62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J62">
+        <v>399.70699999999999</v>
+      </c>
+      <c r="K62" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62">
+        <v>3.9E-2</v>
+      </c>
+      <c r="M62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>9988</v>
+      </c>
+      <c r="B63">
+        <v>1130.019</v>
+      </c>
+      <c r="C63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63">
+        <v>0.109</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63">
+        <v>2.44</v>
+      </c>
+      <c r="G63" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63">
+        <v>261.46100000000001</v>
+      </c>
+      <c r="I63" t="s">
+        <v>12</v>
+      </c>
+      <c r="J63">
+        <v>205.65600000000001</v>
+      </c>
+      <c r="K63" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="M63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>9966</v>
+      </c>
+      <c r="B64">
+        <v>1110.1099999999999</v>
+      </c>
+      <c r="C64" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <v>0.114</v>
+      </c>
+      <c r="E64" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64">
+        <v>3.0630000000000002</v>
+      </c>
+      <c r="G64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64">
+        <v>262.78300000000002</v>
+      </c>
+      <c r="I64" t="s">
+        <v>12</v>
+      </c>
+      <c r="J64">
+        <v>204.172</v>
+      </c>
+      <c r="K64" t="s">
+        <v>32</v>
+      </c>
+      <c r="L64">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M64" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>9941</v>
+      </c>
+      <c r="B65">
+        <v>1109.0930000000001</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65">
+        <v>0.108</v>
+      </c>
+      <c r="E65" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65">
+        <v>3.661</v>
+      </c>
+      <c r="G65" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65">
+        <v>262.80599999999998</v>
+      </c>
+      <c r="I65" t="s">
+        <v>12</v>
+      </c>
+      <c r="J65">
+        <v>192.58500000000001</v>
+      </c>
+      <c r="K65" t="s">
+        <v>32</v>
+      </c>
+      <c r="L65">
+        <v>0.22</v>
+      </c>
+      <c r="M65" t="s">
+        <v>13</v>
+      </c>
+      <c r="N65">
+        <v>817.96100000000001</v>
+      </c>
+      <c r="O65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>9994</v>
+      </c>
+      <c r="B66">
+        <v>1136.242</v>
+      </c>
+      <c r="C66" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66">
+        <v>0.111</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66">
+        <v>3.5670000000000002</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66">
+        <v>262.82499999999999</v>
+      </c>
+      <c r="I66" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66">
+        <v>417.99299999999999</v>
+      </c>
+      <c r="K66" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M66" t="s">
+        <v>13</v>
+      </c>
+      <c r="N66">
+        <v>642.226</v>
+      </c>
+      <c r="O66" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>9934</v>
+      </c>
+      <c r="B67">
+        <v>1000.026</v>
+      </c>
+      <c r="C67" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67">
+        <v>0.108</v>
+      </c>
+      <c r="E67" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67">
+        <v>3.9609999999999999</v>
+      </c>
+      <c r="G67" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67">
+        <v>264.05900000000003</v>
+      </c>
+      <c r="I67" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67">
+        <v>207.10599999999999</v>
+      </c>
+      <c r="K67" t="s">
+        <v>32</v>
+      </c>
+      <c r="L67">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="M67" t="s">
+        <v>13</v>
+      </c>
+      <c r="N67">
+        <v>809.17600000000004</v>
+      </c>
+      <c r="O67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>9965</v>
+      </c>
+      <c r="B68">
+        <v>1119.519</v>
+      </c>
+      <c r="C68" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68">
+        <v>0.109</v>
+      </c>
+      <c r="E68" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68">
+        <v>2.5059999999999998</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68">
+        <v>264.30200000000002</v>
+      </c>
+      <c r="I68" t="s">
+        <v>12</v>
+      </c>
+      <c r="J68">
+        <v>384.709</v>
+      </c>
+      <c r="K68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L68">
+        <v>2.6349999999999998</v>
+      </c>
+      <c r="M68" t="s">
+        <v>13</v>
+      </c>
+      <c r="N68">
+        <v>648.34900000000005</v>
+      </c>
+      <c r="O68" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>9969</v>
+      </c>
+      <c r="B69">
+        <v>1126.1669999999999</v>
+      </c>
+      <c r="C69" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69">
+        <v>0.108</v>
+      </c>
+      <c r="E69" t="s">
+        <v>31</v>
+      </c>
+      <c r="F69">
+        <v>2.0939999999999999</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69">
+        <v>264.79700000000003</v>
+      </c>
+      <c r="I69" t="s">
+        <v>12</v>
+      </c>
+      <c r="J69">
+        <v>237.714</v>
+      </c>
+      <c r="K69" t="s">
+        <v>32</v>
+      </c>
+      <c r="L69">
+        <v>0.504</v>
+      </c>
+      <c r="M69" t="s">
+        <v>13</v>
+      </c>
+      <c r="N69">
+        <v>694.12900000000002</v>
+      </c>
+      <c r="O69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>9909</v>
+      </c>
+      <c r="B70">
+        <v>947.32600000000002</v>
+      </c>
+      <c r="C70" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70">
+        <v>0.108</v>
+      </c>
+      <c r="E70" t="s">
+        <v>31</v>
+      </c>
+      <c r="F70">
+        <v>3.8079999999999998</v>
+      </c>
+      <c r="G70" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70">
+        <v>265.07499999999999</v>
+      </c>
+      <c r="I70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70">
+        <v>226.50399999999999</v>
+      </c>
+      <c r="K70" t="s">
+        <v>32</v>
+      </c>
+      <c r="L70">
+        <v>0.504</v>
+      </c>
+      <c r="M70" t="s">
+        <v>13</v>
+      </c>
+      <c r="N70">
+        <v>644.43100000000004</v>
+      </c>
+      <c r="O70" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>9972</v>
+      </c>
+      <c r="B71">
+        <v>1128.374</v>
+      </c>
+      <c r="C71" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <v>0.109</v>
+      </c>
+      <c r="E71" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71">
+        <v>3.6349999999999998</v>
+      </c>
+      <c r="G71" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71">
+        <v>265.65300000000002</v>
+      </c>
+      <c r="I71" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71">
+        <v>205.46100000000001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="M71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>9990</v>
+      </c>
+      <c r="B72">
+        <v>1133.8800000000001</v>
+      </c>
+      <c r="C72" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72">
+        <v>0.121</v>
+      </c>
+      <c r="E72" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72">
+        <v>266.28800000000001</v>
+      </c>
+      <c r="I72" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72">
+        <v>209.82</v>
+      </c>
+      <c r="K72" t="s">
+        <v>32</v>
+      </c>
+      <c r="L72">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="M72" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>9968</v>
+      </c>
+      <c r="B73">
+        <v>1126.8779999999999</v>
+      </c>
+      <c r="C73" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="E73" t="s">
+        <v>31</v>
+      </c>
+      <c r="F73">
+        <v>3.556</v>
+      </c>
+      <c r="G73" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73">
+        <v>266.33100000000002</v>
+      </c>
+      <c r="I73" t="s">
+        <v>12</v>
+      </c>
+      <c r="J73">
+        <v>204.488</v>
+      </c>
+      <c r="K73" t="s">
+        <v>32</v>
+      </c>
+      <c r="L73">
+        <v>3.9E-2</v>
+      </c>
+      <c r="M73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>9973</v>
+      </c>
+      <c r="B74">
+        <v>1091.4770000000001</v>
+      </c>
+      <c r="C74" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74">
+        <v>0.108</v>
+      </c>
+      <c r="E74" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74">
+        <v>2.1840000000000002</v>
+      </c>
+      <c r="G74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74">
+        <v>267.03800000000001</v>
+      </c>
+      <c r="I74" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74">
+        <v>426.35300000000001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M74" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>9993</v>
+      </c>
+      <c r="B75">
+        <v>1097.1969999999999</v>
+      </c>
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75">
+        <v>0.12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75">
+        <v>2.0470000000000002</v>
+      </c>
+      <c r="G75" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75">
+        <v>267.13400000000001</v>
+      </c>
+      <c r="I75" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75">
+        <v>234.51</v>
+      </c>
+      <c r="K75" t="s">
+        <v>32</v>
+      </c>
+      <c r="L75">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>9962</v>
+      </c>
+      <c r="B76">
+        <v>1091.7629999999999</v>
+      </c>
+      <c r="C76" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>0.108</v>
+      </c>
+      <c r="E76" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76">
+        <v>4.9180000000000001</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76">
+        <v>267.14299999999997</v>
+      </c>
+      <c r="I76" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76">
+        <v>205.803</v>
+      </c>
+      <c r="K76" t="s">
+        <v>32</v>
+      </c>
+      <c r="L76">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>9961</v>
+      </c>
+      <c r="B77">
+        <v>1115.5129999999999</v>
+      </c>
+      <c r="C77" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="E77" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77">
+        <v>2.9049999999999998</v>
+      </c>
+      <c r="G77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77">
+        <v>268.00799999999998</v>
+      </c>
+      <c r="I77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77">
+        <v>226.96199999999999</v>
+      </c>
+      <c r="K77" t="s">
+        <v>32</v>
+      </c>
+      <c r="L77">
+        <v>0.878</v>
+      </c>
+      <c r="M77" t="s">
+        <v>13</v>
+      </c>
+      <c r="N77">
+        <v>843.822</v>
+      </c>
+      <c r="O77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>9933</v>
+      </c>
+      <c r="B78">
+        <v>968.28</v>
+      </c>
+      <c r="C78" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78">
+        <v>0.108</v>
+      </c>
+      <c r="E78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78">
+        <v>268.15499999999997</v>
+      </c>
+      <c r="I78" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78">
+        <v>232.71700000000001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>32</v>
+      </c>
+      <c r="L78">
+        <v>3.9E-2</v>
+      </c>
+      <c r="M78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>9952</v>
+      </c>
+      <c r="B79">
+        <v>1179.4290000000001</v>
+      </c>
+      <c r="C79" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="E79" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79">
+        <v>2.786</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79">
+        <v>270.94600000000003</v>
+      </c>
+      <c r="I79" t="s">
+        <v>12</v>
+      </c>
+      <c r="J79">
+        <v>213.566</v>
+      </c>
+      <c r="K79" t="s">
+        <v>32</v>
+      </c>
+      <c r="L79">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="M79" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>9913</v>
+      </c>
+      <c r="B80">
+        <v>929.06399999999996</v>
+      </c>
+      <c r="C80" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80">
+        <v>0.108</v>
+      </c>
+      <c r="E80" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80">
+        <v>2.9780000000000002</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80">
+        <v>272.45</v>
+      </c>
+      <c r="I80" t="s">
+        <v>12</v>
+      </c>
+      <c r="J80">
+        <v>152.852</v>
+      </c>
+      <c r="K80" t="s">
+        <v>32</v>
+      </c>
+      <c r="L80">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M80" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>9910</v>
+      </c>
+      <c r="B81">
+        <v>926.38499999999999</v>
+      </c>
+      <c r="C81" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="E81" t="s">
+        <v>31</v>
+      </c>
+      <c r="F81">
+        <v>5.3929999999999998</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81">
+        <v>273.21699999999998</v>
+      </c>
+      <c r="I81" t="s">
+        <v>12</v>
+      </c>
+      <c r="J81">
+        <v>200.75899999999999</v>
+      </c>
+      <c r="K81" t="s">
+        <v>32</v>
+      </c>
+      <c r="L81">
+        <v>0.504</v>
+      </c>
+      <c r="M81" t="s">
+        <v>13</v>
+      </c>
+      <c r="N81">
+        <v>687.06700000000001</v>
+      </c>
+      <c r="O81" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>9957</v>
+      </c>
+      <c r="B82">
+        <v>1097.7280000000001</v>
+      </c>
+      <c r="C82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82">
+        <v>0.152</v>
+      </c>
+      <c r="E82" t="s">
+        <v>31</v>
+      </c>
+      <c r="F82">
+        <v>2.8650000000000002</v>
+      </c>
+      <c r="G82" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82">
+        <v>274.61200000000002</v>
+      </c>
+      <c r="I82" t="s">
+        <v>12</v>
+      </c>
+      <c r="J82">
+        <v>227.21899999999999</v>
+      </c>
+      <c r="K82" t="s">
+        <v>32</v>
+      </c>
+      <c r="L82">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="M82" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>9986</v>
+      </c>
+      <c r="B83">
+        <v>1148.01</v>
+      </c>
+      <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="E83" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83">
+        <v>1.986</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83">
+        <v>275.483</v>
+      </c>
+      <c r="I83" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83">
+        <v>386.62900000000002</v>
+      </c>
+      <c r="K83" t="s">
+        <v>32</v>
+      </c>
+      <c r="L83">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="M83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>9921</v>
+      </c>
+      <c r="B84">
+        <v>312.214</v>
+      </c>
+      <c r="C84" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="E84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84">
+        <v>2.1240000000000001</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84">
+        <v>276.334</v>
+      </c>
+      <c r="I84" t="s">
+        <v>12</v>
+      </c>
+      <c r="J84">
+        <v>229.19</v>
+      </c>
+      <c r="K84" t="s">
+        <v>32</v>
+      </c>
+      <c r="L84">
+        <v>0.04</v>
+      </c>
+      <c r="M84" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>9908</v>
+      </c>
+      <c r="B85">
+        <v>944.95100000000002</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="E85" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85">
+        <v>6.3259999999999996</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85">
+        <v>276.81299999999999</v>
+      </c>
+      <c r="I85" t="s">
+        <v>12</v>
+      </c>
+      <c r="J85">
+        <v>207.41800000000001</v>
+      </c>
+      <c r="K85" t="s">
+        <v>32</v>
+      </c>
+      <c r="L85">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="M85" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>9989</v>
+      </c>
+      <c r="B86">
+        <v>1146.6389999999999</v>
+      </c>
+      <c r="C86" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86">
+        <v>0.108</v>
+      </c>
+      <c r="E86" t="s">
+        <v>31</v>
+      </c>
+      <c r="F86">
+        <v>1.6439999999999999</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
+      </c>
+      <c r="H86">
+        <v>281.48899999999998</v>
+      </c>
+      <c r="I86" t="s">
+        <v>12</v>
+      </c>
+      <c r="J86">
+        <v>203.68299999999999</v>
+      </c>
+      <c r="K86" t="s">
+        <v>32</v>
+      </c>
+      <c r="L86">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="M86" t="s">
+        <v>13</v>
+      </c>
+      <c r="N86">
+        <v>859.66300000000001</v>
+      </c>
+      <c r="O86" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>9959</v>
+      </c>
+      <c r="B87">
+        <v>917.04700000000003</v>
+      </c>
+      <c r="C87" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="E87" t="s">
+        <v>31</v>
+      </c>
+      <c r="F87">
+        <v>2.4620000000000002</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87">
+        <v>285.197</v>
+      </c>
+      <c r="I87" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87">
+        <v>183.297</v>
+      </c>
+      <c r="K87" t="s">
+        <v>32</v>
+      </c>
+      <c r="L87">
+        <v>2.4849999999999999</v>
+      </c>
+      <c r="M87" t="s">
+        <v>13</v>
+      </c>
+      <c r="N87">
+        <v>599.80700000000002</v>
+      </c>
+      <c r="O87" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>9949</v>
+      </c>
+      <c r="B88">
+        <v>1277.9259999999999</v>
+      </c>
+      <c r="C88" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88">
+        <v>0.108</v>
+      </c>
+      <c r="E88" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88">
+        <v>2.35</v>
+      </c>
+      <c r="G88" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88">
+        <v>286.69799999999998</v>
+      </c>
+      <c r="I88" t="s">
+        <v>12</v>
+      </c>
+      <c r="J88">
+        <v>238.12799999999999</v>
+      </c>
+      <c r="K88" t="s">
+        <v>32</v>
+      </c>
+      <c r="L88">
+        <v>0.53</v>
+      </c>
+      <c r="M88" t="s">
+        <v>13</v>
+      </c>
+      <c r="N88">
+        <v>846.41800000000001</v>
+      </c>
+      <c r="O88" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>9987</v>
+      </c>
+      <c r="B89">
+        <v>966.60500000000002</v>
+      </c>
+      <c r="C89" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89">
+        <v>0.109</v>
+      </c>
+      <c r="E89" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="G89" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89">
+        <v>315.92200000000003</v>
+      </c>
+      <c r="I89" t="s">
+        <v>12</v>
+      </c>
+      <c r="J89">
+        <v>212.74199999999999</v>
+      </c>
+      <c r="K89" t="s">
+        <v>32</v>
+      </c>
+      <c r="L89">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="M89" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>9975</v>
+      </c>
+      <c r="B90">
+        <v>900.39400000000001</v>
+      </c>
+      <c r="C90" t="s">
+        <v>30</v>
+      </c>
+      <c r="D90">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="E90" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90">
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90">
+        <v>319.39800000000002</v>
+      </c>
+      <c r="I90" t="s">
+        <v>12</v>
+      </c>
+      <c r="J90">
+        <v>168.042</v>
+      </c>
+      <c r="K90" t="s">
+        <v>32</v>
+      </c>
+      <c r="L90">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="M90" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>9977</v>
+      </c>
+      <c r="B91">
+        <v>1231.903</v>
+      </c>
+      <c r="C91" t="s">
+        <v>30</v>
+      </c>
+      <c r="D91">
+        <v>0.108</v>
+      </c>
+      <c r="E91" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91">
+        <v>1.712</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91">
+        <v>323.79700000000003</v>
+      </c>
+      <c r="I91" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91">
+        <v>223.417</v>
+      </c>
+      <c r="K91" t="s">
+        <v>32</v>
+      </c>
+      <c r="L91">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="M91" t="s">
+        <v>29</v>
+      </c>
+      <c r="N91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>9946</v>
+      </c>
+      <c r="B92">
+        <v>221.68700000000001</v>
+      </c>
+      <c r="C92" t="s">
+        <v>30</v>
+      </c>
+      <c r="D92">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="E92" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92">
+        <v>328.87200000000001</v>
+      </c>
+      <c r="I92" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92">
+        <v>221.22200000000001</v>
+      </c>
+      <c r="K92" t="s">
+        <v>32</v>
+      </c>
+      <c r="L92">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M92" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>9906</v>
+      </c>
+      <c r="B93">
+        <v>1051.3019999999999</v>
+      </c>
+      <c r="C93" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="E93" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93">
+        <v>5.5460000000000003</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H93">
+        <v>336.71899999999999</v>
+      </c>
+      <c r="I93" t="s">
+        <v>12</v>
+      </c>
+      <c r="J93">
+        <v>217.48</v>
+      </c>
+      <c r="K93" t="s">
+        <v>32</v>
+      </c>
+      <c r="L93">
+        <v>0.113</v>
+      </c>
+      <c r="M93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>9948</v>
+      </c>
+      <c r="B94">
+        <v>1080.654</v>
+      </c>
+      <c r="C94" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94">
+        <v>0.109</v>
+      </c>
+      <c r="E94" t="s">
+        <v>31</v>
+      </c>
+      <c r="F94">
+        <v>5.593</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94">
+        <v>417.21899999999999</v>
+      </c>
+      <c r="I94" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94">
+        <v>205.38300000000001</v>
+      </c>
+      <c r="K94" t="s">
+        <v>32</v>
+      </c>
+      <c r="L94">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="M94" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>9992</v>
+      </c>
+      <c r="B95">
+        <v>923.86500000000001</v>
+      </c>
+      <c r="C95" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95">
+        <v>0.108</v>
+      </c>
+      <c r="E95" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95">
+        <v>2.746</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95">
+        <v>433.78399999999999</v>
+      </c>
+      <c r="I95" t="s">
+        <v>12</v>
+      </c>
+      <c r="J95">
+        <v>206.745</v>
+      </c>
+      <c r="K95" t="s">
+        <v>32</v>
+      </c>
+      <c r="L95">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M95" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>9954</v>
+      </c>
+      <c r="B96">
+        <v>1109.7460000000001</v>
+      </c>
+      <c r="C96" t="s">
+        <v>30</v>
+      </c>
+      <c r="D96">
+        <v>0.108</v>
+      </c>
+      <c r="E96" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96">
+        <v>3.7029999999999998</v>
+      </c>
+      <c r="G96" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96">
+        <v>438.58499999999998</v>
+      </c>
+      <c r="I96" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96">
+        <v>202.57900000000001</v>
+      </c>
+      <c r="K96" t="s">
+        <v>32</v>
+      </c>
+      <c r="L96">
+        <v>0.375</v>
+      </c>
+      <c r="M96" t="s">
+        <v>13</v>
+      </c>
+      <c r="N96">
+        <v>634.947</v>
+      </c>
+      <c r="O96" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>9956</v>
+      </c>
+      <c r="B97">
+        <v>928.51499999999999</v>
+      </c>
+      <c r="C97" t="s">
+        <v>30</v>
+      </c>
+      <c r="D97">
+        <v>0.108</v>
+      </c>
+      <c r="E97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97">
+        <v>5.1130000000000004</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97">
+        <v>445.66</v>
+      </c>
+      <c r="I97" t="s">
+        <v>12</v>
+      </c>
+      <c r="J97">
+        <v>210.47</v>
+      </c>
+      <c r="K97" t="s">
+        <v>32</v>
+      </c>
+      <c r="L97">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M97" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>10000</v>
+      </c>
+      <c r="B98">
+        <v>1120.711</v>
+      </c>
+      <c r="C98" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98">
+        <v>0.115</v>
+      </c>
+      <c r="E98" t="s">
+        <v>31</v>
+      </c>
+      <c r="F98">
+        <v>2.952</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98">
+        <v>457.27</v>
+      </c>
+      <c r="I98" t="s">
+        <v>12</v>
+      </c>
+      <c r="J98">
+        <v>207.596</v>
+      </c>
+      <c r="K98" t="s">
+        <v>32</v>
+      </c>
+      <c r="L98">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="M98" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>9938</v>
+      </c>
+      <c r="B99">
+        <v>1091.771</v>
+      </c>
+      <c r="C99" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="E99" t="s">
+        <v>31</v>
+      </c>
+      <c r="F99">
+        <v>5.4939999999999998</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+      <c r="H99">
+        <v>458.95499999999998</v>
+      </c>
+      <c r="I99" t="s">
+        <v>12</v>
+      </c>
+      <c r="J99">
+        <v>208.19499999999999</v>
+      </c>
+      <c r="K99" t="s">
+        <v>32</v>
+      </c>
+      <c r="L99">
+        <v>3.9E-2</v>
+      </c>
+      <c r="M99" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>9997</v>
+      </c>
+      <c r="B100">
+        <v>1122.463</v>
+      </c>
+      <c r="C100" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100">
+        <v>0.108</v>
+      </c>
+      <c r="E100" t="s">
+        <v>31</v>
+      </c>
+      <c r="F100">
+        <v>1.911</v>
+      </c>
+      <c r="G100" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100">
+        <v>462.26400000000001</v>
+      </c>
+      <c r="I100" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100">
+        <v>230.17</v>
+      </c>
+      <c r="K100" t="s">
+        <v>32</v>
+      </c>
+      <c r="L100">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="M100" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>9940</v>
+      </c>
+      <c r="B101">
+        <v>1093.037</v>
+      </c>
+      <c r="C101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101">
+        <v>0.108</v>
+      </c>
+      <c r="E101" t="s">
+        <v>31</v>
+      </c>
+      <c r="F101">
+        <v>5.8140000000000001</v>
+      </c>
+      <c r="G101" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101">
+        <v>468.596</v>
+      </c>
+      <c r="I101" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101">
+        <v>205.797</v>
+      </c>
+      <c r="K101" t="s">
+        <v>32</v>
+      </c>
+      <c r="L101">
+        <v>3.9E-2</v>
+      </c>
+      <c r="M101" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>9953</v>
+      </c>
+      <c r="B102">
+        <v>1126.492</v>
+      </c>
+      <c r="C102" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102">
+        <v>0.111</v>
+      </c>
+      <c r="E102" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102">
+        <v>2.17</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102">
+        <v>497.27699999999999</v>
+      </c>
+      <c r="I102" t="s">
+        <v>12</v>
+      </c>
+      <c r="J102">
+        <v>197.345</v>
+      </c>
+      <c r="K102" t="s">
+        <v>32</v>
+      </c>
+      <c r="L102">
+        <v>2.7410000000000001</v>
+      </c>
+      <c r="M102" t="s">
+        <v>13</v>
+      </c>
+      <c r="N102">
+        <v>656.14</v>
+      </c>
+      <c r="O102" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q102" xr:uid="{67C6226A-ABDF-4A08-82A9-477B53B06893}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q102">
+      <sortCondition ref="H1:H102"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3036D-F31B-43BB-BAE9-84B291BC8477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B8CC5D-5606-4541-817B-E445B6373675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="31">
   <si>
     <t>H22</t>
   </si>
@@ -120,6 +120,13 @@
   </si>
   <si>
     <t>H37</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H38</t>
+  </si>
+  <si>
+    <t>H38</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -283,12 +290,6 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -313,16 +314,22 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -639,26 +646,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.625" style="15"/>
-    <col min="2" max="3" width="7.625" style="11"/>
-    <col min="4" max="4" width="7.625" style="11" customWidth="1"/>
-    <col min="5" max="8" width="7.625" style="11"/>
-    <col min="9" max="9" width="7.625" style="12"/>
-    <col min="10" max="10" width="7.625" style="15"/>
-    <col min="11" max="17" width="7.625" style="11"/>
-    <col min="18" max="18" width="7.625" style="12"/>
-    <col min="19" max="19" width="7.625" style="15"/>
-    <col min="20" max="26" width="7.625" style="11"/>
-    <col min="27" max="27" width="7.625" style="12"/>
-    <col min="28" max="28" width="7.625" style="15"/>
-    <col min="29" max="16384" width="7.625" style="11"/>
+    <col min="1" max="1" width="7.625" style="13"/>
+    <col min="2" max="3" width="7.625" style="9"/>
+    <col min="4" max="4" width="7.625" style="9" customWidth="1"/>
+    <col min="5" max="8" width="7.625" style="9"/>
+    <col min="9" max="9" width="7.625" style="10"/>
+    <col min="10" max="10" width="7.625" style="13"/>
+    <col min="11" max="17" width="7.625" style="9"/>
+    <col min="18" max="18" width="7.625" style="10"/>
+    <col min="19" max="19" width="7.625" style="13"/>
+    <col min="20" max="26" width="7.625" style="9"/>
+    <col min="27" max="27" width="7.625" style="10"/>
+    <col min="28" max="28" width="7.625" style="13"/>
+    <col min="29" max="16384" width="7.625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -685,7 +692,7 @@
       <c r="I1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -712,7 +719,7 @@
       <c r="R1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="12" t="s">
         <v>26</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -757,13 +764,13 @@
       <c r="E2" s="5">
         <v>379.02</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="8">
         <v>142.38</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="8">
         <v>120.7</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="8">
         <v>138.46</v>
       </c>
       <c r="I2" s="7">
@@ -785,13 +792,13 @@
       <c r="N2" s="5">
         <v>67.77</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="8">
         <v>5.3</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="8">
         <v>12.99</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="8">
         <v>16.809999999999999</v>
       </c>
       <c r="R2" s="7">
@@ -816,15 +823,15 @@
         <f t="shared" ref="W2:W14" si="3">ROUND(E2/N2,3)</f>
         <v>5.593</v>
       </c>
-      <c r="X2" s="6">
+      <c r="X2" s="8">
         <f t="shared" ref="X2:X14" si="4">ROUND(F2/O2,3)</f>
         <v>26.864000000000001</v>
       </c>
-      <c r="Y2" s="6">
+      <c r="Y2" s="8">
         <f t="shared" ref="Y2:Y14" si="5">ROUND(G2/P2,3)</f>
         <v>9.2919999999999998</v>
       </c>
-      <c r="Z2" s="6">
+      <c r="Z2" s="8">
         <f t="shared" ref="Z2:Z14" si="6">ROUND(H2/Q2,3)</f>
         <v>8.2370000000000001</v>
       </c>
@@ -845,23 +852,23 @@
         <f>D2/D3</f>
         <v>1.5459900666076312</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <f t="shared" ref="D3:D14" si="8">SUM(F3:H3)</f>
         <v>259.72999999999996</v>
       </c>
       <c r="E3" s="5">
         <v>379.46</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="8">
         <v>139.13</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="8">
         <v>118.16</v>
       </c>
       <c r="H3" s="1">
         <v>2.44</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="7">
         <v>227.29</v>
       </c>
       <c r="J3" s="16" t="s">
@@ -875,23 +882,23 @@
         <f>M2/M3</f>
         <v>1.9306930693069304</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="6">
         <f t="shared" ref="M3:M16" si="9">SUM(O3:Q3)</f>
         <v>18.18</v>
       </c>
       <c r="N3" s="5">
         <v>68.98</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="8">
         <v>5.09</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="8">
         <v>12.62</v>
       </c>
       <c r="Q3" s="1">
         <v>0.47</v>
       </c>
-      <c r="R3" s="9">
+      <c r="R3" s="7">
         <v>27.38</v>
       </c>
       <c r="S3" s="16" t="s">
@@ -905,7 +912,7 @@
         <f t="shared" si="1"/>
         <v>0.80100000000000005</v>
       </c>
-      <c r="V3" s="8">
+      <c r="V3" s="6">
         <f t="shared" si="2"/>
         <v>14.287000000000001</v>
       </c>
@@ -913,11 +920,11 @@
         <f t="shared" si="3"/>
         <v>5.5010000000000003</v>
       </c>
-      <c r="X3" s="6">
+      <c r="X3" s="8">
         <f t="shared" si="4"/>
         <v>27.334</v>
       </c>
-      <c r="Y3" s="6">
+      <c r="Y3" s="8">
         <f t="shared" si="5"/>
         <v>9.3629999999999995</v>
       </c>
@@ -925,7 +932,7 @@
         <f t="shared" si="6"/>
         <v>5.1909999999999998</v>
       </c>
-      <c r="AA3" s="9">
+      <c r="AA3" s="7">
         <f t="shared" si="7"/>
         <v>8.3010000000000002</v>
       </c>
@@ -942,7 +949,7 @@
         <f t="shared" ref="C4:C12" si="11">D3/D4</f>
         <v>1.2821740632867649</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <f t="shared" si="8"/>
         <v>202.57</v>
       </c>
@@ -952,10 +959,10 @@
       <c r="F4" s="1">
         <v>74.77</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>125.29</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="8">
         <v>2.5099999999999998</v>
       </c>
       <c r="I4" s="7">
@@ -972,7 +979,7 @@
         <f t="shared" ref="L4:L12" si="13">M3/M4</f>
         <v>1.0706713780918728</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="6">
         <f t="shared" si="9"/>
         <v>16.98</v>
       </c>
@@ -982,10 +989,10 @@
       <c r="O4" s="1">
         <v>3.8</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="8">
         <v>12.7</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="8">
         <v>0.48</v>
       </c>
       <c r="R4" s="7">
@@ -1002,7 +1009,7 @@
         <f t="shared" si="1"/>
         <v>1.198</v>
       </c>
-      <c r="V4" s="8">
+      <c r="V4" s="6">
         <f t="shared" si="2"/>
         <v>11.93</v>
       </c>
@@ -1014,11 +1021,11 @@
         <f t="shared" si="4"/>
         <v>19.675999999999998</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="8">
         <f t="shared" si="5"/>
         <v>9.8650000000000002</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="Z4" s="8">
         <f t="shared" si="6"/>
         <v>5.2290000000000001</v>
       </c>
@@ -1039,20 +1046,20 @@
         <f t="shared" si="11"/>
         <v>1.1412394366197183</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <f t="shared" si="8"/>
         <v>177.5</v>
       </c>
       <c r="E5" s="5">
         <v>379.87</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8">
         <v>75.06</v>
       </c>
       <c r="G5" s="1">
         <v>100.06</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="8">
         <v>2.38</v>
       </c>
       <c r="I5" s="7">
@@ -1069,20 +1076,20 @@
         <f t="shared" si="13"/>
         <v>1.8258064516129031</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="6">
         <f t="shared" si="9"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="N5" s="5">
         <v>67.48</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="8">
         <v>3.79</v>
       </c>
       <c r="P5" s="1">
         <v>5.03</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="8">
         <v>0.48</v>
       </c>
       <c r="R5" s="7">
@@ -1099,7 +1106,7 @@
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
-      <c r="V5" s="8">
+      <c r="V5" s="6">
         <f t="shared" si="2"/>
         <v>19.085999999999999</v>
       </c>
@@ -1107,7 +1114,7 @@
         <f t="shared" si="3"/>
         <v>5.6289999999999996</v>
       </c>
-      <c r="X5" s="6">
+      <c r="X5" s="8">
         <f t="shared" si="4"/>
         <v>19.805</v>
       </c>
@@ -1115,7 +1122,7 @@
         <f t="shared" si="5"/>
         <v>19.893000000000001</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="Z5" s="8">
         <f t="shared" si="6"/>
         <v>4.9580000000000002</v>
       </c>
@@ -1143,13 +1150,13 @@
       <c r="E6" s="5">
         <v>361.21</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <v>73.44</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="8">
         <v>96.29</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>2.27</v>
       </c>
       <c r="I6" s="3">
@@ -1173,13 +1180,13 @@
       <c r="N6" s="5">
         <v>67.34</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="8">
         <v>3.79</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="8">
         <v>5</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="8">
         <v>0.48</v>
       </c>
       <c r="R6" s="3">
@@ -1204,15 +1211,15 @@
         <f t="shared" si="3"/>
         <v>5.3639999999999999</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="8">
         <f t="shared" si="4"/>
         <v>19.376999999999999</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="8">
         <f t="shared" si="5"/>
         <v>19.257999999999999</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="Z6" s="8">
         <f t="shared" si="6"/>
         <v>4.7290000000000001</v>
       </c>
@@ -1240,10 +1247,10 @@
       <c r="E7" s="5">
         <v>377.51</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="8">
         <v>82.34</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="8">
         <v>101.48</v>
       </c>
       <c r="H7" s="1">
@@ -1270,10 +1277,10 @@
       <c r="N7" s="5">
         <v>77.61</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="8">
         <v>3.68</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="8">
         <v>5.0999999999999996</v>
       </c>
       <c r="Q7" s="1">
@@ -1301,11 +1308,11 @@
         <f t="shared" si="3"/>
         <v>4.8639999999999999</v>
       </c>
-      <c r="X7" s="6">
+      <c r="X7" s="8">
         <f t="shared" si="4"/>
         <v>22.375</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="Y7" s="8">
         <f t="shared" si="5"/>
         <v>19.898</v>
       </c>
@@ -1337,13 +1344,13 @@
       <c r="E8" s="5">
         <v>492.18</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8">
         <v>82.65</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="8">
         <v>101.41</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="8">
         <v>1.05</v>
       </c>
       <c r="I8" s="7">
@@ -1367,13 +1374,13 @@
       <c r="N8" s="5">
         <v>96.53</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="8">
         <v>3.62</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="8">
         <v>5</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="Q8" s="8">
         <v>0.2</v>
       </c>
       <c r="R8" s="7">
@@ -1398,15 +1405,15 @@
         <f t="shared" si="3"/>
         <v>5.0990000000000002</v>
       </c>
-      <c r="X8" s="6">
+      <c r="X8" s="8">
         <f t="shared" si="4"/>
         <v>22.831</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="Y8" s="8">
         <f t="shared" si="5"/>
         <v>20.282</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="Z8" s="8">
         <f t="shared" si="6"/>
         <v>5.25</v>
       </c>
@@ -1434,13 +1441,13 @@
       <c r="E9" s="5">
         <v>489.21</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="8">
         <v>81.44</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="8">
         <v>99.21</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="8">
         <v>1.07</v>
       </c>
       <c r="I9" s="7">
@@ -1464,13 +1471,13 @@
       <c r="N9" s="5">
         <v>91.73</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="8">
         <v>3.57</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="8">
         <v>4.92</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="8">
         <v>0.2</v>
       </c>
       <c r="R9" s="7">
@@ -1495,15 +1502,15 @@
         <f t="shared" si="3"/>
         <v>5.3330000000000002</v>
       </c>
-      <c r="X9" s="6">
+      <c r="X9" s="8">
         <f t="shared" si="4"/>
         <v>22.812000000000001</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="Y9" s="8">
         <f t="shared" si="5"/>
         <v>20.164999999999999</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="Z9" s="8">
         <f t="shared" si="6"/>
         <v>5.35</v>
       </c>
@@ -1531,13 +1538,13 @@
       <c r="E10" s="2">
         <v>249.29</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="8">
         <v>81.16</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="8">
         <v>99</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>1.22</v>
       </c>
       <c r="I10" s="7">
@@ -1561,13 +1568,13 @@
       <c r="N10" s="2">
         <v>76.53</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="8">
         <v>3.62</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="8">
         <v>5.0199999999999996</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="8">
         <v>0.2</v>
       </c>
       <c r="R10" s="7">
@@ -1592,15 +1599,15 @@
         <f t="shared" si="3"/>
         <v>3.2570000000000001</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X10" s="8">
         <f t="shared" si="4"/>
         <v>22.42</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Y10" s="8">
         <f t="shared" si="5"/>
         <v>19.721</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="Z10" s="8">
         <f t="shared" si="6"/>
         <v>6.1</v>
       </c>
@@ -1621,7 +1628,7 @@
         <f t="shared" si="11"/>
         <v>1.2281129392646759</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <f t="shared" si="8"/>
         <v>147.69</v>
       </c>
@@ -1631,13 +1638,13 @@
       <c r="F11" s="1">
         <v>43.93</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="8">
         <v>102.58</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="8">
         <v>1.18</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="7">
         <v>90.86</v>
       </c>
       <c r="J11" s="16" t="s">
@@ -1651,7 +1658,7 @@
         <f t="shared" si="13"/>
         <v>1.085995085995086</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="6">
         <f t="shared" si="9"/>
         <v>8.14</v>
       </c>
@@ -1661,13 +1668,13 @@
       <c r="O11" s="1">
         <v>1.45</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="8">
         <v>6.49</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="Q11" s="8">
         <v>0.2</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="7">
         <v>6.06</v>
       </c>
       <c r="S11" s="16" t="s">
@@ -1681,7 +1688,7 @@
         <f t="shared" si="1"/>
         <v>1.131</v>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="6">
         <f t="shared" si="2"/>
         <v>18.143999999999998</v>
       </c>
@@ -1693,15 +1700,15 @@
         <f t="shared" si="4"/>
         <v>30.297000000000001</v>
       </c>
-      <c r="Y11" s="6">
+      <c r="Y11" s="8">
         <f t="shared" si="5"/>
         <v>15.805999999999999</v>
       </c>
-      <c r="Z11" s="6">
+      <c r="Z11" s="8">
         <f t="shared" si="6"/>
         <v>5.9</v>
       </c>
-      <c r="AA11" s="9">
+      <c r="AA11" s="7">
         <f t="shared" si="7"/>
         <v>14.993</v>
       </c>
@@ -1718,20 +1725,20 @@
         <f t="shared" si="11"/>
         <v>1.081978021978022</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <f t="shared" si="8"/>
         <v>136.5</v>
       </c>
       <c r="E12" s="5">
         <v>217.24</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="8">
         <v>45.28</v>
       </c>
       <c r="G12" s="1">
         <v>90.1</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="8">
         <v>1.1200000000000001</v>
       </c>
       <c r="I12" s="3">
@@ -1748,20 +1755,20 @@
         <f t="shared" si="13"/>
         <v>1.2941176470588236</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="6">
         <f t="shared" si="9"/>
         <v>6.29</v>
       </c>
       <c r="N12" s="5">
         <v>75.3</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="8">
         <v>1.27</v>
       </c>
       <c r="P12" s="1">
         <v>4.82</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="8">
         <v>0.2</v>
       </c>
       <c r="R12" s="3">
@@ -1778,7 +1785,7 @@
         <f t="shared" si="1"/>
         <v>0.83599999999999997</v>
       </c>
-      <c r="V12" s="8">
+      <c r="V12" s="6">
         <f t="shared" si="2"/>
         <v>21.701000000000001</v>
       </c>
@@ -1786,7 +1793,7 @@
         <f t="shared" si="3"/>
         <v>2.8849999999999998</v>
       </c>
-      <c r="X12" s="10">
+      <c r="X12" s="8">
         <f t="shared" si="4"/>
         <v>35.654000000000003</v>
       </c>
@@ -1794,7 +1801,7 @@
         <f t="shared" si="5"/>
         <v>18.693000000000001</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="Z12" s="8">
         <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
@@ -1815,7 +1822,7 @@
         <f t="shared" ref="C13:C14" si="15">D12/D13</f>
         <v>1.1618010043407949</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <f t="shared" si="8"/>
         <v>117.49</v>
       </c>
@@ -1825,13 +1832,13 @@
       <c r="F13" s="1">
         <v>26.86</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>89.56</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="8">
         <v>1.07</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="7">
         <v>73.39</v>
       </c>
       <c r="J13" s="17" t="s">
@@ -1845,7 +1852,7 @@
         <f t="shared" ref="L13:L14" si="17">M12/M13</f>
         <v>1.0553691275167785</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="6">
         <f t="shared" si="9"/>
         <v>5.96</v>
       </c>
@@ -1855,13 +1862,13 @@
       <c r="O13" s="1">
         <v>0.89</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="8">
         <v>4.87</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="8">
         <v>0.2</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="7">
         <v>4.08</v>
       </c>
       <c r="S13" s="17" t="s">
@@ -1875,7 +1882,7 @@
         <f t="shared" si="1"/>
         <v>1.101</v>
       </c>
-      <c r="V13" s="8">
+      <c r="V13" s="6">
         <f t="shared" si="2"/>
         <v>19.713000000000001</v>
       </c>
@@ -1887,15 +1894,15 @@
         <f t="shared" si="4"/>
         <v>30.18</v>
       </c>
-      <c r="Y13" s="10">
+      <c r="Y13" s="8">
         <f t="shared" si="5"/>
         <v>18.39</v>
       </c>
-      <c r="Z13" s="6">
+      <c r="Z13" s="8">
         <f t="shared" si="6"/>
         <v>5.35</v>
       </c>
-      <c r="AA13" s="9">
+      <c r="AA13" s="7">
         <f t="shared" si="7"/>
         <v>17.988</v>
       </c>
@@ -1922,13 +1929,13 @@
       <c r="F14" s="1">
         <v>25.05</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="8">
         <v>89.65</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="8">
         <v>1.07</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <v>73.08</v>
       </c>
       <c r="J14" s="18" t="s">
@@ -1952,13 +1959,13 @@
       <c r="O14" s="1">
         <v>0.85</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="8">
         <v>4.83</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="Q14" s="8">
         <v>0.19</v>
       </c>
-      <c r="R14" s="9">
+      <c r="R14" s="7">
         <v>4.0199999999999996</v>
       </c>
       <c r="S14" s="18" t="s">
@@ -1984,15 +1991,15 @@
         <f t="shared" si="4"/>
         <v>29.471</v>
       </c>
-      <c r="Y14" s="10">
+      <c r="Y14" s="8">
         <f t="shared" si="5"/>
         <v>18.561</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="Z14" s="8">
         <f t="shared" si="6"/>
         <v>5.6319999999999997</v>
       </c>
-      <c r="AA14" s="9">
+      <c r="AA14" s="7">
         <f t="shared" si="7"/>
         <v>18.178999999999998</v>
       </c>
@@ -2003,95 +2010,95 @@
       </c>
       <c r="B15" s="2">
         <f t="shared" ref="B15" si="18">D$2/D15</f>
-        <v>4.1558683502380456</v>
+        <v>4.0584192439862532</v>
       </c>
       <c r="C15" s="2">
         <f t="shared" ref="C15" si="19">D14/D15</f>
-        <v>1.1981991306147797</v>
-      </c>
-      <c r="D15" s="8">
+        <v>1.170103092783505</v>
+      </c>
+      <c r="D15" s="6">
         <f>SUM(F15:H15)</f>
-        <v>96.61999999999999</v>
+        <v>98.940000000000012</v>
       </c>
       <c r="E15" s="5">
-        <v>223.26</v>
-      </c>
-      <c r="F15" s="10">
-        <v>24.74</v>
+        <v>213.68</v>
+      </c>
+      <c r="F15" s="8">
+        <v>26.71</v>
       </c>
       <c r="G15" s="1">
-        <v>70.88</v>
-      </c>
-      <c r="H15" s="6">
-        <v>1</v>
+        <v>71.22</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1.01</v>
       </c>
       <c r="I15" s="3">
-        <v>50.94</v>
+        <v>51.44</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15" si="20">M$2/M15</f>
-        <v>6.4640883977900545</v>
+        <v>6.5241635687732336</v>
       </c>
       <c r="L15" s="2">
         <f t="shared" ref="L15" si="21">M14/M15</f>
-        <v>1.0810313075506446</v>
-      </c>
-      <c r="M15" s="8">
+        <v>1.0910780669144982</v>
+      </c>
+      <c r="M15" s="6">
         <f t="shared" si="9"/>
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="N15" s="5">
-        <v>76.180000000000007</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0.84</v>
+        <v>75.06</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.88</v>
       </c>
       <c r="P15" s="1">
-        <v>4.38</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0.21</v>
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0.19</v>
       </c>
       <c r="R15" s="3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="S15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="0"/>
-        <v>0.64300000000000002</v>
+        <v>0.622</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="1"/>
-        <v>1.1080000000000001</v>
-      </c>
-      <c r="V15" s="8">
+        <v>1.0720000000000001</v>
+      </c>
+      <c r="V15" s="6">
         <f t="shared" si="2"/>
-        <v>17.794</v>
+        <v>18.39</v>
       </c>
       <c r="W15" s="5">
-        <f>ROUND(E15/N15,3)</f>
-        <v>2.931</v>
-      </c>
-      <c r="X15" s="10">
-        <f>ROUND(F15/O15,3)</f>
-        <v>29.452000000000002</v>
+        <f t="shared" ref="W15:AA17" si="22">ROUND(E15/N15,3)</f>
+        <v>2.847</v>
+      </c>
+      <c r="X15" s="8">
+        <f t="shared" si="22"/>
+        <v>30.352</v>
       </c>
       <c r="Y15" s="1">
-        <f>ROUND(G15/P15,3)</f>
-        <v>16.183</v>
-      </c>
-      <c r="Z15" s="6">
-        <f>ROUND(H15/Q15,3)</f>
-        <v>4.7619999999999996</v>
+        <f t="shared" si="22"/>
+        <v>16.524000000000001</v>
+      </c>
+      <c r="Z15" s="8">
+        <f t="shared" si="22"/>
+        <v>5.3159999999999998</v>
       </c>
       <c r="AA15" s="3">
-        <f>ROUND(I15/R15,3)</f>
-        <v>13.584</v>
+        <f t="shared" si="22"/>
+        <v>13.903</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2099,96 +2106,96 @@
         <v>27</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" ref="B16" si="22">D$2/D16</f>
-        <v>3.9693554764729138</v>
+        <f t="shared" ref="B16" si="23">D$2/D16</f>
+        <v>4.0029907287409028</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16" si="23">D15/D16</f>
-        <v>0.95512060102807428</v>
+        <f t="shared" ref="C16" si="24">D15/D16</f>
+        <v>0.98634233874987554</v>
       </c>
       <c r="D16" s="4">
         <f>SUM(F16:H16)</f>
-        <v>101.16</v>
-      </c>
-      <c r="E16" s="19">
-        <v>223.91</v>
-      </c>
-      <c r="F16" s="11">
-        <v>26.58</v>
-      </c>
-      <c r="G16" s="11">
-        <v>73.55</v>
-      </c>
-      <c r="H16" s="11">
-        <v>1.03</v>
-      </c>
-      <c r="I16" s="12">
-        <v>52.04</v>
+        <v>100.31</v>
+      </c>
+      <c r="E16" s="1">
+        <v>209.82</v>
+      </c>
+      <c r="F16" s="8">
+        <v>26.99</v>
+      </c>
+      <c r="G16" s="8">
+        <v>72.2</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I16" s="7">
+        <v>51.91</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16" si="24">M$2/M16</f>
-        <v>6.4403669724770634</v>
+        <f t="shared" ref="K16" si="25">M$2/M16</f>
+        <v>6.5</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16" si="25">M15/M16</f>
-        <v>0.99633027522935769</v>
+        <f t="shared" ref="L16" si="26">M15/M16</f>
+        <v>0.99629629629629635</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="9"/>
-        <v>5.45</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="N16" s="1">
-        <v>14.05</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="P16" s="6">
-        <v>4.38</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0.21</v>
+        <v>10.38</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="P16" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0.2</v>
       </c>
       <c r="R16" s="7">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="S16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T16" s="5">
         <f t="shared" si="0"/>
         <v>0.61599999999999999</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="5">
         <f t="shared" si="1"/>
-        <v>0.95899999999999996</v>
-      </c>
-      <c r="V16" s="8">
+        <v>0.99</v>
+      </c>
+      <c r="V16" s="4">
         <f t="shared" si="2"/>
-        <v>18.561</v>
-      </c>
-      <c r="W16" s="2">
-        <f>ROUND(E16/N16,3)</f>
-        <v>15.936999999999999</v>
-      </c>
-      <c r="X16" s="10">
-        <f>ROUND(F16/O16,3)</f>
-        <v>30.907</v>
-      </c>
-      <c r="Y16" s="1">
-        <f>ROUND(G16/P16,3)</f>
-        <v>16.792000000000002</v>
-      </c>
-      <c r="Z16" s="6">
-        <f>ROUND(H16/Q16,3)</f>
-        <v>4.9050000000000002</v>
-      </c>
-      <c r="AA16" s="3">
-        <f>ROUND(I16/R16,3)</f>
-        <v>13.877000000000001</v>
+        <v>18.576000000000001</v>
+      </c>
+      <c r="W16" s="1">
+        <f t="shared" si="22"/>
+        <v>20.213999999999999</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" si="22"/>
+        <v>31.753</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" si="22"/>
+        <v>16.597999999999999</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" si="22"/>
+        <v>5.6</v>
+      </c>
+      <c r="AA16" s="7">
+        <f t="shared" si="22"/>
+        <v>13.917</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2196,96 +2203,193 @@
         <v>28</v>
       </c>
       <c r="B17" s="5">
-        <f t="shared" ref="B17" si="26">D$2/D17</f>
-        <v>3.9811620067420184</v>
+        <f t="shared" ref="B17" si="27">D$2/D17</f>
+        <v>4.1036280020439451</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17" si="27">D16/D17</f>
-        <v>1.0029744199881023</v>
+        <f t="shared" ref="C17" si="28">D16/D17</f>
+        <v>1.0251405212059275</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(F17:H17)</f>
-        <v>100.86</v>
+        <v>97.85</v>
       </c>
       <c r="E17" s="19">
-        <v>224.63</v>
-      </c>
-      <c r="F17" s="11">
-        <v>26.34</v>
-      </c>
-      <c r="G17" s="19">
-        <v>73.489999999999995</v>
-      </c>
-      <c r="H17" s="11">
-        <v>1.03</v>
-      </c>
-      <c r="I17" s="11">
-        <v>52.58</v>
+        <v>210.28</v>
+      </c>
+      <c r="F17" s="19">
+        <v>26.49</v>
+      </c>
+      <c r="G17" s="14">
+        <v>70.31</v>
+      </c>
+      <c r="H17" s="19">
+        <v>1.05</v>
+      </c>
+      <c r="I17" s="19">
+        <v>51.16</v>
       </c>
       <c r="J17" s="18" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" ref="K17" si="28">M$2/M17</f>
-        <v>7.4999999999999991</v>
+        <f t="shared" ref="K17" si="29">M$2/M17</f>
+        <v>7.7483443708609254</v>
       </c>
       <c r="L17" s="5">
-        <f t="shared" ref="L17" si="29">M16/M17</f>
-        <v>1.1645299145299146</v>
+        <f t="shared" ref="L17" si="30">M16/M17</f>
+        <v>1.1920529801324502</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" ref="M17" si="30">SUM(O17:Q17)</f>
-        <v>4.68</v>
+        <f t="shared" ref="M17" si="31">SUM(O17:Q17)</f>
+        <v>4.53</v>
       </c>
       <c r="N17" s="19">
-        <v>11.02</v>
-      </c>
-      <c r="O17" s="11">
-        <v>0.87</v>
-      </c>
-      <c r="P17" s="19">
-        <v>3.6</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>0.21</v>
-      </c>
-      <c r="R17" s="11">
-        <v>3.01</v>
+        <v>10.52</v>
+      </c>
+      <c r="O17" s="19">
+        <v>0.85</v>
+      </c>
+      <c r="P17" s="14">
+        <v>3.49</v>
+      </c>
+      <c r="Q17" s="19">
+        <v>0.19</v>
+      </c>
+      <c r="R17" s="19">
+        <v>2.96</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>28</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" ref="T17" si="31">ROUND(B17/K17,3)</f>
-        <v>0.53100000000000003</v>
+        <f t="shared" ref="T17" si="32">ROUND(B17/K17,3)</f>
+        <v>0.53</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" ref="U17" si="32">ROUND(C17/L17,3)</f>
-        <v>0.86099999999999999</v>
+        <f t="shared" ref="U17" si="33">ROUND(C17/L17,3)</f>
+        <v>0.86</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" ref="V17" si="33">ROUND(D17/M17,3)</f>
-        <v>21.550999999999998</v>
-      </c>
-      <c r="W17" s="2">
-        <f>ROUND(E17/N17,3)</f>
-        <v>20.384</v>
-      </c>
-      <c r="X17" s="10">
-        <f>ROUND(F17/O17,3)</f>
-        <v>30.276</v>
-      </c>
-      <c r="Y17" s="1">
-        <f>ROUND(G17/P17,3)</f>
-        <v>20.414000000000001</v>
-      </c>
-      <c r="Z17" s="10">
-        <f>ROUND(H17/Q17,3)</f>
-        <v>4.9050000000000002</v>
-      </c>
-      <c r="AA17" s="9">
-        <f>ROUND(I17/R17,3)</f>
-        <v>17.468</v>
+        <f t="shared" ref="V17" si="34">ROUND(D17/M17,3)</f>
+        <v>21.6</v>
+      </c>
+      <c r="W17" s="19">
+        <f t="shared" si="22"/>
+        <v>19.989000000000001</v>
+      </c>
+      <c r="X17" s="19">
+        <f t="shared" si="22"/>
+        <v>31.164999999999999</v>
+      </c>
+      <c r="Y17" s="14">
+        <f t="shared" si="22"/>
+        <v>20.146000000000001</v>
+      </c>
+      <c r="Z17" s="19">
+        <f t="shared" si="22"/>
+        <v>5.5259999999999998</v>
+      </c>
+      <c r="AA17" s="19">
+        <f t="shared" si="22"/>
+        <v>17.283999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="5">
+        <f t="shared" ref="B18" si="35">D$2/D18</f>
+        <v>4.0490067560754266</v>
+      </c>
+      <c r="C18" s="5">
+        <f t="shared" ref="C18" si="36">D17/D18</f>
+        <v>0.98668952304124236</v>
+      </c>
+      <c r="D18" s="4">
+        <f>SUM(F18:H18)</f>
+        <v>99.169999999999987</v>
+      </c>
+      <c r="E18" s="19">
+        <v>215.48</v>
+      </c>
+      <c r="F18" s="19">
+        <v>26.83</v>
+      </c>
+      <c r="G18" s="14">
+        <v>71.349999999999994</v>
+      </c>
+      <c r="H18" s="19">
+        <v>0.99</v>
+      </c>
+      <c r="I18" s="15">
+        <v>51.3</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" ref="K18" si="37">M$2/M18</f>
+        <v>8.125</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" ref="L18" si="38">M17/M18</f>
+        <v>1.0486111111111114</v>
+      </c>
+      <c r="M18" s="4">
+        <f t="shared" ref="M18" si="39">SUM(O18:Q18)</f>
+        <v>4.3199999999999994</v>
+      </c>
+      <c r="N18" s="19">
+        <v>10.51</v>
+      </c>
+      <c r="O18" s="19">
+        <v>0.86</v>
+      </c>
+      <c r="P18" s="14">
+        <v>3.28</v>
+      </c>
+      <c r="Q18" s="19">
+        <v>0.18</v>
+      </c>
+      <c r="R18" s="15">
+        <v>2.62</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="T18" s="5">
+        <f t="shared" ref="T18" si="40">ROUND(B18/K18,3)</f>
+        <v>0.498</v>
+      </c>
+      <c r="U18" s="5">
+        <f t="shared" ref="U18" si="41">ROUND(C18/L18,3)</f>
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="V18" s="4">
+        <f t="shared" ref="V18" si="42">ROUND(D18/M18,3)</f>
+        <v>22.956</v>
+      </c>
+      <c r="W18" s="19">
+        <f t="shared" ref="W18" si="43">ROUND(E18/N18,3)</f>
+        <v>20.501999999999999</v>
+      </c>
+      <c r="X18" s="19">
+        <f t="shared" ref="X18" si="44">ROUND(F18/O18,3)</f>
+        <v>31.198</v>
+      </c>
+      <c r="Y18" s="14">
+        <f t="shared" ref="Y18" si="45">ROUND(G18/P18,3)</f>
+        <v>21.753</v>
+      </c>
+      <c r="Z18" s="19">
+        <f t="shared" ref="Z18" si="46">ROUND(H18/Q18,3)</f>
+        <v>5.5</v>
+      </c>
+      <c r="AA18" s="15">
+        <f t="shared" ref="AA18" si="47">ROUND(I18/R18,3)</f>
+        <v>19.579999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B8CC5D-5606-4541-817B-E445B6373675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD01AE5-B344-4BEC-B77D-C72F186C2EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>H22</t>
   </si>
@@ -127,6 +127,10 @@
   </si>
   <si>
     <t>H38</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H39</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -271,7 +275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -330,6 +334,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -646,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="13"/>
@@ -2010,95 +2017,95 @@
       </c>
       <c r="B15" s="2">
         <f t="shared" ref="B15" si="18">D$2/D15</f>
-        <v>4.0584192439862532</v>
+        <v>4.1468553134359185</v>
       </c>
       <c r="C15" s="2">
         <f t="shared" ref="C15" si="19">D14/D15</f>
-        <v>1.170103092783505</v>
+        <v>1.1956005370236498</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(F15:H15)</f>
-        <v>98.940000000000012</v>
+        <v>96.83</v>
       </c>
       <c r="E15" s="5">
-        <v>213.68</v>
+        <v>218.71</v>
       </c>
       <c r="F15" s="8">
-        <v>26.71</v>
+        <v>25.46</v>
       </c>
       <c r="G15" s="1">
-        <v>71.22</v>
+        <v>70.33</v>
       </c>
       <c r="H15" s="8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I15" s="3">
-        <v>51.44</v>
+        <v>50.34</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15" si="20">M$2/M15</f>
-        <v>6.5241635687732336</v>
+        <v>6.5730337078651662</v>
       </c>
       <c r="L15" s="2">
         <f t="shared" ref="L15" si="21">M14/M15</f>
-        <v>1.0910780669144982</v>
+        <v>1.0992509363295879</v>
       </c>
       <c r="M15" s="6">
         <f t="shared" si="9"/>
-        <v>5.38</v>
+        <v>5.3400000000000007</v>
       </c>
       <c r="N15" s="5">
-        <v>75.06</v>
+        <v>77.02</v>
       </c>
       <c r="O15" s="8">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="P15" s="1">
-        <v>4.3099999999999996</v>
+        <v>4.29</v>
       </c>
       <c r="Q15" s="8">
         <v>0.19</v>
       </c>
       <c r="R15" s="3">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="S15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="0"/>
-        <v>0.622</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="1"/>
-        <v>1.0720000000000001</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="V15" s="6">
         <f t="shared" si="2"/>
-        <v>18.39</v>
+        <v>18.132999999999999</v>
       </c>
       <c r="W15" s="5">
-        <f t="shared" ref="W15:AA17" si="22">ROUND(E15/N15,3)</f>
-        <v>2.847</v>
+        <f>ROUND(E15/N15,3)</f>
+        <v>2.84</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" si="22"/>
-        <v>30.352</v>
+        <f>ROUND(F15/O15,3)</f>
+        <v>29.605</v>
       </c>
       <c r="Y15" s="1">
-        <f t="shared" si="22"/>
-        <v>16.524000000000001</v>
+        <f>ROUND(G15/P15,3)</f>
+        <v>16.393999999999998</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="22"/>
-        <v>5.3159999999999998</v>
+        <f>ROUND(H15/Q15,3)</f>
+        <v>5.4740000000000002</v>
       </c>
       <c r="AA15" s="3">
-        <f t="shared" si="22"/>
-        <v>13.903</v>
+        <f>ROUND(I15/R15,3)</f>
+        <v>13.532</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2106,96 +2113,96 @@
         <v>27</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" ref="B16" si="23">D$2/D16</f>
-        <v>4.0029907287409028</v>
+        <f t="shared" ref="B16" si="22">D$2/D16</f>
+        <v>4.1753145471560771</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16" si="24">D15/D16</f>
-        <v>0.98634233874987554</v>
+        <f t="shared" ref="C16" si="23">D15/D16</f>
+        <v>1.0068628470416969</v>
       </c>
       <c r="D16" s="4">
         <f>SUM(F16:H16)</f>
-        <v>100.31</v>
+        <v>96.17</v>
       </c>
       <c r="E16" s="1">
-        <v>209.82</v>
+        <v>208.27</v>
       </c>
       <c r="F16" s="8">
-        <v>26.99</v>
+        <v>25.17</v>
       </c>
       <c r="G16" s="8">
-        <v>72.2</v>
+        <v>70.02</v>
       </c>
       <c r="H16" s="8">
-        <v>1.1200000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="7">
-        <v>51.91</v>
+        <v>50.21</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16" si="25">M$2/M16</f>
-        <v>6.5</v>
+        <f t="shared" ref="K16" si="24">M$2/M16</f>
+        <v>6.6603415559772277</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16" si="26">M15/M16</f>
-        <v>0.99629629629629635</v>
+        <f t="shared" ref="L16" si="25">M15/M16</f>
+        <v>1.013282732447818</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="9"/>
-        <v>5.3999999999999995</v>
+        <v>5.2700000000000005</v>
       </c>
       <c r="N16" s="1">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="O16" s="8">
         <v>0.85</v>
       </c>
       <c r="P16" s="8">
-        <v>4.3499999999999996</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="Q16" s="8">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="R16" s="7">
-        <v>3.73</v>
+        <v>3.64</v>
       </c>
       <c r="S16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="T16" s="5">
         <f t="shared" si="0"/>
-        <v>0.61599999999999999</v>
+        <v>0.627</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="2"/>
-        <v>18.576000000000001</v>
+        <v>18.248999999999999</v>
       </c>
       <c r="W16" s="1">
-        <f t="shared" si="22"/>
-        <v>20.213999999999999</v>
+        <f>ROUND(E16/N16,3)</f>
+        <v>19.835000000000001</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="22"/>
-        <v>31.753</v>
+        <f>ROUND(F16/O16,3)</f>
+        <v>29.611999999999998</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" si="22"/>
-        <v>16.597999999999999</v>
+        <f>ROUND(G16/P16,3)</f>
+        <v>16.553000000000001</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" si="22"/>
-        <v>5.6</v>
+        <f>ROUND(H16/Q16,3)</f>
+        <v>5.1580000000000004</v>
       </c>
       <c r="AA16" s="7">
-        <f t="shared" si="22"/>
-        <v>13.917</v>
+        <f>ROUND(I16/R16,3)</f>
+        <v>13.794</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2203,96 +2210,96 @@
         <v>28</v>
       </c>
       <c r="B17" s="5">
-        <f t="shared" ref="B17" si="27">D$2/D17</f>
-        <v>4.1036280020439451</v>
+        <f t="shared" ref="B17" si="26">D$2/D17</f>
+        <v>4.1692451458830853</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17" si="28">D16/D17</f>
-        <v>1.0251405212059275</v>
+        <f t="shared" ref="C17" si="27">D16/D17</f>
+        <v>0.99854636071020664</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(F17:H17)</f>
-        <v>97.85</v>
+        <v>96.31</v>
       </c>
       <c r="E17" s="19">
-        <v>210.28</v>
+        <v>204.49</v>
       </c>
       <c r="F17" s="19">
-        <v>26.49</v>
+        <v>25.01</v>
       </c>
       <c r="G17" s="14">
-        <v>70.31</v>
+        <v>70.25</v>
       </c>
       <c r="H17" s="19">
         <v>1.05</v>
       </c>
       <c r="I17" s="19">
-        <v>51.16</v>
+        <v>49.46</v>
       </c>
       <c r="J17" s="18" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" ref="K17" si="29">M$2/M17</f>
+        <f t="shared" ref="K17" si="28">M$2/M17</f>
         <v>7.7483443708609254</v>
       </c>
       <c r="L17" s="5">
-        <f t="shared" ref="L17" si="30">M16/M17</f>
-        <v>1.1920529801324502</v>
+        <f t="shared" ref="L17" si="29">M16/M17</f>
+        <v>1.1633554083885209</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" ref="M17" si="31">SUM(O17:Q17)</f>
+        <f t="shared" ref="M17" si="30">SUM(O17:Q17)</f>
         <v>4.53</v>
       </c>
       <c r="N17" s="19">
-        <v>10.52</v>
+        <v>10.039999999999999</v>
       </c>
       <c r="O17" s="19">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="P17" s="14">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
       <c r="Q17" s="19">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="R17" s="19">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="S17" s="18" t="s">
         <v>28</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" ref="T17" si="32">ROUND(B17/K17,3)</f>
-        <v>0.53</v>
+        <f t="shared" ref="T17" si="31">ROUND(B17/K17,3)</f>
+        <v>0.53800000000000003</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" ref="U17" si="33">ROUND(C17/L17,3)</f>
-        <v>0.86</v>
+        <f t="shared" ref="U17" si="32">ROUND(C17/L17,3)</f>
+        <v>0.85799999999999998</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" ref="V17" si="34">ROUND(D17/M17,3)</f>
-        <v>21.6</v>
+        <f t="shared" ref="V17" si="33">ROUND(D17/M17,3)</f>
+        <v>21.26</v>
       </c>
       <c r="W17" s="19">
-        <f t="shared" si="22"/>
-        <v>19.989000000000001</v>
+        <f>ROUND(E17/N17,3)</f>
+        <v>20.367999999999999</v>
       </c>
       <c r="X17" s="19">
-        <f t="shared" si="22"/>
-        <v>31.164999999999999</v>
+        <f>ROUND(F17/O17,3)</f>
+        <v>31.658000000000001</v>
       </c>
       <c r="Y17" s="14">
-        <f t="shared" si="22"/>
-        <v>20.146000000000001</v>
+        <f>ROUND(G17/P17,3)</f>
+        <v>19.844999999999999</v>
       </c>
       <c r="Z17" s="19">
-        <f t="shared" si="22"/>
-        <v>5.5259999999999998</v>
+        <f>ROUND(H17/Q17,3)</f>
+        <v>5.25</v>
       </c>
       <c r="AA17" s="19">
-        <f t="shared" si="22"/>
-        <v>17.283999999999999</v>
+        <f>ROUND(I17/R17,3)</f>
+        <v>16.765999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2300,52 +2307,52 @@
         <v>30</v>
       </c>
       <c r="B18" s="5">
-        <f t="shared" ref="B18" si="35">D$2/D18</f>
-        <v>4.0490067560754266</v>
+        <f t="shared" ref="B18" si="34">D$2/D18</f>
+        <v>4.1550082781456954</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18" si="36">D17/D18</f>
-        <v>0.98668952304124236</v>
+        <f t="shared" ref="C18" si="35">D17/D18</f>
+        <v>0.99658526490066224</v>
       </c>
       <c r="D18" s="4">
         <f>SUM(F18:H18)</f>
-        <v>99.169999999999987</v>
+        <v>96.64</v>
       </c>
       <c r="E18" s="19">
-        <v>215.48</v>
+        <v>203.64</v>
       </c>
       <c r="F18" s="19">
-        <v>26.83</v>
+        <v>25.53</v>
       </c>
       <c r="G18" s="14">
-        <v>71.349999999999994</v>
+        <v>70.13</v>
       </c>
       <c r="H18" s="19">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I18" s="15">
-        <v>51.3</v>
+        <v>49.91</v>
       </c>
       <c r="J18" s="18" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="5">
-        <f t="shared" ref="K18" si="37">M$2/M18</f>
-        <v>8.125</v>
+        <f t="shared" ref="K18" si="36">M$2/M18</f>
+        <v>8.2009345794392523</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" ref="L18" si="38">M17/M18</f>
-        <v>1.0486111111111114</v>
+        <f t="shared" ref="L18" si="37">M17/M18</f>
+        <v>1.0584112149532712</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" ref="M18" si="39">SUM(O18:Q18)</f>
-        <v>4.3199999999999994</v>
+        <f t="shared" ref="M18" si="38">SUM(O18:Q18)</f>
+        <v>4.2799999999999994</v>
       </c>
       <c r="N18" s="19">
-        <v>10.51</v>
+        <v>10.11</v>
       </c>
       <c r="O18" s="19">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="P18" s="14">
         <v>3.28</v>
@@ -2360,36 +2367,133 @@
         <v>29</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18" si="40">ROUND(B18/K18,3)</f>
-        <v>0.498</v>
+        <f t="shared" ref="T18" si="39">ROUND(B18/K18,3)</f>
+        <v>0.50700000000000001</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" ref="U18" si="41">ROUND(C18/L18,3)</f>
-        <v>0.94099999999999995</v>
+        <f t="shared" ref="U18" si="40">ROUND(C18/L18,3)</f>
+        <v>0.94199999999999995</v>
       </c>
       <c r="V18" s="4">
-        <f t="shared" ref="V18" si="42">ROUND(D18/M18,3)</f>
-        <v>22.956</v>
+        <f t="shared" ref="V18" si="41">ROUND(D18/M18,3)</f>
+        <v>22.579000000000001</v>
       </c>
       <c r="W18" s="19">
-        <f t="shared" ref="W18" si="43">ROUND(E18/N18,3)</f>
-        <v>20.501999999999999</v>
+        <f>ROUND(E18/N18,3)</f>
+        <v>20.141999999999999</v>
       </c>
       <c r="X18" s="19">
-        <f t="shared" ref="X18" si="44">ROUND(F18/O18,3)</f>
-        <v>31.198</v>
+        <f>ROUND(F18/O18,3)</f>
+        <v>31.134</v>
       </c>
       <c r="Y18" s="14">
-        <f t="shared" ref="Y18" si="45">ROUND(G18/P18,3)</f>
-        <v>21.753</v>
+        <f>ROUND(G18/P18,3)</f>
+        <v>21.381</v>
       </c>
       <c r="Z18" s="19">
-        <f t="shared" ref="Z18" si="46">ROUND(H18/Q18,3)</f>
-        <v>5.5</v>
+        <f>ROUND(H18/Q18,3)</f>
+        <v>5.444</v>
       </c>
       <c r="AA18" s="15">
-        <f t="shared" ref="AA18" si="47">ROUND(I18/R18,3)</f>
-        <v>19.579999999999998</v>
+        <f>ROUND(I18/R18,3)</f>
+        <v>19.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="5">
+        <f t="shared" ref="B19" si="42">D$2/D19</f>
+        <v>4.3316073354908298</v>
+      </c>
+      <c r="C19" s="5">
+        <f t="shared" ref="C19" si="43">D18/D19</f>
+        <v>1.0425026968716289</v>
+      </c>
+      <c r="D19" s="4">
+        <f>SUM(F19:H19)</f>
+        <v>92.7</v>
+      </c>
+      <c r="E19" s="9">
+        <v>208.8</v>
+      </c>
+      <c r="F19" s="9">
+        <v>25.04</v>
+      </c>
+      <c r="G19" s="14">
+        <v>66.61</v>
+      </c>
+      <c r="H19" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="I19" s="10">
+        <v>49.6</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" ref="K19" si="44">M$2/M19</f>
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" ref="L19" si="45">M18/M19</f>
+        <v>1.0974358974358973</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" ref="M19" si="46">SUM(O19:Q19)</f>
+        <v>3.9</v>
+      </c>
+      <c r="N19" s="9">
+        <v>10.81</v>
+      </c>
+      <c r="O19" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="P19" s="14">
+        <v>2.86</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="R19" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="S19" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" ref="T19" si="47">ROUND(B19/K19,3)</f>
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" ref="U19" si="48">ROUND(C19/L19,3)</f>
+        <v>0.95</v>
+      </c>
+      <c r="V19" s="4">
+        <f t="shared" ref="V19" si="49">ROUND(D19/M19,3)</f>
+        <v>23.768999999999998</v>
+      </c>
+      <c r="W19" s="19">
+        <f>ROUND(E19/N19,3)</f>
+        <v>19.315000000000001</v>
+      </c>
+      <c r="X19" s="19">
+        <f>ROUND(F19/O19,3)</f>
+        <v>29.459</v>
+      </c>
+      <c r="Y19" s="14">
+        <f>ROUND(G19/P19,3)</f>
+        <v>23.29</v>
+      </c>
+      <c r="Z19" s="19">
+        <f>ROUND(H19/Q19,3)</f>
+        <v>5.5259999999999998</v>
+      </c>
+      <c r="AA19" s="20">
+        <f>ROUND(I19/R19,3)</f>
+        <v>19.84</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD01AE5-B344-4BEC-B77D-C72F186C2EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A703F5F7-5A89-4FEE-9336-BA81F180CF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
   <si>
     <t>H22</t>
   </si>
@@ -124,14 +124,14 @@
   </si>
   <si>
     <t>H38</t>
-  </si>
-  <si>
-    <t>H38</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>H39</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H40</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="13"/>
@@ -766,22 +766,22 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(F2:H2)</f>
-        <v>401.53999999999996</v>
+        <v>391.68</v>
       </c>
       <c r="E2" s="5">
-        <v>379.02</v>
+        <v>372.69</v>
       </c>
       <c r="F2" s="8">
-        <v>142.38</v>
+        <v>140.16</v>
       </c>
       <c r="G2" s="8">
-        <v>120.7</v>
+        <v>115.45</v>
       </c>
       <c r="H2" s="8">
-        <v>138.46</v>
+        <v>136.07</v>
       </c>
       <c r="I2" s="7">
-        <v>226.37</v>
+        <v>223.78</v>
       </c>
       <c r="J2" s="16" t="s">
         <v>0</v>
@@ -794,22 +794,22 @@
       </c>
       <c r="M2" s="4">
         <f>SUM(O2:Q2)</f>
-        <v>35.099999999999994</v>
+        <v>32.869999999999997</v>
       </c>
       <c r="N2" s="5">
-        <v>67.77</v>
+        <v>68.569999999999993</v>
       </c>
       <c r="O2" s="8">
-        <v>5.3</v>
+        <v>4.99</v>
       </c>
       <c r="P2" s="8">
-        <v>12.99</v>
+        <v>12.19</v>
       </c>
       <c r="Q2" s="8">
-        <v>16.809999999999999</v>
+        <v>15.69</v>
       </c>
       <c r="R2" s="7">
-        <v>28.39</v>
+        <v>26.66</v>
       </c>
       <c r="S2" s="16" t="s">
         <v>0</v>
@@ -824,27 +824,27 @@
       </c>
       <c r="V2" s="4">
         <f t="shared" ref="V2:V16" si="2">ROUND(D2/M2,3)</f>
-        <v>11.44</v>
+        <v>11.916</v>
       </c>
       <c r="W2" s="5">
         <f t="shared" ref="W2:W14" si="3">ROUND(E2/N2,3)</f>
-        <v>5.593</v>
+        <v>5.4349999999999996</v>
       </c>
       <c r="X2" s="8">
         <f t="shared" ref="X2:X14" si="4">ROUND(F2/O2,3)</f>
-        <v>26.864000000000001</v>
+        <v>28.088000000000001</v>
       </c>
       <c r="Y2" s="8">
         <f t="shared" ref="Y2:Y14" si="5">ROUND(G2/P2,3)</f>
-        <v>9.2919999999999998</v>
+        <v>9.4710000000000001</v>
       </c>
       <c r="Z2" s="8">
         <f t="shared" ref="Z2:Z14" si="6">ROUND(H2/Q2,3)</f>
-        <v>8.2370000000000001</v>
+        <v>8.6720000000000006</v>
       </c>
       <c r="AA2" s="7">
         <f t="shared" ref="AA2:AA14" si="7">ROUND(I2/R2,3)</f>
-        <v>7.9740000000000002</v>
+        <v>8.3940000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -853,95 +853,95 @@
       </c>
       <c r="B3" s="2">
         <f>D$2/D3</f>
-        <v>1.5459900666076312</v>
+        <v>1.5574996023540639</v>
       </c>
       <c r="C3" s="2">
         <f>D2/D3</f>
-        <v>1.5459900666076312</v>
+        <v>1.5574996023540639</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" ref="D3:D14" si="8">SUM(F3:H3)</f>
-        <v>259.72999999999996</v>
+        <v>251.48000000000002</v>
       </c>
       <c r="E3" s="5">
-        <v>379.46</v>
+        <v>365.53</v>
       </c>
       <c r="F3" s="8">
-        <v>139.13</v>
+        <v>134.85</v>
       </c>
       <c r="G3" s="8">
-        <v>118.16</v>
+        <v>114.51</v>
       </c>
       <c r="H3" s="1">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="I3" s="7">
-        <v>227.29</v>
+        <v>219.12</v>
       </c>
       <c r="J3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="2">
         <f>M$2/M3</f>
-        <v>1.9306930693069304</v>
+        <v>1.8697383390216151</v>
       </c>
       <c r="L3" s="2">
         <f>M2/M3</f>
-        <v>1.9306930693069304</v>
+        <v>1.8697383390216151</v>
       </c>
       <c r="M3" s="6">
         <f t="shared" ref="M3:M16" si="9">SUM(O3:Q3)</f>
-        <v>18.18</v>
+        <v>17.580000000000002</v>
       </c>
       <c r="N3" s="5">
-        <v>68.98</v>
+        <v>68.42</v>
       </c>
       <c r="O3" s="8">
-        <v>5.09</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="P3" s="8">
-        <v>12.62</v>
+        <v>12.26</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="R3" s="7">
-        <v>27.38</v>
+        <v>26.59</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="2">
         <f t="shared" si="0"/>
-        <v>0.80100000000000005</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="U3" s="2">
         <f t="shared" si="1"/>
-        <v>0.80100000000000005</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="V3" s="6">
         <f t="shared" si="2"/>
-        <v>14.287000000000001</v>
+        <v>14.305</v>
       </c>
       <c r="W3" s="5">
         <f t="shared" si="3"/>
-        <v>5.5010000000000003</v>
+        <v>5.3419999999999996</v>
       </c>
       <c r="X3" s="8">
         <f t="shared" si="4"/>
-        <v>27.334</v>
+        <v>27.747</v>
       </c>
       <c r="Y3" s="8">
         <f t="shared" si="5"/>
-        <v>9.3629999999999995</v>
+        <v>9.34</v>
       </c>
       <c r="Z3" s="1">
         <f t="shared" si="6"/>
-        <v>5.1909999999999998</v>
+        <v>4.609</v>
       </c>
       <c r="AA3" s="7">
         <f t="shared" si="7"/>
-        <v>8.3010000000000002</v>
+        <v>8.2409999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -950,95 +950,95 @@
       </c>
       <c r="B4" s="2">
         <f t="shared" ref="B4:B12" si="10">D$2/D4</f>
-        <v>1.9822283655032826</v>
+        <v>1.9913569576490926</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:C12" si="11">D3/D4</f>
-        <v>1.2821740632867649</v>
+        <v>1.2785601708271901</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="8"/>
-        <v>202.57</v>
+        <v>196.69</v>
       </c>
       <c r="E4" s="5">
-        <v>364.8</v>
+        <v>369.35</v>
       </c>
       <c r="F4" s="1">
-        <v>74.77</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="G4" s="8">
-        <v>125.29</v>
+        <v>121.84</v>
       </c>
       <c r="H4" s="8">
-        <v>2.5099999999999998</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I4" s="7">
-        <v>222.02</v>
+        <v>215.94</v>
       </c>
       <c r="J4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="2">
         <f t="shared" ref="K4:K12" si="12">M$2/M4</f>
-        <v>2.0671378091872787</v>
+        <v>2.0030469226081657</v>
       </c>
       <c r="L4" s="2">
         <f t="shared" ref="L4:L12" si="13">M3/M4</f>
-        <v>1.0706713780918728</v>
+        <v>1.0712979890310788</v>
       </c>
       <c r="M4" s="6">
         <f t="shared" si="9"/>
-        <v>16.98</v>
+        <v>16.41</v>
       </c>
       <c r="N4" s="5">
-        <v>68.959999999999994</v>
+        <v>69.11</v>
       </c>
       <c r="O4" s="1">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P4" s="8">
-        <v>12.7</v>
+        <v>12.29</v>
       </c>
       <c r="Q4" s="8">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="R4" s="7">
-        <v>27.4</v>
+        <v>26.68</v>
       </c>
       <c r="S4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="2">
         <f t="shared" si="0"/>
-        <v>0.95899999999999996</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" si="1"/>
-        <v>1.198</v>
+        <v>1.1930000000000001</v>
       </c>
       <c r="V4" s="6">
         <f t="shared" si="2"/>
-        <v>11.93</v>
+        <v>11.986000000000001</v>
       </c>
       <c r="W4" s="5">
         <f t="shared" si="3"/>
-        <v>5.29</v>
+        <v>5.3440000000000003</v>
       </c>
       <c r="X4" s="1">
         <f t="shared" si="4"/>
-        <v>19.675999999999998</v>
+        <v>19.904</v>
       </c>
       <c r="Y4" s="8">
         <f t="shared" si="5"/>
-        <v>9.8650000000000002</v>
+        <v>9.9139999999999997</v>
       </c>
       <c r="Z4" s="8">
         <f t="shared" si="6"/>
-        <v>5.2290000000000001</v>
+        <v>4.681</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" si="7"/>
-        <v>8.1029999999999998</v>
+        <v>8.0939999999999994</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1047,95 +1047,95 @@
       </c>
       <c r="B5" s="2">
         <f t="shared" si="10"/>
-        <v>2.2621971830985914</v>
+        <v>2.2487082328625561</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" si="11"/>
-        <v>1.1412394366197183</v>
+        <v>1.1292341256171776</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="8"/>
-        <v>177.5</v>
+        <v>174.18</v>
       </c>
       <c r="E5" s="5">
-        <v>379.87</v>
+        <v>364.67</v>
       </c>
       <c r="F5" s="8">
-        <v>75.06</v>
+        <v>73.83</v>
       </c>
       <c r="G5" s="1">
-        <v>100.06</v>
+        <v>98.15</v>
       </c>
       <c r="H5" s="8">
-        <v>2.38</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I5" s="7">
-        <v>221.9</v>
+        <v>217.76</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" si="12"/>
-        <v>3.7741935483870961</v>
+        <v>3.6280353200882991</v>
       </c>
       <c r="L5" s="2">
         <f t="shared" si="13"/>
-        <v>1.8258064516129031</v>
+        <v>1.811258278145695</v>
       </c>
       <c r="M5" s="6">
         <f t="shared" si="9"/>
-        <v>9.3000000000000007</v>
+        <v>9.0600000000000023</v>
       </c>
       <c r="N5" s="5">
-        <v>67.48</v>
+        <v>65.209999999999994</v>
       </c>
       <c r="O5" s="8">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
       <c r="P5" s="1">
-        <v>5.03</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="Q5" s="8">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="R5" s="7">
-        <v>27.22</v>
+        <v>26.2</v>
       </c>
       <c r="S5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="T5" s="2">
         <f t="shared" si="0"/>
-        <v>0.59899999999999998</v>
+        <v>0.62</v>
       </c>
       <c r="U5" s="2">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.623</v>
       </c>
       <c r="V5" s="6">
         <f t="shared" si="2"/>
-        <v>19.085999999999999</v>
+        <v>19.225000000000001</v>
       </c>
       <c r="W5" s="5">
         <f t="shared" si="3"/>
-        <v>5.6289999999999996</v>
+        <v>5.5919999999999996</v>
       </c>
       <c r="X5" s="8">
         <f t="shared" si="4"/>
-        <v>19.805</v>
+        <v>20.172000000000001</v>
       </c>
       <c r="Y5" s="1">
         <f t="shared" si="5"/>
-        <v>19.893000000000001</v>
+        <v>19.867999999999999</v>
       </c>
       <c r="Z5" s="8">
         <f t="shared" si="6"/>
-        <v>4.9580000000000002</v>
+        <v>4.7830000000000004</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="7"/>
-        <v>8.1519999999999992</v>
+        <v>8.3109999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1144,87 +1144,87 @@
       </c>
       <c r="B6" s="5">
         <f t="shared" si="10"/>
-        <v>2.3345348837209294</v>
+        <v>2.260779220779221</v>
       </c>
       <c r="C6" s="5">
         <f t="shared" si="11"/>
-        <v>1.0319767441860463</v>
+        <v>1.0053679653679655</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="8"/>
-        <v>172.00000000000003</v>
+        <v>173.25</v>
       </c>
       <c r="E6" s="5">
-        <v>361.21</v>
+        <v>355.68</v>
       </c>
       <c r="F6" s="8">
-        <v>73.44</v>
+        <v>73.319999999999993</v>
       </c>
       <c r="G6" s="8">
-        <v>96.29</v>
+        <v>97.66</v>
       </c>
       <c r="H6" s="8">
         <v>2.27</v>
       </c>
       <c r="I6" s="3">
-        <v>80.819999999999993</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="J6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="5">
         <f t="shared" si="12"/>
-        <v>3.7864077669902909</v>
+        <v>3.6280353200882995</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" si="13"/>
-        <v>1.0032362459546926</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="9"/>
-        <v>9.27</v>
+        <v>9.06</v>
       </c>
       <c r="N6" s="5">
-        <v>67.34</v>
+        <v>67.66</v>
       </c>
       <c r="O6" s="8">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
       <c r="P6" s="8">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="Q6" s="8">
         <v>0.48</v>
       </c>
       <c r="R6" s="3">
-        <v>4.5599999999999996</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="S6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="0"/>
-        <v>0.61699999999999999</v>
+        <v>0.623</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="1"/>
-        <v>1.0289999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="2"/>
-        <v>18.553999999999998</v>
+        <v>19.123000000000001</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="3"/>
-        <v>5.3639999999999999</v>
+        <v>5.2569999999999997</v>
       </c>
       <c r="X6" s="8">
         <f t="shared" si="4"/>
-        <v>19.376999999999999</v>
+        <v>20.033000000000001</v>
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="5"/>
-        <v>19.257999999999999</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="Z6" s="8">
         <f t="shared" si="6"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AA6" s="3">
         <f t="shared" si="7"/>
-        <v>17.724</v>
+        <v>17.779</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1241,95 +1241,95 @@
       </c>
       <c r="B7" s="5">
         <f t="shared" si="10"/>
-        <v>2.1703691692340952</v>
+        <v>2.1988435412339302</v>
       </c>
       <c r="C7" s="5">
         <f t="shared" si="11"/>
-        <v>0.92967947678503882</v>
+        <v>0.97260427777465885</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="8"/>
-        <v>185.01</v>
+        <v>178.13000000000002</v>
       </c>
       <c r="E7" s="5">
-        <v>377.51</v>
+        <v>361.32</v>
       </c>
       <c r="F7" s="8">
-        <v>82.34</v>
+        <v>79.7</v>
       </c>
       <c r="G7" s="8">
-        <v>101.48</v>
+        <v>97.35</v>
       </c>
       <c r="H7" s="1">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="I7" s="7">
-        <v>82.8</v>
+        <v>80.17</v>
       </c>
       <c r="J7" s="16" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="5">
         <f t="shared" si="12"/>
-        <v>3.908685968819599</v>
+        <v>3.6932584269662918</v>
       </c>
       <c r="L7" s="5">
         <f t="shared" si="13"/>
-        <v>1.0322939866369711</v>
+        <v>1.0179775280898877</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="9"/>
-        <v>8.9799999999999986</v>
+        <v>8.9</v>
       </c>
       <c r="N7" s="5">
-        <v>77.61</v>
+        <v>76.17</v>
       </c>
       <c r="O7" s="8">
         <v>3.68</v>
       </c>
       <c r="P7" s="8">
-        <v>5.0999999999999996</v>
+        <v>5.03</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="R7" s="7">
-        <v>4.57</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="S7" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="0"/>
-        <v>0.55500000000000005</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="1"/>
-        <v>0.90100000000000002</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="V7" s="4">
         <f t="shared" si="2"/>
-        <v>20.602</v>
+        <v>20.015000000000001</v>
       </c>
       <c r="W7" s="5">
         <f t="shared" si="3"/>
-        <v>4.8639999999999999</v>
+        <v>4.7439999999999998</v>
       </c>
       <c r="X7" s="8">
         <f t="shared" si="4"/>
-        <v>22.375</v>
+        <v>21.658000000000001</v>
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="5"/>
-        <v>19.898</v>
+        <v>19.353999999999999</v>
       </c>
       <c r="Z7" s="1">
         <f t="shared" si="6"/>
-        <v>5.95</v>
+        <v>5.6840000000000002</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="7"/>
-        <v>18.117999999999999</v>
+        <v>17.895</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1338,95 +1338,95 @@
       </c>
       <c r="B8" s="5">
         <f t="shared" si="10"/>
-        <v>2.1691966938577059</v>
+        <v>2.1740674955595027</v>
       </c>
       <c r="C8" s="5">
         <f t="shared" si="11"/>
-        <v>0.99945978067095231</v>
+        <v>0.98873223801065735</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="8"/>
-        <v>185.11</v>
+        <v>180.16</v>
       </c>
       <c r="E8" s="5">
-        <v>492.18</v>
+        <v>468.52</v>
       </c>
       <c r="F8" s="8">
-        <v>82.65</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="G8" s="8">
-        <v>101.41</v>
+        <v>98.54</v>
       </c>
       <c r="H8" s="8">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="I8" s="7">
-        <v>82.93</v>
+        <v>82.18</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="5">
         <f t="shared" si="12"/>
-        <v>3.9795918367346932</v>
+        <v>3.7912341407151091</v>
       </c>
       <c r="L8" s="5">
         <f t="shared" si="13"/>
-        <v>1.0181405895691609</v>
+        <v>1.0265282583621684</v>
       </c>
       <c r="M8" s="4">
         <f t="shared" si="9"/>
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="N8" s="5">
-        <v>96.53</v>
+        <v>89.32</v>
       </c>
       <c r="O8" s="8">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="P8" s="8">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="Q8" s="8">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="R8" s="7">
-        <v>4.47</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="S8" s="16" t="s">
         <v>6</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="0"/>
-        <v>0.54500000000000004</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="1"/>
-        <v>0.98199999999999998</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="V8" s="4">
         <f t="shared" si="2"/>
-        <v>20.988</v>
+        <v>20.78</v>
       </c>
       <c r="W8" s="5">
         <f t="shared" si="3"/>
-        <v>5.0990000000000002</v>
+        <v>5.2450000000000001</v>
       </c>
       <c r="X8" s="8">
         <f t="shared" si="4"/>
-        <v>22.831</v>
+        <v>22.64</v>
       </c>
       <c r="Y8" s="8">
         <f t="shared" si="5"/>
-        <v>20.282</v>
+        <v>19.988</v>
       </c>
       <c r="Z8" s="8">
         <f t="shared" si="6"/>
-        <v>5.25</v>
+        <v>5.6669999999999998</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="7"/>
-        <v>18.553000000000001</v>
+        <v>18.344000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1435,95 +1435,95 @@
       </c>
       <c r="B9" s="5">
         <f t="shared" si="10"/>
-        <v>2.2096632181377944</v>
+        <v>2.2244434348023625</v>
       </c>
       <c r="C9" s="5">
         <f t="shared" si="11"/>
-        <v>1.0186550737398197</v>
+        <v>1.0231712857791913</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="8"/>
-        <v>181.71999999999997</v>
+        <v>176.08</v>
       </c>
       <c r="E9" s="5">
-        <v>489.21</v>
+        <v>465.99</v>
       </c>
       <c r="F9" s="8">
-        <v>81.44</v>
+        <v>78.61</v>
       </c>
       <c r="G9" s="8">
-        <v>99.21</v>
+        <v>96.48</v>
       </c>
       <c r="H9" s="8">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="I9" s="7">
-        <v>80.959999999999994</v>
+        <v>78.36</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="K9" s="5">
         <f t="shared" si="12"/>
-        <v>4.0391254315304943</v>
+        <v>3.6002190580503837</v>
       </c>
       <c r="L9" s="5">
         <f t="shared" si="13"/>
-        <v>1.0149597238204835</v>
+        <v>0.94961664841182925</v>
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>8.69</v>
+        <v>9.129999999999999</v>
       </c>
       <c r="N9" s="5">
-        <v>91.73</v>
+        <v>89.84</v>
       </c>
       <c r="O9" s="8">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="P9" s="8">
-        <v>4.92</v>
+        <v>5.16</v>
       </c>
       <c r="Q9" s="8">
         <v>0.2</v>
       </c>
       <c r="R9" s="7">
-        <v>4.4400000000000004</v>
+        <v>4.67</v>
       </c>
       <c r="S9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="0"/>
-        <v>0.54700000000000004</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="1"/>
-        <v>1.004</v>
+        <v>1.077</v>
       </c>
       <c r="V9" s="4">
         <f t="shared" si="2"/>
-        <v>20.911000000000001</v>
+        <v>19.286000000000001</v>
       </c>
       <c r="W9" s="5">
         <f t="shared" si="3"/>
-        <v>5.3330000000000002</v>
+        <v>5.1870000000000003</v>
       </c>
       <c r="X9" s="8">
         <f t="shared" si="4"/>
-        <v>22.812000000000001</v>
+        <v>20.850999999999999</v>
       </c>
       <c r="Y9" s="8">
         <f t="shared" si="5"/>
-        <v>20.164999999999999</v>
+        <v>18.698</v>
       </c>
       <c r="Z9" s="8">
         <f t="shared" si="6"/>
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="7"/>
-        <v>18.234000000000002</v>
+        <v>16.779</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1532,95 +1532,95 @@
       </c>
       <c r="B10" s="5">
         <f t="shared" si="10"/>
-        <v>2.2138052707023927</v>
+        <v>2.2100095920555214</v>
       </c>
       <c r="C10" s="5">
         <f t="shared" si="11"/>
-        <v>1.0018745175873855</v>
+        <v>0.99351125655927341</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="8"/>
-        <v>181.38</v>
+        <v>177.23</v>
       </c>
       <c r="E10" s="2">
-        <v>249.29</v>
+        <v>241.42</v>
       </c>
       <c r="F10" s="8">
-        <v>81.16</v>
+        <v>79.81</v>
       </c>
       <c r="G10" s="8">
-        <v>99</v>
+        <v>96.38</v>
       </c>
       <c r="H10" s="8">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="I10" s="7">
-        <v>80.72</v>
+        <v>78.36</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="12"/>
-        <v>3.9705882352941169</v>
+        <v>3.6808510638297869</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="13"/>
-        <v>0.98303167420814475</v>
+        <v>1.0223964165733481</v>
       </c>
       <c r="M10" s="4">
         <f t="shared" si="9"/>
-        <v>8.84</v>
+        <v>8.93</v>
       </c>
       <c r="N10" s="2">
-        <v>76.53</v>
+        <v>77.58</v>
       </c>
       <c r="O10" s="8">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="P10" s="8">
-        <v>5.0199999999999996</v>
+        <v>5.08</v>
       </c>
       <c r="Q10" s="8">
         <v>0.2</v>
       </c>
       <c r="R10" s="7">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="S10" s="16" t="s">
         <v>8</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="0"/>
-        <v>0.55800000000000005</v>
+        <v>0.6</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="1"/>
-        <v>1.0189999999999999</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="V10" s="4">
         <f t="shared" si="2"/>
-        <v>20.518000000000001</v>
+        <v>19.847000000000001</v>
       </c>
       <c r="W10" s="2">
         <f t="shared" si="3"/>
-        <v>3.2570000000000001</v>
+        <v>3.1120000000000001</v>
       </c>
       <c r="X10" s="8">
         <f t="shared" si="4"/>
-        <v>22.42</v>
+        <v>21.866</v>
       </c>
       <c r="Y10" s="8">
         <f t="shared" si="5"/>
-        <v>19.721</v>
+        <v>18.972000000000001</v>
       </c>
       <c r="Z10" s="8">
         <f t="shared" si="6"/>
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="7"/>
-        <v>17.78</v>
+        <v>17.222000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1629,95 +1629,95 @@
       </c>
       <c r="B11" s="2">
         <f t="shared" si="10"/>
-        <v>2.7188028979619472</v>
+        <v>2.7175466592659405</v>
       </c>
       <c r="C11" s="2">
         <f t="shared" si="11"/>
-        <v>1.2281129392646759</v>
+        <v>1.2296537847776312</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="8"/>
-        <v>147.69</v>
+        <v>144.13</v>
       </c>
       <c r="E11" s="5">
-        <v>215.95</v>
+        <v>206.67</v>
       </c>
       <c r="F11" s="1">
-        <v>43.93</v>
+        <v>42.84</v>
       </c>
       <c r="G11" s="8">
-        <v>102.58</v>
+        <v>100.16</v>
       </c>
       <c r="H11" s="8">
-        <v>1.18</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="I11" s="7">
-        <v>90.86</v>
+        <v>89.04</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="12"/>
-        <v>4.3120393120393112</v>
+        <v>4.0183374083129584</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="13"/>
-        <v>1.085995085995086</v>
+        <v>1.0916870415647921</v>
       </c>
       <c r="M11" s="6">
         <f t="shared" si="9"/>
-        <v>8.14</v>
+        <v>8.18</v>
       </c>
       <c r="N11" s="5">
-        <v>76.48</v>
+        <v>74.05</v>
       </c>
       <c r="O11" s="1">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P11" s="8">
-        <v>6.49</v>
+        <v>6.57</v>
       </c>
       <c r="Q11" s="8">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="R11" s="7">
-        <v>6.06</v>
+        <v>6.04</v>
       </c>
       <c r="S11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="T11" s="2">
         <f t="shared" si="0"/>
-        <v>0.63100000000000001</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="1"/>
-        <v>1.131</v>
+        <v>1.1259999999999999</v>
       </c>
       <c r="V11" s="6">
         <f t="shared" si="2"/>
-        <v>18.143999999999998</v>
+        <v>17.62</v>
       </c>
       <c r="W11" s="5">
         <f t="shared" si="3"/>
-        <v>2.8239999999999998</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" si="4"/>
-        <v>30.297000000000001</v>
+        <v>30.169</v>
       </c>
       <c r="Y11" s="8">
         <f t="shared" si="5"/>
-        <v>15.805999999999999</v>
+        <v>15.244999999999999</v>
       </c>
       <c r="Z11" s="8">
         <f t="shared" si="6"/>
-        <v>5.9</v>
+        <v>5.9470000000000001</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="7"/>
-        <v>14.993</v>
+        <v>14.742000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1726,95 +1726,95 @@
       </c>
       <c r="B12" s="2">
         <f t="shared" si="10"/>
-        <v>2.9416849816849813</v>
+        <v>2.9690721649484533</v>
       </c>
       <c r="C12" s="2">
         <f t="shared" si="11"/>
-        <v>1.081978021978022</v>
+        <v>1.0925560946027895</v>
       </c>
       <c r="D12" s="6">
         <f t="shared" si="8"/>
-        <v>136.5</v>
+        <v>131.92000000000002</v>
       </c>
       <c r="E12" s="5">
-        <v>217.24</v>
+        <v>209.07</v>
       </c>
       <c r="F12" s="8">
-        <v>45.28</v>
+        <v>43.17</v>
       </c>
       <c r="G12" s="1">
-        <v>90.1</v>
+        <v>87.7</v>
       </c>
       <c r="H12" s="8">
-        <v>1.1200000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="I12" s="3">
-        <v>73.63</v>
+        <v>71.48</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="K12" s="2">
         <f t="shared" si="12"/>
-        <v>5.5802861685214618</v>
+        <v>5.2009493670886071</v>
       </c>
       <c r="L12" s="2">
         <f t="shared" si="13"/>
-        <v>1.2941176470588236</v>
+        <v>1.2943037974683542</v>
       </c>
       <c r="M12" s="6">
         <f t="shared" si="9"/>
-        <v>6.29</v>
+        <v>6.32</v>
       </c>
       <c r="N12" s="5">
-        <v>75.3</v>
+        <v>73.63</v>
       </c>
       <c r="O12" s="8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P12" s="1">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="Q12" s="8">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="R12" s="3">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="S12" s="16" t="s">
         <v>10</v>
       </c>
       <c r="T12" s="2">
         <f t="shared" si="0"/>
-        <v>0.52700000000000002</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="U12" s="2">
         <f t="shared" si="1"/>
-        <v>0.83599999999999997</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="V12" s="6">
         <f t="shared" si="2"/>
-        <v>21.701000000000001</v>
+        <v>20.873000000000001</v>
       </c>
       <c r="W12" s="5">
         <f t="shared" si="3"/>
-        <v>2.8849999999999998</v>
+        <v>2.839</v>
       </c>
       <c r="X12" s="8">
         <f t="shared" si="4"/>
-        <v>35.654000000000003</v>
+        <v>33.207999999999998</v>
       </c>
       <c r="Y12" s="1">
         <f t="shared" si="5"/>
-        <v>18.693000000000001</v>
+        <v>18.157</v>
       </c>
       <c r="Z12" s="8">
         <f t="shared" si="6"/>
-        <v>5.6</v>
+        <v>5.5259999999999998</v>
       </c>
       <c r="AA12" s="3">
         <f t="shared" si="7"/>
-        <v>18.18</v>
+        <v>17.693000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1823,95 +1823,95 @@
       </c>
       <c r="B13" s="2">
         <f t="shared" ref="B13:B14" si="14">D$2/D13</f>
-        <v>3.4176525661758448</v>
+        <v>3.3684210526315788</v>
       </c>
       <c r="C13" s="2">
         <f t="shared" ref="C13:C14" si="15">D12/D13</f>
-        <v>1.1618010043407949</v>
+        <v>1.1345029239766082</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="8"/>
-        <v>117.49</v>
+        <v>116.28</v>
       </c>
       <c r="E13" s="5">
-        <v>217.95</v>
+        <v>221.39</v>
       </c>
       <c r="F13" s="1">
-        <v>26.86</v>
+        <v>25.59</v>
       </c>
       <c r="G13" s="8">
-        <v>89.56</v>
+        <v>89.09</v>
       </c>
       <c r="H13" s="8">
-        <v>1.07</v>
+        <v>1.6</v>
       </c>
       <c r="I13" s="7">
-        <v>73.39</v>
+        <v>71.73</v>
       </c>
       <c r="J13" s="17" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" ref="K13:K14" si="16">M$2/M13</f>
-        <v>5.8892617449664417</v>
+        <v>5.6188034188034184</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" ref="L13:L14" si="17">M12/M13</f>
-        <v>1.0553691275167785</v>
+        <v>1.0803418803418805</v>
       </c>
       <c r="M13" s="6">
         <f t="shared" si="9"/>
-        <v>5.96</v>
+        <v>5.85</v>
       </c>
       <c r="N13" s="5">
-        <v>75.64</v>
+        <v>75.28</v>
       </c>
       <c r="O13" s="1">
         <v>0.89</v>
       </c>
       <c r="P13" s="8">
-        <v>4.87</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q13" s="8">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="R13" s="7">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="S13" s="17" t="s">
         <v>22</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="0"/>
-        <v>0.57999999999999996</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="1"/>
-        <v>1.101</v>
+        <v>1.05</v>
       </c>
       <c r="V13" s="6">
         <f t="shared" si="2"/>
-        <v>19.713000000000001</v>
+        <v>19.876999999999999</v>
       </c>
       <c r="W13" s="5">
         <f t="shared" si="3"/>
-        <v>2.8809999999999998</v>
+        <v>2.9409999999999998</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" si="4"/>
-        <v>30.18</v>
+        <v>28.753</v>
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="5"/>
-        <v>18.39</v>
+        <v>18.677</v>
       </c>
       <c r="Z13" s="8">
         <f t="shared" si="6"/>
-        <v>5.35</v>
+        <v>8.4209999999999994</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="7"/>
-        <v>17.988</v>
+        <v>17.933</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1920,95 +1920,95 @@
       </c>
       <c r="B14" s="5">
         <f t="shared" si="14"/>
-        <v>3.4684287812041115</v>
+        <v>3.3888215954317356</v>
       </c>
       <c r="C14" s="5">
         <f t="shared" si="15"/>
-        <v>1.0148570441392415</v>
+        <v>1.0060564111437966</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="8"/>
-        <v>115.77</v>
+        <v>115.58</v>
       </c>
       <c r="E14" s="5">
-        <v>217.66</v>
+        <v>210.13</v>
       </c>
       <c r="F14" s="1">
-        <v>25.05</v>
+        <v>25.46</v>
       </c>
       <c r="G14" s="8">
-        <v>89.65</v>
+        <v>89.08</v>
       </c>
       <c r="H14" s="8">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="I14" s="7">
-        <v>73.08</v>
+        <v>72.56</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" si="16"/>
-        <v>5.9795570698466767</v>
+        <v>5.7165217391304344</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="17"/>
-        <v>1.0153321976149914</v>
+        <v>1.017391304347826</v>
       </c>
       <c r="M14" s="4">
         <f t="shared" si="9"/>
-        <v>5.87</v>
+        <v>5.75</v>
       </c>
       <c r="N14" s="5">
-        <v>76.8</v>
+        <v>73.13</v>
       </c>
       <c r="O14" s="1">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="P14" s="8">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="Q14" s="8">
         <v>0.19</v>
       </c>
       <c r="R14" s="7">
-        <v>4.0199999999999996</v>
+        <v>3.94</v>
       </c>
       <c r="S14" s="18" t="s">
         <v>23</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" si="0"/>
-        <v>0.57999999999999996</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="2"/>
-        <v>19.722000000000001</v>
+        <v>20.100999999999999</v>
       </c>
       <c r="W14" s="5">
         <f t="shared" si="3"/>
-        <v>2.8340000000000001</v>
+        <v>2.8730000000000002</v>
       </c>
       <c r="X14" s="1">
         <f t="shared" si="4"/>
-        <v>29.471</v>
+        <v>30.31</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="5"/>
-        <v>18.561</v>
+        <v>18.873000000000001</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="6"/>
-        <v>5.6319999999999997</v>
+        <v>5.4740000000000002</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="7"/>
-        <v>18.178999999999998</v>
+        <v>18.416</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2017,95 +2017,95 @@
       </c>
       <c r="B15" s="2">
         <f t="shared" ref="B15" si="18">D$2/D15</f>
-        <v>4.1468553134359185</v>
+        <v>4.0077765271666834</v>
       </c>
       <c r="C15" s="2">
         <f t="shared" ref="C15" si="19">D14/D15</f>
-        <v>1.1956005370236498</v>
+        <v>1.1826460656911899</v>
       </c>
       <c r="D15" s="6">
         <f>SUM(F15:H15)</f>
-        <v>96.83</v>
+        <v>97.73</v>
       </c>
       <c r="E15" s="5">
-        <v>218.71</v>
+        <v>209.57</v>
       </c>
       <c r="F15" s="8">
-        <v>25.46</v>
+        <v>26.2</v>
       </c>
       <c r="G15" s="1">
-        <v>70.33</v>
+        <v>70.55</v>
       </c>
       <c r="H15" s="8">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="I15" s="3">
-        <v>50.34</v>
+        <v>50.26</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15" si="20">M$2/M15</f>
-        <v>6.5730337078651662</v>
+        <v>6.0422794117647047</v>
       </c>
       <c r="L15" s="2">
         <f t="shared" ref="L15" si="21">M14/M15</f>
-        <v>1.0992509363295879</v>
+        <v>1.056985294117647</v>
       </c>
       <c r="M15" s="6">
         <f t="shared" si="9"/>
-        <v>5.3400000000000007</v>
+        <v>5.44</v>
       </c>
       <c r="N15" s="5">
-        <v>77.02</v>
+        <v>75.37</v>
       </c>
       <c r="O15" s="8">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="P15" s="1">
-        <v>4.29</v>
+        <v>4.37</v>
       </c>
       <c r="Q15" s="8">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="R15" s="3">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="S15" s="18" t="s">
         <v>25</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="0"/>
-        <v>0.63100000000000001</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="1"/>
-        <v>1.0880000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="V15" s="6">
         <f t="shared" si="2"/>
-        <v>18.132999999999999</v>
+        <v>17.965</v>
       </c>
       <c r="W15" s="5">
-        <f>ROUND(E15/N15,3)</f>
-        <v>2.84</v>
+        <f t="shared" ref="W15:AA19" si="22">ROUND(E15/N15,3)</f>
+        <v>2.7810000000000001</v>
       </c>
       <c r="X15" s="8">
-        <f>ROUND(F15/O15,3)</f>
-        <v>29.605</v>
+        <f t="shared" si="22"/>
+        <v>30.114999999999998</v>
       </c>
       <c r="Y15" s="1">
-        <f>ROUND(G15/P15,3)</f>
-        <v>16.393999999999998</v>
+        <f t="shared" si="22"/>
+        <v>16.143999999999998</v>
       </c>
       <c r="Z15" s="8">
-        <f>ROUND(H15/Q15,3)</f>
-        <v>5.4740000000000002</v>
+        <f t="shared" si="22"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AA15" s="3">
-        <f>ROUND(I15/R15,3)</f>
-        <v>13.532</v>
+        <f t="shared" si="22"/>
+        <v>13.367000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2113,96 +2113,96 @@
         <v>27</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" ref="B16" si="22">D$2/D16</f>
-        <v>4.1753145471560771</v>
+        <f t="shared" ref="B16" si="23">D$2/D16</f>
+        <v>4.0634920634920633</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16" si="23">D15/D16</f>
-        <v>1.0068628470416969</v>
+        <f t="shared" ref="C16" si="24">D15/D16</f>
+        <v>1.0139018570391121</v>
       </c>
       <c r="D16" s="4">
         <f>SUM(F16:H16)</f>
-        <v>96.17</v>
+        <v>96.39</v>
       </c>
       <c r="E16" s="1">
-        <v>208.27</v>
+        <v>208.68</v>
       </c>
       <c r="F16" s="8">
-        <v>25.17</v>
+        <v>25.49</v>
       </c>
       <c r="G16" s="8">
-        <v>70.02</v>
+        <v>69.89</v>
       </c>
       <c r="H16" s="8">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="I16" s="7">
-        <v>50.21</v>
+        <v>49.77</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16" si="24">M$2/M16</f>
-        <v>6.6603415559772277</v>
+        <f t="shared" ref="K16" si="25">M$2/M16</f>
+        <v>6.1210428305400368</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16" si="25">M15/M16</f>
-        <v>1.013282732447818</v>
+        <f t="shared" ref="L16" si="26">M15/M16</f>
+        <v>1.0130353817504656</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="9"/>
-        <v>5.2700000000000005</v>
+        <v>5.37</v>
       </c>
       <c r="N16" s="1">
-        <v>10.5</v>
+        <v>10.34</v>
       </c>
       <c r="O16" s="8">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="P16" s="8">
-        <v>4.2300000000000004</v>
+        <v>4.37</v>
       </c>
       <c r="Q16" s="8">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="R16" s="7">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="S16" s="18" t="s">
         <v>27</v>
       </c>
       <c r="T16" s="5">
         <f t="shared" si="0"/>
-        <v>0.627</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99399999999999999</v>
+        <v>1.0009999999999999</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="2"/>
-        <v>18.248999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="W16" s="1">
-        <f>ROUND(E16/N16,3)</f>
-        <v>19.835000000000001</v>
+        <f t="shared" si="22"/>
+        <v>20.181999999999999</v>
       </c>
       <c r="X16" s="8">
-        <f>ROUND(F16/O16,3)</f>
-        <v>29.611999999999998</v>
+        <f t="shared" si="22"/>
+        <v>31.863</v>
       </c>
       <c r="Y16" s="8">
-        <f>ROUND(G16/P16,3)</f>
-        <v>16.553000000000001</v>
+        <f t="shared" si="22"/>
+        <v>15.993</v>
       </c>
       <c r="Z16" s="8">
-        <f>ROUND(H16/Q16,3)</f>
-        <v>5.1580000000000004</v>
+        <f t="shared" si="22"/>
+        <v>5.05</v>
       </c>
       <c r="AA16" s="7">
-        <f>ROUND(I16/R16,3)</f>
-        <v>13.794</v>
+        <f t="shared" si="22"/>
+        <v>13.451000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2210,58 +2210,58 @@
         <v>28</v>
       </c>
       <c r="B17" s="5">
-        <f t="shared" ref="B17" si="26">D$2/D17</f>
-        <v>4.1692451458830853</v>
+        <f t="shared" ref="B17" si="27">D$2/D17</f>
+        <v>4.0945013589797208</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17" si="27">D16/D17</f>
-        <v>0.99854636071020664</v>
+        <f t="shared" ref="C17" si="28">D16/D17</f>
+        <v>1.0076311938114155</v>
       </c>
       <c r="D17" s="4">
         <f>SUM(F17:H17)</f>
-        <v>96.31</v>
+        <v>95.659999999999982</v>
       </c>
       <c r="E17" s="19">
-        <v>204.49</v>
+        <v>205.93</v>
       </c>
       <c r="F17" s="19">
-        <v>25.01</v>
+        <v>24.74</v>
       </c>
       <c r="G17" s="14">
-        <v>70.25</v>
+        <v>69.959999999999994</v>
       </c>
       <c r="H17" s="19">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="I17" s="19">
-        <v>49.46</v>
+        <v>48.83</v>
       </c>
       <c r="J17" s="18" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" ref="K17" si="28">M$2/M17</f>
-        <v>7.7483443708609254</v>
+        <f t="shared" ref="K17" si="29">M$2/M17</f>
+        <v>7.2083333333333321</v>
       </c>
       <c r="L17" s="5">
-        <f t="shared" ref="L17" si="29">M16/M17</f>
-        <v>1.1633554083885209</v>
+        <f t="shared" ref="L17" si="30">M16/M17</f>
+        <v>1.1776315789473684</v>
       </c>
       <c r="M17" s="4">
-        <f t="shared" ref="M17" si="30">SUM(O17:Q17)</f>
-        <v>4.53</v>
+        <f t="shared" ref="M17" si="31">SUM(O17:Q17)</f>
+        <v>4.5600000000000005</v>
       </c>
       <c r="N17" s="19">
-        <v>10.039999999999999</v>
+        <v>10.66</v>
       </c>
       <c r="O17" s="19">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="P17" s="14">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" s="19">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="R17" s="19">
         <v>2.95</v>
@@ -2270,230 +2270,327 @@
         <v>28</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" ref="T17" si="31">ROUND(B17/K17,3)</f>
-        <v>0.53800000000000003</v>
+        <f t="shared" ref="T17" si="32">ROUND(B17/K17,3)</f>
+        <v>0.56799999999999995</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" ref="U17" si="32">ROUND(C17/L17,3)</f>
-        <v>0.85799999999999998</v>
+        <f t="shared" ref="U17" si="33">ROUND(C17/L17,3)</f>
+        <v>0.85599999999999998</v>
       </c>
       <c r="V17" s="4">
-        <f t="shared" ref="V17" si="33">ROUND(D17/M17,3)</f>
-        <v>21.26</v>
+        <f t="shared" ref="V17" si="34">ROUND(D17/M17,3)</f>
+        <v>20.978000000000002</v>
       </c>
       <c r="W17" s="19">
-        <f>ROUND(E17/N17,3)</f>
-        <v>20.367999999999999</v>
+        <f t="shared" si="22"/>
+        <v>19.318000000000001</v>
       </c>
       <c r="X17" s="19">
-        <f>ROUND(F17/O17,3)</f>
-        <v>31.658000000000001</v>
+        <f t="shared" si="22"/>
+        <v>30.170999999999999</v>
       </c>
       <c r="Y17" s="14">
-        <f>ROUND(G17/P17,3)</f>
-        <v>19.844999999999999</v>
+        <f t="shared" si="22"/>
+        <v>19.707000000000001</v>
       </c>
       <c r="Z17" s="19">
-        <f>ROUND(H17/Q17,3)</f>
-        <v>5.25</v>
+        <f t="shared" si="22"/>
+        <v>5.0529999999999999</v>
       </c>
       <c r="AA17" s="19">
-        <f>ROUND(I17/R17,3)</f>
-        <v>16.765999999999998</v>
+        <f t="shared" si="22"/>
+        <v>16.553000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="5">
-        <f t="shared" ref="B18" si="34">D$2/D18</f>
-        <v>4.1550082781456954</v>
+        <f t="shared" ref="B18" si="35">D$2/D18</f>
+        <v>4.0685571829230289</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18" si="35">D17/D18</f>
-        <v>0.99658526490066224</v>
+        <f t="shared" ref="C18" si="36">D17/D18</f>
+        <v>0.99366365430559866</v>
       </c>
       <c r="D18" s="4">
         <f>SUM(F18:H18)</f>
-        <v>96.64</v>
+        <v>96.27</v>
       </c>
       <c r="E18" s="19">
-        <v>203.64</v>
+        <v>204.06</v>
       </c>
       <c r="F18" s="19">
-        <v>25.53</v>
+        <v>25.06</v>
       </c>
       <c r="G18" s="14">
-        <v>70.13</v>
+        <v>70.22</v>
       </c>
       <c r="H18" s="19">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I18" s="15">
-        <v>49.91</v>
+        <v>49.89</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K18" s="5">
-        <f t="shared" ref="K18" si="36">M$2/M18</f>
-        <v>8.2009345794392523</v>
+        <f t="shared" ref="K18" si="37">M$2/M18</f>
+        <v>7.6264501160092797</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" ref="L18" si="37">M17/M18</f>
-        <v>1.0584112149532712</v>
+        <f t="shared" ref="L18" si="38">M17/M18</f>
+        <v>1.0580046403712298</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" ref="M18" si="38">SUM(O18:Q18)</f>
-        <v>4.2799999999999994</v>
+        <f t="shared" ref="M18" si="39">SUM(O18:Q18)</f>
+        <v>4.3100000000000005</v>
       </c>
       <c r="N18" s="19">
-        <v>10.11</v>
+        <v>10.47</v>
       </c>
       <c r="O18" s="19">
         <v>0.82</v>
       </c>
       <c r="P18" s="14">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Q18" s="19">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="R18" s="15">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S18" s="18" t="s">
         <v>29</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" ref="T18" si="39">ROUND(B18/K18,3)</f>
-        <v>0.50700000000000001</v>
+        <f t="shared" ref="T18" si="40">ROUND(B18/K18,3)</f>
+        <v>0.53300000000000003</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" ref="U18" si="40">ROUND(C18/L18,3)</f>
-        <v>0.94199999999999995</v>
+        <f t="shared" ref="U18" si="41">ROUND(C18/L18,3)</f>
+        <v>0.93899999999999995</v>
       </c>
       <c r="V18" s="4">
-        <f t="shared" ref="V18" si="41">ROUND(D18/M18,3)</f>
-        <v>22.579000000000001</v>
+        <f t="shared" ref="V18" si="42">ROUND(D18/M18,3)</f>
+        <v>22.335999999999999</v>
       </c>
       <c r="W18" s="19">
-        <f>ROUND(E18/N18,3)</f>
-        <v>20.141999999999999</v>
+        <f t="shared" si="22"/>
+        <v>19.489999999999998</v>
       </c>
       <c r="X18" s="19">
-        <f>ROUND(F18/O18,3)</f>
-        <v>31.134</v>
+        <f t="shared" si="22"/>
+        <v>30.561</v>
       </c>
       <c r="Y18" s="14">
-        <f>ROUND(G18/P18,3)</f>
-        <v>21.381</v>
+        <f t="shared" si="22"/>
+        <v>21.279</v>
       </c>
       <c r="Z18" s="19">
-        <f>ROUND(H18/Q18,3)</f>
-        <v>5.444</v>
+        <f t="shared" si="22"/>
+        <v>5.2110000000000003</v>
       </c>
       <c r="AA18" s="15">
-        <f>ROUND(I18/R18,3)</f>
-        <v>19.05</v>
+        <f t="shared" si="22"/>
+        <v>18.97</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="5">
-        <f t="shared" ref="B19" si="42">D$2/D19</f>
-        <v>4.3316073354908298</v>
+        <f t="shared" ref="B19" si="43">D$2/D19</f>
+        <v>4.184615384615384</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19" si="43">D18/D19</f>
-        <v>1.0425026968716289</v>
+        <f t="shared" ref="C19" si="44">D18/D19</f>
+        <v>1.0285256410256409</v>
       </c>
       <c r="D19" s="4">
         <f>SUM(F19:H19)</f>
-        <v>92.7</v>
+        <v>93.600000000000009</v>
       </c>
       <c r="E19" s="9">
-        <v>208.8</v>
+        <v>210.23</v>
       </c>
       <c r="F19" s="9">
-        <v>25.04</v>
+        <v>26.34</v>
       </c>
       <c r="G19" s="14">
-        <v>66.61</v>
+        <v>66.260000000000005</v>
       </c>
       <c r="H19" s="9">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="I19" s="10">
-        <v>49.6</v>
+        <v>50.19</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K19" s="5">
-        <f t="shared" ref="K19" si="44">M$2/M19</f>
-        <v>8.9999999999999982</v>
+        <f t="shared" ref="K19" si="45">M$2/M19</f>
+        <v>8.3426395939086291</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" ref="L19" si="45">M18/M19</f>
-        <v>1.0974358974358973</v>
+        <f t="shared" ref="L19" si="46">M18/M19</f>
+        <v>1.0939086294416245</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" ref="M19" si="46">SUM(O19:Q19)</f>
-        <v>3.9</v>
+        <f t="shared" ref="M19" si="47">SUM(O19:Q19)</f>
+        <v>3.94</v>
       </c>
       <c r="N19" s="9">
-        <v>10.81</v>
+        <v>10.27</v>
       </c>
       <c r="O19" s="9">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="P19" s="14">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="Q19" s="9">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="R19" s="10">
         <v>2.5</v>
       </c>
       <c r="S19" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T19" s="5">
-        <f t="shared" ref="T19" si="47">ROUND(B19/K19,3)</f>
-        <v>0.48099999999999998</v>
+        <f t="shared" ref="T19" si="48">ROUND(B19/K19,3)</f>
+        <v>0.502</v>
       </c>
       <c r="U19" s="5">
-        <f t="shared" ref="U19" si="48">ROUND(C19/L19,3)</f>
-        <v>0.95</v>
+        <f t="shared" ref="U19" si="49">ROUND(C19/L19,3)</f>
+        <v>0.94</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" ref="V19" si="49">ROUND(D19/M19,3)</f>
-        <v>23.768999999999998</v>
+        <f t="shared" ref="V19" si="50">ROUND(D19/M19,3)</f>
+        <v>23.756</v>
       </c>
       <c r="W19" s="19">
-        <f>ROUND(E19/N19,3)</f>
-        <v>19.315000000000001</v>
+        <f t="shared" si="22"/>
+        <v>20.47</v>
       </c>
       <c r="X19" s="19">
-        <f>ROUND(F19/O19,3)</f>
-        <v>29.459</v>
+        <f t="shared" si="22"/>
+        <v>31.356999999999999</v>
       </c>
       <c r="Y19" s="14">
-        <f>ROUND(G19/P19,3)</f>
-        <v>23.29</v>
+        <f t="shared" si="22"/>
+        <v>22.692</v>
       </c>
       <c r="Z19" s="19">
-        <f>ROUND(H19/Q19,3)</f>
-        <v>5.5259999999999998</v>
+        <f t="shared" si="22"/>
+        <v>5.556</v>
       </c>
       <c r="AA19" s="20">
-        <f>ROUND(I19/R19,3)</f>
-        <v>19.84</v>
+        <f t="shared" si="22"/>
+        <v>20.076000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="5">
+        <f t="shared" ref="B20" si="51">D$2/D20</f>
+        <v>4.8278072229754709</v>
+      </c>
+      <c r="C20" s="5">
+        <f t="shared" ref="C20" si="52">D19/D20</f>
+        <v>1.15370393196105</v>
+      </c>
+      <c r="D20" s="4">
+        <f>SUM(F20:H20)</f>
+        <v>81.13000000000001</v>
+      </c>
+      <c r="E20" s="9">
+        <v>208.06</v>
+      </c>
+      <c r="F20" s="9">
+        <v>24.71</v>
+      </c>
+      <c r="G20" s="14">
+        <v>55.38</v>
+      </c>
+      <c r="H20" s="9">
+        <v>1.04</v>
+      </c>
+      <c r="I20" s="15">
+        <v>42.98</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" ref="K20" si="53">M$2/M20</f>
+        <v>8.2795969773299749</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" ref="L20" si="54">M19/M20</f>
+        <v>0.9924433249370278</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" ref="M20" si="55">SUM(O20:Q20)</f>
+        <v>3.9699999999999998</v>
+      </c>
+      <c r="N20" s="9">
+        <v>10.65</v>
+      </c>
+      <c r="O20" s="9">
+        <v>0.88</v>
+      </c>
+      <c r="P20" s="14">
+        <v>2.9</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="R20" s="15">
+        <v>2.52</v>
+      </c>
+      <c r="S20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" ref="T20" si="56">ROUND(B20/K20,3)</f>
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="U20" s="5">
+        <f t="shared" ref="U20" si="57">ROUND(C20/L20,3)</f>
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="V20" s="4">
+        <f t="shared" ref="V20" si="58">ROUND(D20/M20,3)</f>
+        <v>20.436</v>
+      </c>
+      <c r="W20" s="19">
+        <f t="shared" ref="W20" si="59">ROUND(E20/N20,3)</f>
+        <v>19.536000000000001</v>
+      </c>
+      <c r="X20" s="19">
+        <f t="shared" ref="X20" si="60">ROUND(F20/O20,3)</f>
+        <v>28.08</v>
+      </c>
+      <c r="Y20" s="14">
+        <f t="shared" ref="Y20" si="61">ROUND(G20/P20,3)</f>
+        <v>19.097000000000001</v>
+      </c>
+      <c r="Z20" s="19">
+        <f t="shared" ref="Z20" si="62">ROUND(H20/Q20,3)</f>
+        <v>5.4740000000000002</v>
+      </c>
+      <c r="AA20" s="15">
+        <f t="shared" ref="AA20" si="63">ROUND(I20/R20,3)</f>
+        <v>17.056000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA929256-E440-45E4-A04D-B012F5452188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB389FE4-2AAE-4F83-B57A-C0E931C3EA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="65">
   <si>
     <t>H23</t>
   </si>
@@ -257,6 +257,14 @@
   </si>
   <si>
     <t>H73</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H74</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H74</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -779,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB53"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5634,87 +5642,87 @@
       </c>
       <c r="B51" s="2">
         <f t="shared" ref="B51" si="360">D$2/D51</f>
-        <v>32.885546108567688</v>
+        <v>32.650649350649338</v>
       </c>
       <c r="C51" s="2">
         <f t="shared" ref="C51" si="361">D50/D51</f>
-        <v>1.143230869849575</v>
+        <v>1.1350649350649349</v>
       </c>
       <c r="D51" s="6">
         <f t="shared" ref="D51" si="362">SUM(F51:H51)</f>
-        <v>15.29</v>
+        <v>15.400000000000002</v>
       </c>
       <c r="E51" s="9">
         <v>0.65</v>
       </c>
       <c r="F51" s="9">
-        <v>7.72</v>
+        <v>7.82</v>
       </c>
       <c r="G51" s="13">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="H51" s="9">
         <v>0.64</v>
       </c>
       <c r="I51" s="14">
-        <v>4.91</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="2">
         <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
-        <v>63.196969696969681</v>
+        <v>61.338235294117631</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" ref="L51:L53" si="364">M50/M51</f>
-        <v>1.1212121212121211</v>
+        <v>1.088235294117647</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" ref="M51:M53" si="365">SUM(O51:Q51)</f>
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="N51" s="9">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O51" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P51" s="13">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="Q51" s="9">
         <v>0.03</v>
       </c>
       <c r="R51" s="14">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="T51" s="2">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
-        <v>0.52</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="U51" s="2">
         <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
-        <v>1.02</v>
+        <v>1.0429999999999999</v>
       </c>
       <c r="V51" s="6">
         <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
-        <v>23.167000000000002</v>
+        <v>22.646999999999998</v>
       </c>
       <c r="W51" s="9">
         <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
-        <v>5.4169999999999998</v>
+        <v>9.2859999999999996</v>
       </c>
       <c r="X51" s="9">
         <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
-        <v>16.425999999999998</v>
+        <v>16.292000000000002</v>
       </c>
       <c r="Y51" s="13">
         <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
-        <v>43.313000000000002</v>
+        <v>40.823999999999998</v>
       </c>
       <c r="Z51" s="9">
         <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
@@ -5722,7 +5730,7 @@
       </c>
       <c r="AA51" s="14">
         <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
-        <v>28.882000000000001</v>
+        <v>27.222000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5735,47 +5743,47 @@
       </c>
       <c r="C52" s="5">
         <f t="shared" ref="C52:C53" si="375">D51/D52</f>
-        <v>0.99999999999999989</v>
+        <v>1.0071942446043167</v>
       </c>
       <c r="D52" s="4">
         <f t="shared" ref="D52:D53" si="376">SUM(F52:H52)</f>
         <v>15.290000000000001</v>
       </c>
       <c r="E52" s="9">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="F52" s="9">
         <v>7.69</v>
       </c>
       <c r="G52" s="9">
-        <v>6.94</v>
+        <v>6.95</v>
       </c>
       <c r="H52" s="9">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I52" s="14">
-        <v>4.92</v>
+        <v>4.87</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>61</v>
       </c>
       <c r="K52" s="5">
         <f t="shared" si="363"/>
-        <v>62.253731343283569</v>
+        <v>61.338235294117631</v>
       </c>
       <c r="L52" s="5">
         <f t="shared" si="364"/>
-        <v>0.9850746268656716</v>
+        <v>1</v>
       </c>
       <c r="M52" s="4">
         <f t="shared" si="365"/>
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="N52" s="9">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O52" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P52" s="9">
         <v>0.17</v>
@@ -5791,35 +5799,35 @@
       </c>
       <c r="T52" s="5">
         <f t="shared" ref="T52:T53" si="377">ROUND(B52/K52,3)</f>
-        <v>0.52800000000000002</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="U52" s="5">
         <f t="shared" ref="U52:U53" si="378">ROUND(C52/L52,3)</f>
-        <v>1.0149999999999999</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="V52" s="4">
         <f t="shared" ref="V52:V53" si="379">ROUND(D52/M52,3)</f>
-        <v>22.821000000000002</v>
+        <v>22.484999999999999</v>
       </c>
       <c r="W52" s="18">
         <f t="shared" ref="W52:W53" si="380">ROUND(E52/N52,3)</f>
-        <v>8.1110000000000007</v>
+        <v>9.4290000000000003</v>
       </c>
       <c r="X52" s="18">
         <f t="shared" ref="X52:X53" si="381">ROUND(F52/O52,3)</f>
-        <v>16.361999999999998</v>
+        <v>16.021000000000001</v>
       </c>
       <c r="Y52" s="18">
         <f t="shared" ref="Y52:Y53" si="382">ROUND(G52/P52,3)</f>
-        <v>40.823999999999998</v>
+        <v>40.881999999999998</v>
       </c>
       <c r="Z52" s="18">
         <f t="shared" ref="Z52:Z53" si="383">ROUND(H52/Q52,3)</f>
-        <v>22</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA52" s="14">
         <f t="shared" ref="AA52:AA53" si="384">ROUND(I52/R52,3)</f>
-        <v>27.332999999999998</v>
+        <v>27.056000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5828,51 +5836,51 @@
       </c>
       <c r="B53" s="5">
         <f t="shared" si="374"/>
-        <v>33.365627073656263</v>
+        <v>33.409966777408634</v>
       </c>
       <c r="C53" s="5">
         <f t="shared" si="375"/>
-        <v>1.0145985401459854</v>
+        <v>1.0159468438538206</v>
       </c>
       <c r="D53" s="4">
         <f t="shared" si="376"/>
-        <v>15.07</v>
+        <v>15.05</v>
       </c>
       <c r="E53" s="9">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="F53" s="9">
-        <v>7.74</v>
+        <v>7.68</v>
       </c>
       <c r="G53" s="13">
-        <v>6.67</v>
+        <v>6.69</v>
       </c>
       <c r="H53" s="9">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="I53" s="14">
-        <v>4.82</v>
+        <v>4.88</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K53" s="5">
         <f t="shared" si="363"/>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L53" s="5">
         <f t="shared" si="364"/>
-        <v>1.0151515151515151</v>
+        <v>1.0461538461538462</v>
       </c>
       <c r="M53" s="4">
         <f t="shared" si="365"/>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N53" s="9">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O53" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P53" s="13">
         <v>0.15</v>
@@ -5888,35 +5896,132 @@
       </c>
       <c r="T53" s="5">
         <f t="shared" si="377"/>
-        <v>0.52800000000000002</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="378"/>
-        <v>0.999</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="V53" s="4">
         <f t="shared" si="379"/>
-        <v>22.832999999999998</v>
+        <v>23.154</v>
       </c>
       <c r="W53" s="18">
         <f t="shared" si="380"/>
-        <v>7.3330000000000002</v>
+        <v>8.8569999999999993</v>
       </c>
       <c r="X53" s="18">
         <f t="shared" si="381"/>
-        <v>16.125</v>
+        <v>16.34</v>
       </c>
       <c r="Y53" s="13">
         <f t="shared" si="382"/>
-        <v>44.466999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="Z53" s="18">
         <f t="shared" si="383"/>
-        <v>22</v>
+        <v>22.667000000000002</v>
       </c>
       <c r="AA53" s="14">
         <f t="shared" si="384"/>
-        <v>30.125</v>
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="5">
+        <f t="shared" ref="B54" si="385">D$2/D54</f>
+        <v>33.34350132625994</v>
+      </c>
+      <c r="C54" s="5">
+        <f t="shared" ref="C54" si="386">D53/D54</f>
+        <v>0.99801061007957559</v>
+      </c>
+      <c r="D54" s="4">
+        <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
+        <v>15.08</v>
+      </c>
+      <c r="E54" s="13">
+        <v>0.41</v>
+      </c>
+      <c r="F54" s="9">
+        <v>7.64</v>
+      </c>
+      <c r="G54" s="9">
+        <v>6.79</v>
+      </c>
+      <c r="H54" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="I54" s="10">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K54" s="5">
+        <f t="shared" ref="K54" si="388">M$2/M54</f>
+        <v>64.169230769230751</v>
+      </c>
+      <c r="L54" s="5">
+        <f t="shared" ref="L54" si="389">M53/M54</f>
+        <v>1</v>
+      </c>
+      <c r="M54" s="4">
+        <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
+        <v>0.65</v>
+      </c>
+      <c r="N54" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="O54" s="9">
+        <v>0.47</v>
+      </c>
+      <c r="P54" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="R54" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="S54" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="T54" s="5">
+        <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
+        <v>0.52</v>
+      </c>
+      <c r="U54" s="5">
+        <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
+        <v>0.998</v>
+      </c>
+      <c r="V54" s="4">
+        <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
+        <v>23.2</v>
+      </c>
+      <c r="W54" s="13">
+        <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
+        <v>6.8330000000000002</v>
+      </c>
+      <c r="X54" s="18">
+        <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
+        <v>16.254999999999999</v>
+      </c>
+      <c r="Y54" s="18">
+        <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
+        <v>45.267000000000003</v>
+      </c>
+      <c r="Z54" s="18">
+        <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
+        <v>21.667000000000002</v>
+      </c>
+      <c r="AA54" s="19">
+        <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
+        <v>31.8</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB389FE4-2AAE-4F83-B57A-C0E931C3EA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8322B291-9E99-4228-96FE-E8A9DEEB04C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="66">
   <si>
     <t>H23</t>
   </si>
@@ -265,6 +265,10 @@
   </si>
   <si>
     <t>H74</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H75</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -787,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB54"/>
+  <dimension ref="A1:AB55"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5642,54 +5646,54 @@
       </c>
       <c r="B51" s="2">
         <f t="shared" ref="B51" si="360">D$2/D51</f>
-        <v>32.650649350649338</v>
+        <v>33.189438943894388</v>
       </c>
       <c r="C51" s="2">
         <f t="shared" ref="C51" si="361">D50/D51</f>
-        <v>1.1350649350649349</v>
+        <v>1.1537953795379539</v>
       </c>
       <c r="D51" s="6">
         <f t="shared" ref="D51" si="362">SUM(F51:H51)</f>
-        <v>15.400000000000002</v>
+        <v>15.15</v>
       </c>
       <c r="E51" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="F51" s="9">
+        <v>7.6</v>
+      </c>
+      <c r="G51" s="13">
+        <v>6.9</v>
+      </c>
+      <c r="H51" s="9">
         <v>0.65</v>
       </c>
-      <c r="F51" s="9">
-        <v>7.82</v>
-      </c>
-      <c r="G51" s="13">
-        <v>6.94</v>
-      </c>
-      <c r="H51" s="9">
-        <v>0.64</v>
-      </c>
       <c r="I51" s="14">
-        <v>4.9000000000000004</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="2">
         <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
-        <v>61.338235294117631</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" ref="L51:L53" si="364">M50/M51</f>
-        <v>1.088235294117647</v>
+        <v>1.1212121212121211</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" ref="M51:M53" si="365">SUM(O51:Q51)</f>
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="N51" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O51" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P51" s="13">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Q51" s="9">
         <v>0.03</v>
@@ -5702,35 +5706,35 @@
       </c>
       <c r="T51" s="2">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
-        <v>0.53200000000000003</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="U51" s="2">
         <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
-        <v>1.0429999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
       <c r="V51" s="6">
         <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
-        <v>22.646999999999998</v>
+        <v>22.954999999999998</v>
       </c>
       <c r="W51" s="9">
         <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
-        <v>9.2859999999999996</v>
+        <v>9.8569999999999993</v>
       </c>
       <c r="X51" s="9">
         <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
-        <v>16.292000000000002</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="Y51" s="13">
         <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
-        <v>40.823999999999998</v>
+        <v>43.125</v>
       </c>
       <c r="Z51" s="9">
         <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA51" s="14">
         <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
-        <v>27.222000000000001</v>
+        <v>27.167000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5739,51 +5743,51 @@
       </c>
       <c r="B52" s="5">
         <f t="shared" ref="B52:B53" si="374">D$2/D52</f>
-        <v>32.885546108567688</v>
+        <v>32.79973907371167</v>
       </c>
       <c r="C52" s="5">
         <f t="shared" ref="C52:C53" si="375">D51/D52</f>
-        <v>1.0071942446043167</v>
+        <v>0.98825831702544031</v>
       </c>
       <c r="D52" s="4">
         <f t="shared" ref="D52:D53" si="376">SUM(F52:H52)</f>
-        <v>15.290000000000001</v>
+        <v>15.33</v>
       </c>
       <c r="E52" s="9">
         <v>0.66</v>
       </c>
       <c r="F52" s="9">
-        <v>7.69</v>
+        <v>7.7</v>
       </c>
       <c r="G52" s="9">
-        <v>6.95</v>
+        <v>6.97</v>
       </c>
       <c r="H52" s="9">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I52" s="14">
-        <v>4.87</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>61</v>
       </c>
       <c r="K52" s="5">
         <f t="shared" si="363"/>
-        <v>61.338235294117631</v>
+        <v>62.253731343283569</v>
       </c>
       <c r="L52" s="5">
         <f t="shared" si="364"/>
-        <v>1</v>
+        <v>0.9850746268656716</v>
       </c>
       <c r="M52" s="4">
         <f t="shared" si="365"/>
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N52" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O52" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P52" s="9">
         <v>0.17</v>
@@ -5792,22 +5796,22 @@
         <v>0.03</v>
       </c>
       <c r="R52" s="14">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="S52" s="12" t="s">
         <v>61</v>
       </c>
       <c r="T52" s="5">
         <f t="shared" ref="T52:T53" si="377">ROUND(B52/K52,3)</f>
-        <v>0.53600000000000003</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="U52" s="5">
         <f t="shared" ref="U52:U53" si="378">ROUND(C52/L52,3)</f>
-        <v>1.0069999999999999</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="V52" s="4">
         <f t="shared" ref="V52:V53" si="379">ROUND(D52/M52,3)</f>
-        <v>22.484999999999999</v>
+        <v>22.881</v>
       </c>
       <c r="W52" s="18">
         <f t="shared" ref="W52:W53" si="380">ROUND(E52/N52,3)</f>
@@ -5815,19 +5819,19 @@
       </c>
       <c r="X52" s="18">
         <f t="shared" ref="X52:X53" si="381">ROUND(F52/O52,3)</f>
-        <v>16.021000000000001</v>
+        <v>16.382999999999999</v>
       </c>
       <c r="Y52" s="18">
         <f t="shared" ref="Y52:Y53" si="382">ROUND(G52/P52,3)</f>
-        <v>40.881999999999998</v>
+        <v>41</v>
       </c>
       <c r="Z52" s="18">
         <f t="shared" ref="Z52:Z53" si="383">ROUND(H52/Q52,3)</f>
-        <v>21.667000000000002</v>
+        <v>22</v>
       </c>
       <c r="AA52" s="14">
         <f t="shared" ref="AA52:AA53" si="384">ROUND(I52/R52,3)</f>
-        <v>27.056000000000001</v>
+        <v>28.824000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5836,51 +5840,51 @@
       </c>
       <c r="B53" s="5">
         <f t="shared" si="374"/>
-        <v>33.409966777408634</v>
+        <v>33.255291005290999</v>
       </c>
       <c r="C53" s="5">
         <f t="shared" si="375"/>
-        <v>1.0159468438538206</v>
+        <v>1.0138888888888888</v>
       </c>
       <c r="D53" s="4">
         <f t="shared" si="376"/>
-        <v>15.05</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E53" s="9">
         <v>0.62</v>
       </c>
       <c r="F53" s="9">
-        <v>7.68</v>
+        <v>7.77</v>
       </c>
       <c r="G53" s="13">
         <v>6.69</v>
       </c>
       <c r="H53" s="9">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="I53" s="14">
-        <v>4.88</v>
+        <v>4.91</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K53" s="5">
         <f t="shared" si="363"/>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L53" s="5">
         <f t="shared" si="364"/>
-        <v>1.0461538461538462</v>
+        <v>1.0151515151515151</v>
       </c>
       <c r="M53" s="4">
         <f t="shared" si="365"/>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N53" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O53" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P53" s="13">
         <v>0.15</v>
@@ -5896,15 +5900,15 @@
       </c>
       <c r="T53" s="5">
         <f t="shared" si="377"/>
-        <v>0.52100000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="378"/>
-        <v>0.97099999999999997</v>
+        <v>0.999</v>
       </c>
       <c r="V53" s="4">
         <f t="shared" si="379"/>
-        <v>23.154</v>
+        <v>22.908999999999999</v>
       </c>
       <c r="W53" s="18">
         <f t="shared" si="380"/>
@@ -5912,7 +5916,7 @@
       </c>
       <c r="X53" s="18">
         <f t="shared" si="381"/>
-        <v>16.34</v>
+        <v>16.187999999999999</v>
       </c>
       <c r="Y53" s="13">
         <f t="shared" si="382"/>
@@ -5920,11 +5924,11 @@
       </c>
       <c r="Z53" s="18">
         <f t="shared" si="383"/>
-        <v>22.667000000000002</v>
+        <v>22</v>
       </c>
       <c r="AA53" s="14">
         <f t="shared" si="384"/>
-        <v>30.5</v>
+        <v>30.687999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5933,30 +5937,30 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.34350132625994</v>
+        <v>33.499000666222507</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>0.99801061007957559</v>
+        <v>1.0073284477015323</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.08</v>
+        <v>15.010000000000002</v>
       </c>
       <c r="E54" s="13">
         <v>0.41</v>
       </c>
       <c r="F54" s="9">
-        <v>7.64</v>
+        <v>7.59</v>
       </c>
       <c r="G54" s="9">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
       <c r="H54" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I54" s="10">
-        <v>4.7699999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>64</v>
@@ -5967,7 +5971,7 @@
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>1</v>
+        <v>1.0153846153846153</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
@@ -5993,15 +5997,15 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>0.998</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.2</v>
+        <v>23.091999999999999</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
@@ -6009,19 +6013,116 @@
       </c>
       <c r="X54" s="18">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.254999999999999</v>
+        <v>16.149000000000001</v>
       </c>
       <c r="Y54" s="18">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.267000000000003</v>
+        <v>45.2</v>
       </c>
       <c r="Z54" s="18">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA54" s="19">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.8</v>
+        <v>31.332999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="2">
+        <f t="shared" ref="B55" si="399">D$2/D55</f>
+        <v>46.730483271375462</v>
+      </c>
+      <c r="C55" s="2">
+        <f t="shared" ref="C55" si="400">D54/D55</f>
+        <v>1.3949814126394053</v>
+      </c>
+      <c r="D55" s="6">
+        <f t="shared" ref="D55" si="401">SUM(F55:H55)</f>
+        <v>10.76</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="F55" s="9">
+        <v>7.22</v>
+      </c>
+      <c r="G55" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="H55" s="13">
+        <v>0.24</v>
+      </c>
+      <c r="I55" s="14">
+        <v>2.73</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K55" s="2">
+        <f t="shared" ref="K55" si="402">M$2/M55</f>
+        <v>64.169230769230751</v>
+      </c>
+      <c r="L55" s="2">
+        <f t="shared" ref="L55" si="403">M54/M55</f>
+        <v>1</v>
+      </c>
+      <c r="M55" s="6">
+        <f t="shared" ref="M55" si="404">SUM(O55:Q55)</f>
+        <v>0.65</v>
+      </c>
+      <c r="N55" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O55" s="9">
+        <v>0.47</v>
+      </c>
+      <c r="P55" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="Q55" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="R55" s="14">
+        <v>0.15</v>
+      </c>
+      <c r="S55" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="T55" s="2">
+        <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="U55" s="2">
+        <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
+        <v>1.395</v>
+      </c>
+      <c r="V55" s="6">
+        <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
+        <v>16.553999999999998</v>
+      </c>
+      <c r="W55" s="9">
+        <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
+        <v>6.2859999999999996</v>
+      </c>
+      <c r="X55" s="9">
+        <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
+        <v>15.362</v>
+      </c>
+      <c r="Y55" s="9">
+        <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
+        <v>22</v>
+      </c>
+      <c r="Z55" s="13">
+        <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
+        <v>8</v>
+      </c>
+      <c r="AA55" s="14">
+        <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8322B291-9E99-4228-96FE-E8A9DEEB04C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1240B072-743A-4B43-A142-B2ED70C86018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="67">
   <si>
     <t>H23</t>
   </si>
@@ -269,6 +269,10 @@
   </si>
   <si>
     <t>H75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H76</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -791,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB55"/>
+  <dimension ref="A1:AB56"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5446,7 +5450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>58</v>
       </c>
@@ -5543,7 +5547,7 @@
         <v>29.167000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>59</v>
       </c>
@@ -5640,127 +5644,127 @@
         <v>28.957999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B51" s="2">
         <f t="shared" ref="B51" si="360">D$2/D51</f>
-        <v>33.189438943894388</v>
+        <v>33.167546174142473</v>
       </c>
       <c r="C51" s="2">
         <f t="shared" ref="C51" si="361">D50/D51</f>
-        <v>1.1537953795379539</v>
+        <v>1.1530343007915567</v>
       </c>
       <c r="D51" s="6">
         <f t="shared" ref="D51" si="362">SUM(F51:H51)</f>
-        <v>15.15</v>
+        <v>15.16</v>
       </c>
       <c r="E51" s="9">
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="F51" s="9">
-        <v>7.6</v>
+        <v>7.63</v>
       </c>
       <c r="G51" s="13">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="H51" s="9">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I51" s="14">
-        <v>4.8899999999999997</v>
+        <v>4.87</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="2">
         <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
-        <v>63.196969696969681</v>
+        <v>61.338235294117631</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" ref="L51:L53" si="364">M50/M51</f>
-        <v>1.1212121212121211</v>
+        <v>1.088235294117647</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" ref="M51:M53" si="365">SUM(O51:Q51)</f>
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="N51" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O51" s="9">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="P51" s="13">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="Q51" s="9">
         <v>0.03</v>
       </c>
       <c r="R51" s="14">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="T51" s="2">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
-        <v>0.52500000000000002</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="U51" s="2">
         <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
-        <v>1.0289999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="V51" s="6">
         <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
-        <v>22.954999999999998</v>
+        <v>22.294</v>
       </c>
       <c r="W51" s="9">
         <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
-        <v>9.8569999999999993</v>
+        <v>9.2859999999999996</v>
       </c>
       <c r="X51" s="9">
         <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
-        <v>16.170000000000002</v>
+        <v>15.896000000000001</v>
       </c>
       <c r="Y51" s="13">
         <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
-        <v>43.125</v>
+        <v>40.529000000000003</v>
       </c>
       <c r="Z51" s="9">
         <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
-        <v>21.667000000000002</v>
+        <v>21.332999999999998</v>
       </c>
       <c r="AA51" s="14">
         <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
-        <v>27.167000000000002</v>
+        <v>28.646999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B52" s="5">
         <f t="shared" ref="B52:B53" si="374">D$2/D52</f>
-        <v>32.79973907371167</v>
+        <v>33.080263157894734</v>
       </c>
       <c r="C52" s="5">
         <f t="shared" ref="C52:C53" si="375">D51/D52</f>
-        <v>0.98825831702544031</v>
+        <v>0.99736842105263168</v>
       </c>
       <c r="D52" s="4">
         <f t="shared" ref="D52:D53" si="376">SUM(F52:H52)</f>
-        <v>15.33</v>
+        <v>15.2</v>
       </c>
       <c r="E52" s="9">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="F52" s="9">
-        <v>7.7</v>
+        <v>7.63</v>
       </c>
       <c r="G52" s="9">
-        <v>6.97</v>
+        <v>6.91</v>
       </c>
       <c r="H52" s="9">
         <v>0.66</v>
@@ -5773,21 +5777,21 @@
       </c>
       <c r="K52" s="5">
         <f t="shared" si="363"/>
-        <v>62.253731343283569</v>
+        <v>60.449275362318829</v>
       </c>
       <c r="L52" s="5">
         <f t="shared" si="364"/>
-        <v>0.9850746268656716</v>
+        <v>0.98550724637681153</v>
       </c>
       <c r="M52" s="4">
         <f t="shared" si="365"/>
-        <v>0.67</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="N52" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O52" s="9">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="P52" s="9">
         <v>0.17</v>
@@ -5803,27 +5807,27 @@
       </c>
       <c r="T52" s="5">
         <f t="shared" ref="T52:T53" si="377">ROUND(B52/K52,3)</f>
-        <v>0.52700000000000002</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="U52" s="5">
         <f t="shared" ref="U52:U53" si="378">ROUND(C52/L52,3)</f>
-        <v>1.0029999999999999</v>
+        <v>1.012</v>
       </c>
       <c r="V52" s="4">
         <f t="shared" ref="V52:V53" si="379">ROUND(D52/M52,3)</f>
-        <v>22.881</v>
+        <v>22.029</v>
       </c>
       <c r="W52" s="18">
         <f t="shared" ref="W52:W53" si="380">ROUND(E52/N52,3)</f>
-        <v>9.4290000000000003</v>
+        <v>8.8569999999999993</v>
       </c>
       <c r="X52" s="18">
         <f t="shared" ref="X52:X53" si="381">ROUND(F52/O52,3)</f>
-        <v>16.382999999999999</v>
+        <v>15.571</v>
       </c>
       <c r="Y52" s="18">
         <f t="shared" ref="Y52:Y53" si="382">ROUND(G52/P52,3)</f>
-        <v>41</v>
+        <v>40.646999999999998</v>
       </c>
       <c r="Z52" s="18">
         <f t="shared" ref="Z52:Z53" si="383">ROUND(H52/Q52,3)</f>
@@ -5834,57 +5838,57 @@
         <v>28.824000000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>62</v>
       </c>
       <c r="B53" s="5">
         <f t="shared" si="374"/>
-        <v>33.255291005290999</v>
+        <v>33.566088117489983</v>
       </c>
       <c r="C53" s="5">
         <f t="shared" si="375"/>
-        <v>1.0138888888888888</v>
+        <v>1.0146862483311081</v>
       </c>
       <c r="D53" s="4">
         <f t="shared" si="376"/>
-        <v>15.120000000000001</v>
+        <v>14.98</v>
       </c>
       <c r="E53" s="9">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="F53" s="9">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="G53" s="13">
-        <v>6.69</v>
+        <v>6.62</v>
       </c>
       <c r="H53" s="9">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="I53" s="14">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>62</v>
       </c>
       <c r="K53" s="5">
         <f t="shared" si="363"/>
-        <v>63.196969696969681</v>
+        <v>64.169230769230751</v>
       </c>
       <c r="L53" s="5">
         <f t="shared" si="364"/>
-        <v>1.0151515151515151</v>
+        <v>1.0615384615384615</v>
       </c>
       <c r="M53" s="4">
         <f t="shared" si="365"/>
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N53" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O53" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P53" s="13">
         <v>0.15</v>
@@ -5900,67 +5904,67 @@
       </c>
       <c r="T53" s="5">
         <f t="shared" si="377"/>
-        <v>0.52600000000000002</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="378"/>
-        <v>0.999</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="V53" s="4">
         <f t="shared" si="379"/>
-        <v>22.908999999999999</v>
+        <v>23.045999999999999</v>
       </c>
       <c r="W53" s="18">
         <f t="shared" si="380"/>
-        <v>8.8569999999999993</v>
+        <v>9.2859999999999996</v>
       </c>
       <c r="X53" s="18">
         <f t="shared" si="381"/>
-        <v>16.187999999999999</v>
+        <v>16.404</v>
       </c>
       <c r="Y53" s="13">
         <f t="shared" si="382"/>
-        <v>44.6</v>
+        <v>44.133000000000003</v>
       </c>
       <c r="Z53" s="18">
         <f t="shared" si="383"/>
-        <v>22</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA53" s="14">
         <f t="shared" si="384"/>
-        <v>30.687999999999999</v>
+        <v>30.437999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.499000666222507</v>
+        <v>33.723675385647205</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.0073284477015323</v>
+        <v>1.004694835680751</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>15.010000000000002</v>
+        <v>14.910000000000002</v>
       </c>
       <c r="E54" s="13">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.59</v>
+        <v>7.53</v>
       </c>
       <c r="G54" s="9">
-        <v>6.78</v>
+        <v>6.73</v>
       </c>
       <c r="H54" s="9">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I54" s="10">
-        <v>4.7</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>64</v>
@@ -5971,7 +5975,7 @@
       </c>
       <c r="L54" s="5">
         <f t="shared" ref="L54" si="389">M53/M54</f>
-        <v>1.0153846153846153</v>
+        <v>1</v>
       </c>
       <c r="M54" s="4">
         <f t="shared" ref="M54" si="390">SUM(O54:Q54)</f>
@@ -5997,60 +6001,60 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52200000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>0.99199999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>23.091999999999999</v>
+        <v>22.937999999999999</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
-        <v>6.8330000000000002</v>
+        <v>6.6669999999999998</v>
       </c>
       <c r="X54" s="18">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.149000000000001</v>
+        <v>16.021000000000001</v>
       </c>
       <c r="Y54" s="18">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>45.2</v>
+        <v>44.866999999999997</v>
       </c>
       <c r="Z54" s="18">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA54" s="19">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31.332999999999998</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B55" s="2">
-        <f t="shared" ref="B55" si="399">D$2/D55</f>
-        <v>46.730483271375462</v>
+        <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
+        <v>46.90485074626865</v>
       </c>
       <c r="C55" s="2">
-        <f t="shared" ref="C55" si="400">D54/D55</f>
-        <v>1.3949814126394053</v>
+        <f t="shared" ref="C55:C56" si="400">D54/D55</f>
+        <v>1.3908582089552239</v>
       </c>
       <c r="D55" s="6">
-        <f t="shared" ref="D55" si="401">SUM(F55:H55)</f>
-        <v>10.76</v>
+        <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
+        <v>10.72</v>
       </c>
       <c r="E55" s="9">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="F55" s="9">
-        <v>7.22</v>
-      </c>
-      <c r="G55" s="9">
+        <v>7.18</v>
+      </c>
+      <c r="G55" s="13">
         <v>3.3</v>
       </c>
       <c r="H55" s="13">
@@ -6063,24 +6067,24 @@
         <v>65</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" ref="K55" si="402">M$2/M55</f>
+        <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
         <v>64.169230769230751</v>
       </c>
       <c r="L55" s="2">
-        <f t="shared" ref="L55" si="403">M54/M55</f>
+        <f t="shared" ref="L55:L56" si="403">M54/M55</f>
         <v>1</v>
       </c>
       <c r="M55" s="6">
-        <f t="shared" ref="M55" si="404">SUM(O55:Q55)</f>
+        <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
         <v>0.65</v>
       </c>
       <c r="N55" s="9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O55" s="9">
         <v>0.47</v>
       </c>
-      <c r="P55" s="9">
+      <c r="P55" s="13">
         <v>0.15</v>
       </c>
       <c r="Q55" s="13">
@@ -6094,25 +6098,25 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.72799999999999998</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.395</v>
+        <v>1.391</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.553999999999998</v>
+        <v>16.492000000000001</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>6.2859999999999996</v>
+        <v>4.875</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.362</v>
-      </c>
-      <c r="Y55" s="9">
+        <v>15.276999999999999</v>
+      </c>
+      <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
         <v>22</v>
       </c>
@@ -6124,6 +6128,104 @@
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
         <v>18.2</v>
       </c>
+    </row>
+    <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="5">
+        <f t="shared" si="399"/>
+        <v>46.385608856088552</v>
+      </c>
+      <c r="C56" s="5">
+        <f t="shared" si="400"/>
+        <v>0.98892988929889303</v>
+      </c>
+      <c r="D56" s="4">
+        <f t="shared" si="401"/>
+        <v>10.84</v>
+      </c>
+      <c r="E56" s="13">
+        <v>0.39</v>
+      </c>
+      <c r="F56" s="18">
+        <v>7.3</v>
+      </c>
+      <c r="G56" s="18">
+        <v>3.31</v>
+      </c>
+      <c r="H56" s="13">
+        <v>0.23</v>
+      </c>
+      <c r="I56" s="19">
+        <v>2.73</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56" s="5">
+        <f t="shared" si="402"/>
+        <v>64.169230769230751</v>
+      </c>
+      <c r="L56" s="5">
+        <f t="shared" si="403"/>
+        <v>1</v>
+      </c>
+      <c r="M56" s="4">
+        <f t="shared" si="404"/>
+        <v>0.65</v>
+      </c>
+      <c r="N56" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="O56" s="18">
+        <v>0.48</v>
+      </c>
+      <c r="P56" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="Q56" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="R56" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="S56" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="T56" s="5">
+        <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="U56" s="5">
+        <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="V56" s="4">
+        <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
+        <v>16.677</v>
+      </c>
+      <c r="W56" s="13">
+        <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
+        <v>6.5</v>
+      </c>
+      <c r="X56" s="18">
+        <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
+        <v>15.208</v>
+      </c>
+      <c r="Y56" s="18">
+        <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
+        <v>22.067</v>
+      </c>
+      <c r="Z56" s="13">
+        <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA56" s="19">
+        <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
+        <v>18.2</v>
+      </c>
+      <c r="AB56" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/all_results.xlsx
+++ b/all_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1240B072-743A-4B43-A142-B2ED70C86018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8394354F-CAEF-4198-ADCC-2B7FE7005493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7D9E62D1-CE3F-4CF7-9B1B-78C5766E129E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="69">
   <si>
     <t>H23</t>
   </si>
@@ -273,6 +273,14 @@
   </si>
   <si>
     <t>H76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H77</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H78</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -795,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76A733-9BF5-4E02-BF58-4A4E24DE2BDD}">
-  <dimension ref="A1:AB56"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.625" style="12"/>
@@ -5650,51 +5658,51 @@
       </c>
       <c r="B51" s="2">
         <f t="shared" ref="B51" si="360">D$2/D51</f>
-        <v>33.167546174142473</v>
+        <v>32.608300907911797</v>
       </c>
       <c r="C51" s="2">
         <f t="shared" ref="C51" si="361">D50/D51</f>
-        <v>1.1530343007915567</v>
+        <v>1.1335927367055771</v>
       </c>
       <c r="D51" s="6">
         <f t="shared" ref="D51" si="362">SUM(F51:H51)</f>
-        <v>15.16</v>
+        <v>15.42</v>
       </c>
       <c r="E51" s="9">
+        <v>0.66</v>
+      </c>
+      <c r="F51" s="9">
+        <v>7.76</v>
+      </c>
+      <c r="G51" s="13">
+        <v>7.01</v>
+      </c>
+      <c r="H51" s="9">
         <v>0.65</v>
       </c>
-      <c r="F51" s="9">
-        <v>7.63</v>
-      </c>
-      <c r="G51" s="13">
-        <v>6.89</v>
-      </c>
-      <c r="H51" s="9">
-        <v>0.64</v>
-      </c>
       <c r="I51" s="14">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="K51" s="2">
         <f t="shared" ref="K51:K53" si="363">M$2/M51</f>
-        <v>61.338235294117631</v>
+        <v>62.253731343283569</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" ref="L51:L53" si="364">M50/M51</f>
-        <v>1.088235294117647</v>
+        <v>1.1044776119402984</v>
       </c>
       <c r="M51" s="6">
         <f t="shared" ref="M51:M53" si="365">SUM(O51:Q51)</f>
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N51" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O51" s="9">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="P51" s="13">
         <v>0.17</v>
@@ -5703,42 +5711,42 @@
         <v>0.03</v>
       </c>
       <c r="R51" s="14">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>60</v>
       </c>
       <c r="T51" s="2">
         <f t="shared" ref="T51" si="366">ROUND(B51/K51,3)</f>
-        <v>0.54100000000000004</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="U51" s="2">
         <f t="shared" ref="U51" si="367">ROUND(C51/L51,3)</f>
-        <v>1.06</v>
+        <v>1.026</v>
       </c>
       <c r="V51" s="6">
         <f t="shared" ref="V51" si="368">ROUND(D51/M51,3)</f>
-        <v>22.294</v>
+        <v>23.015000000000001</v>
       </c>
       <c r="W51" s="9">
         <f t="shared" ref="W51" si="369">ROUND(E51/N51,3)</f>
-        <v>9.2859999999999996</v>
+        <v>9.4290000000000003</v>
       </c>
       <c r="X51" s="9">
         <f t="shared" ref="X51" si="370">ROUND(F51/O51,3)</f>
-        <v>15.896000000000001</v>
+        <v>16.510999999999999</v>
       </c>
       <c r="Y51" s="13">
         <f t="shared" ref="Y51" si="371">ROUND(G51/P51,3)</f>
-        <v>40.529000000000003</v>
+        <v>41.234999999999999</v>
       </c>
       <c r="Z51" s="9">
         <f t="shared" ref="Z51" si="372">ROUND(H51/Q51,3)</f>
-        <v>21.332999999999998</v>
+        <v>21.667000000000002</v>
       </c>
       <c r="AA51" s="14">
         <f t="shared" ref="AA51" si="373">ROUND(I51/R51,3)</f>
-        <v>28.646999999999998</v>
+        <v>27.556000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5747,51 +5755,51 @@
       </c>
       <c r="B52" s="5">
         <f t="shared" ref="B52:B53" si="374">D$2/D52</f>
-        <v>33.080263157894734</v>
+        <v>32.356499356499349</v>
       </c>
       <c r="C52" s="5">
         <f t="shared" ref="C52:C53" si="375">D51/D52</f>
-        <v>0.99736842105263168</v>
+        <v>0.99227799227799218</v>
       </c>
       <c r="D52" s="4">
         <f t="shared" ref="D52:D53" si="376">SUM(F52:H52)</f>
-        <v>15.2</v>
+        <v>15.540000000000001</v>
       </c>
       <c r="E52" s="9">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="F52" s="9">
-        <v>7.63</v>
+        <v>7.82</v>
       </c>
       <c r="G52" s="9">
-        <v>6.91</v>
+        <v>7.03</v>
       </c>
       <c r="H52" s="9">
-        <v>0.66</v>
+        <v>0.69</v>
       </c>
       <c r="I52" s="14">
-        <v>4.9000000000000004</v>
+        <v>4.97</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>61</v>
       </c>
       <c r="K52" s="5">
         <f t="shared" si="363"/>
-        <v>60.449275362318829</v>
+        <v>62.253731343283569</v>
       </c>
       <c r="L52" s="5">
         <f t="shared" si="364"/>
-        <v>0.98550724637681153</v>
+        <v>1</v>
       </c>
       <c r="M52" s="4">
         <f t="shared" si="365"/>
-        <v>0.69000000000000006</v>
+        <v>0.67</v>
       </c>
       <c r="N52" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O52" s="9">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="P52" s="9">
         <v>0.17</v>
@@ -5800,42 +5808,42 @@
         <v>0.03</v>
       </c>
       <c r="R52" s="14">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="S52" s="12" t="s">
         <v>61</v>
       </c>
       <c r="T52" s="5">
         <f t="shared" ref="T52:T53" si="377">ROUND(B52/K52,3)</f>
-        <v>0.54700000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="U52" s="5">
         <f t="shared" ref="U52:U53" si="378">ROUND(C52/L52,3)</f>
-        <v>1.012</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="V52" s="4">
         <f t="shared" ref="V52:V53" si="379">ROUND(D52/M52,3)</f>
-        <v>22.029</v>
+        <v>23.193999999999999</v>
       </c>
       <c r="W52" s="18">
         <f t="shared" ref="W52:W53" si="380">ROUND(E52/N52,3)</f>
-        <v>8.8569999999999993</v>
+        <v>9</v>
       </c>
       <c r="X52" s="18">
         <f t="shared" ref="X52:X53" si="381">ROUND(F52/O52,3)</f>
-        <v>15.571</v>
+        <v>16.638000000000002</v>
       </c>
       <c r="Y52" s="18">
         <f t="shared" ref="Y52:Y53" si="382">ROUND(G52/P52,3)</f>
-        <v>40.646999999999998</v>
+        <v>41.353000000000002</v>
       </c>
       <c r="Z52" s="18">
         <f t="shared" ref="Z52:Z53" si="383">ROUND(H52/Q52,3)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA52" s="14">
         <f t="shared" ref="AA52:AA53" si="384">ROUND(I52/R52,3)</f>
-        <v>28.824000000000002</v>
+        <v>27.611000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5844,30 +5852,30 @@
       </c>
       <c r="B53" s="5">
         <f t="shared" si="374"/>
-        <v>33.566088117489983</v>
+        <v>33.233311302048904</v>
       </c>
       <c r="C53" s="5">
         <f t="shared" si="375"/>
-        <v>1.0146862483311081</v>
+        <v>1.0270984798413747</v>
       </c>
       <c r="D53" s="4">
         <f t="shared" si="376"/>
-        <v>14.98</v>
+        <v>15.13</v>
       </c>
       <c r="E53" s="9">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="F53" s="9">
-        <v>7.71</v>
+        <v>7.78</v>
       </c>
       <c r="G53" s="13">
-        <v>6.62</v>
+        <v>6.68</v>
       </c>
       <c r="H53" s="9">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="I53" s="14">
-        <v>4.87</v>
+        <v>4.91</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>62</v>
@@ -5878,7 +5886,7 @@
       </c>
       <c r="L53" s="5">
         <f t="shared" si="364"/>
-        <v>1.0615384615384615</v>
+        <v>1.0307692307692309</v>
       </c>
       <c r="M53" s="4">
         <f t="shared" si="365"/>
@@ -5904,35 +5912,35 @@
       </c>
       <c r="T53" s="5">
         <f t="shared" si="377"/>
-        <v>0.52300000000000002</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="378"/>
-        <v>0.95599999999999996</v>
+        <v>0.996</v>
       </c>
       <c r="V53" s="4">
         <f t="shared" si="379"/>
-        <v>23.045999999999999</v>
+        <v>23.277000000000001</v>
       </c>
       <c r="W53" s="18">
         <f t="shared" si="380"/>
-        <v>9.2859999999999996</v>
+        <v>9.5709999999999997</v>
       </c>
       <c r="X53" s="18">
         <f t="shared" si="381"/>
-        <v>16.404</v>
+        <v>16.553000000000001</v>
       </c>
       <c r="Y53" s="13">
         <f t="shared" si="382"/>
-        <v>44.133000000000003</v>
+        <v>44.533000000000001</v>
       </c>
       <c r="Z53" s="18">
         <f t="shared" si="383"/>
-        <v>21.667000000000002</v>
+        <v>22.332999999999998</v>
       </c>
       <c r="AA53" s="14">
         <f t="shared" si="384"/>
-        <v>30.437999999999999</v>
+        <v>30.687999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5941,30 +5949,30 @@
       </c>
       <c r="B54" s="5">
         <f t="shared" ref="B54" si="385">D$2/D54</f>
-        <v>33.723675385647205</v>
+        <v>33.34350132625994</v>
       </c>
       <c r="C54" s="5">
         <f t="shared" ref="C54" si="386">D53/D54</f>
-        <v>1.004694835680751</v>
+        <v>1.0033156498673741</v>
       </c>
       <c r="D54" s="4">
         <f t="shared" ref="D54" si="387">SUM(F54:H54)</f>
-        <v>14.910000000000002</v>
+        <v>15.08</v>
       </c>
       <c r="E54" s="13">
         <v>0.4</v>
       </c>
       <c r="F54" s="9">
-        <v>7.53</v>
+        <v>7.61</v>
       </c>
       <c r="G54" s="9">
-        <v>6.73</v>
+        <v>6.81</v>
       </c>
       <c r="H54" s="9">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I54" s="10">
-        <v>4.6500000000000004</v>
+        <v>4.75</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>64</v>
@@ -6001,15 +6009,15 @@
       </c>
       <c r="T54" s="5">
         <f t="shared" ref="T54" si="391">ROUND(B54/K54,3)</f>
-        <v>0.52600000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" ref="U54" si="392">ROUND(C54/L54,3)</f>
-        <v>1.0049999999999999</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="V54" s="4">
         <f t="shared" ref="V54" si="393">ROUND(D54/M54,3)</f>
-        <v>22.937999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="W54" s="13">
         <f t="shared" ref="W54" si="394">ROUND(E54/N54,3)</f>
@@ -6017,19 +6025,19 @@
       </c>
       <c r="X54" s="18">
         <f t="shared" ref="X54" si="395">ROUND(F54/O54,3)</f>
-        <v>16.021000000000001</v>
+        <v>16.190999999999999</v>
       </c>
       <c r="Y54" s="18">
         <f t="shared" ref="Y54" si="396">ROUND(G54/P54,3)</f>
-        <v>44.866999999999997</v>
+        <v>45.4</v>
       </c>
       <c r="Z54" s="18">
         <f t="shared" ref="Z54" si="397">ROUND(H54/Q54,3)</f>
-        <v>21.667000000000002</v>
+        <v>22</v>
       </c>
       <c r="AA54" s="19">
         <f t="shared" ref="AA54" si="398">ROUND(I54/R54,3)</f>
-        <v>31</v>
+        <v>31.667000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6038,54 +6046,54 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:B56" si="399">D$2/D55</f>
-        <v>46.90485074626865</v>
+        <v>45.79417122040072</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" ref="C55:C56" si="400">D54/D55</f>
-        <v>1.3908582089552239</v>
+        <v>1.3734061930783241</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" ref="D55:D56" si="401">SUM(F55:H55)</f>
-        <v>10.72</v>
+        <v>10.98</v>
       </c>
       <c r="E55" s="9">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F55" s="9">
-        <v>7.18</v>
+        <v>7.4</v>
       </c>
       <c r="G55" s="13">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="H55" s="13">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="I55" s="14">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>65</v>
       </c>
       <c r="K55" s="2">
         <f t="shared" ref="K55:K56" si="402">M$2/M55</f>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" ref="L55:L56" si="403">M54/M55</f>
-        <v>1</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="M55" s="6">
         <f t="shared" ref="M55:M56" si="404">SUM(O55:Q55)</f>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N55" s="9">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O55" s="9">
         <v>0.47</v>
       </c>
       <c r="P55" s="13">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q55" s="13">
         <v>0.03</v>
@@ -6098,35 +6106,35 @@
       </c>
       <c r="T55" s="2">
         <f t="shared" ref="T55" si="405">ROUND(B55/K55,3)</f>
-        <v>0.73099999999999998</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="U55" s="2">
         <f t="shared" ref="U55" si="406">ROUND(C55/L55,3)</f>
-        <v>1.391</v>
+        <v>1.395</v>
       </c>
       <c r="V55" s="6">
         <f t="shared" ref="V55" si="407">ROUND(D55/M55,3)</f>
-        <v>16.492000000000001</v>
+        <v>16.635999999999999</v>
       </c>
       <c r="W55" s="9">
         <f t="shared" ref="W55" si="408">ROUND(E55/N55,3)</f>
-        <v>4.875</v>
+        <v>5.7140000000000004</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55" si="409">ROUND(F55/O55,3)</f>
-        <v>15.276999999999999</v>
+        <v>15.744999999999999</v>
       </c>
       <c r="Y55" s="13">
         <f t="shared" ref="Y55" si="410">ROUND(G55/P55,3)</f>
-        <v>22</v>
+        <v>20.812999999999999</v>
       </c>
       <c r="Z55" s="13">
         <f t="shared" ref="Z55" si="411">ROUND(H55/Q55,3)</f>
-        <v>8</v>
+        <v>8.3330000000000002</v>
       </c>
       <c r="AA55" s="14">
         <f t="shared" ref="AA55" si="412">ROUND(I55/R55,3)</f>
-        <v>18.2</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6135,37 +6143,37 @@
       </c>
       <c r="B56" s="5">
         <f t="shared" si="399"/>
-        <v>46.385608856088552</v>
+        <v>46.514338575393147</v>
       </c>
       <c r="C56" s="5">
         <f t="shared" si="400"/>
-        <v>0.98892988929889303</v>
+        <v>1.0157261794634598</v>
       </c>
       <c r="D56" s="4">
         <f t="shared" si="401"/>
-        <v>10.84</v>
+        <v>10.81</v>
       </c>
       <c r="E56" s="13">
         <v>0.39</v>
       </c>
       <c r="F56" s="18">
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="G56" s="18">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="H56" s="13">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I56" s="19">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>66</v>
       </c>
       <c r="K56" s="5">
         <f t="shared" si="402"/>
-        <v>64.169230769230751</v>
+        <v>63.196969696969681</v>
       </c>
       <c r="L56" s="5">
         <f t="shared" si="403"/>
@@ -6173,7 +6181,7 @@
       </c>
       <c r="M56" s="4">
         <f t="shared" si="404"/>
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N56" s="13">
         <v>0.06</v>
@@ -6182,7 +6190,7 @@
         <v>0.48</v>
       </c>
       <c r="P56" s="18">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q56" s="13">
         <v>0.02</v>
@@ -6195,15 +6203,15 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" ref="T56" si="413">ROUND(B56/K56,3)</f>
-        <v>0.72299999999999998</v>
+        <v>0.73599999999999999</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" ref="U56" si="414">ROUND(C56/L56,3)</f>
-        <v>0.98899999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="V56" s="4">
         <f t="shared" ref="V56" si="415">ROUND(D56/M56,3)</f>
-        <v>16.677</v>
+        <v>16.379000000000001</v>
       </c>
       <c r="W56" s="13">
         <f t="shared" ref="W56" si="416">ROUND(E56/N56,3)</f>
@@ -6211,21 +6219,215 @@
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56" si="417">ROUND(F56/O56,3)</f>
-        <v>15.208</v>
+        <v>15.083</v>
       </c>
       <c r="Y56" s="18">
         <f t="shared" ref="Y56" si="418">ROUND(G56/P56,3)</f>
-        <v>22.067</v>
+        <v>20.75</v>
       </c>
       <c r="Z56" s="13">
         <f t="shared" ref="Z56" si="419">ROUND(H56/Q56,3)</f>
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA56" s="19">
         <f t="shared" ref="AA56" si="420">ROUND(I56/R56,3)</f>
-        <v>18.2</v>
+        <v>18.466999999999999</v>
       </c>
       <c r="AB56" s="20"/>
+    </row>
+    <row r="57" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="2">
+        <f t="shared" ref="B57:B58" si="421">D$2/D57</f>
+        <v>50.031840796019893</v>
+      </c>
+      <c r="C57" s="2">
+        <f t="shared" ref="C57:C58" si="422">D56/D57</f>
+        <v>1.0756218905472636</v>
+      </c>
+      <c r="D57" s="6">
+        <f t="shared" ref="D57:D58" si="423">SUM(F57:H57)</f>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="F57" s="13">
+        <v>6.64</v>
+      </c>
+      <c r="G57" s="13">
+        <v>3.18</v>
+      </c>
+      <c r="H57" s="13">
+        <v>0.23</v>
+      </c>
+      <c r="I57" s="14">
+        <v>2.61</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K57" s="2">
+        <f t="shared" ref="K57:K58" si="424">M$2/M57</f>
+        <v>65.171874999999986</v>
+      </c>
+      <c r="L57" s="2">
+        <f t="shared" ref="L57:L58" si="425">M56/M57</f>
+        <v>1.03125</v>
+      </c>
+      <c r="M57" s="6">
+        <f t="shared" ref="M57:M58" si="426">SUM(O57:Q57)</f>
+        <v>0.64</v>
+      </c>
+      <c r="N57" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="O57" s="13">
+        <v>0.47</v>
+      </c>
+      <c r="P57" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="Q57" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="R57" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S57" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="T57" s="2">
+        <f t="shared" ref="T57:T58" si="427">ROUND(B57/K57,3)</f>
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="U57" s="2">
+        <f t="shared" ref="U57:U58" si="428">ROUND(C57/L57,3)</f>
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="V57" s="6">
+        <f t="shared" ref="V57:V58" si="429">ROUND(D57/M57,3)</f>
+        <v>15.702999999999999</v>
+      </c>
+      <c r="W57" s="9">
+        <f t="shared" ref="W57:W58" si="430">ROUND(E57/N57,3)</f>
+        <v>6.5</v>
+      </c>
+      <c r="X57" s="13">
+        <f t="shared" ref="X57:X58" si="431">ROUND(F57/O57,3)</f>
+        <v>14.128</v>
+      </c>
+      <c r="Y57" s="13">
+        <f t="shared" ref="Y57:Y58" si="432">ROUND(G57/P57,3)</f>
+        <v>21.2</v>
+      </c>
+      <c r="Z57" s="13">
+        <f t="shared" ref="Z57:Z58" si="433">ROUND(H57/Q57,3)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AA57" s="14">
+        <f t="shared" ref="AA57:AA58" si="434">ROUND(I57/R57,3)</f>
+        <v>18.643000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="2">
+        <f t="shared" si="421"/>
+        <v>51.571282051282047</v>
+      </c>
+      <c r="C58" s="2">
+        <f t="shared" si="422"/>
+        <v>1.0307692307692309</v>
+      </c>
+      <c r="D58" s="6">
+        <f t="shared" si="423"/>
+        <v>9.75</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0.39</v>
+      </c>
+      <c r="F58" s="13">
+        <v>6.51</v>
+      </c>
+      <c r="G58" s="13">
+        <v>3.01</v>
+      </c>
+      <c r="H58" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="I58" s="14">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="J58" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K58" s="2">
+        <f t="shared" si="424"/>
+        <v>66.206349206349202</v>
+      </c>
+      <c r="L58" s="2">
+        <f t="shared" si="425"/>
+        <v>1.0158730158730158</v>
+      </c>
+      <c r="M58" s="6">
+        <f t="shared" si="426"/>
+        <v>0.63</v>
+      </c>
+      <c r="N58" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="O58" s="13">
+        <v>0.46</v>
+      </c>
+      <c r="P58" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="Q58" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="R58" s="14">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S58" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="T58" s="2">
+        <f t="shared" si="427"/>
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="U58" s="2">
+        <f t="shared" si="428"/>
+        <v>1.0149999999999999</v>
+      </c>
+      <c r="V58" s="6">
+        <f t="shared" si="429"/>
+        <v>15.476000000000001</v>
+      </c>
+      <c r="W58" s="9">
+        <f t="shared" si="430"/>
+        <v>5.5709999999999997</v>
+      </c>
+      <c r="X58" s="13">
+        <f t="shared" si="431"/>
+        <v>14.151999999999999</v>
+      </c>
+      <c r="Y58" s="13">
+        <f t="shared" si="432"/>
+        <v>20.067</v>
+      </c>
+      <c r="Z58" s="9">
+        <f t="shared" si="433"/>
+        <v>11.5</v>
+      </c>
+      <c r="AA58" s="14">
+        <f t="shared" si="434"/>
+        <v>17.5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
